--- a/molecule_data.xlsx
+++ b/molecule_data.xlsx
@@ -11272,7 +11272,7 @@
   <dimension ref="A1:N104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
@@ -11363,7 +11363,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>F001</t>
+          <t>F_CARBOXYLIC_ACID</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -11435,7 +11435,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>F002</t>
+          <t>F_AMINE_1</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -11507,7 +11507,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>F003</t>
+          <t>F_ALCOHOL_1</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -11579,7 +11579,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>F004</t>
+          <t>F_ESTER</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -11651,7 +11651,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>F005</t>
+          <t>F_ALKENE</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -11711,7 +11711,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>F006</t>
+          <t>F_ALKENE_TERMINAL</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -11771,7 +11771,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>F007</t>
+          <t>F_ALKYNE</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -11819,7 +11819,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>F008</t>
+          <t>F_ALKYNE_TERMINAL</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -11879,7 +11879,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -11939,7 +11939,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>F010</t>
+          <t>F_ALKYL_BROMIDE</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -11991,7 +11991,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>F011</t>
+          <t>F_ALKYL_CHLORIDE</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -12043,7 +12043,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>F012</t>
+          <t>F_ALKYL_IODIDE</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -12095,7 +12095,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>F013</t>
+          <t>F_ARYL_BROMIDE</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -12143,7 +12143,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>F014</t>
+          <t>F_ALCOHOL_SP3</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -12211,7 +12211,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>F015</t>
+          <t>F_ALCOHOL_2</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -12275,7 +12275,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>F016</t>
+          <t>F_ALCOHOL_3</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -12339,7 +12339,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>F017</t>
+          <t>F_DIOL_1_2</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -12395,7 +12395,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>F018</t>
+          <t>F_ALDEHYDE</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -12459,7 +12459,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>F019</t>
+          <t>F_KETONE</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -12519,7 +12519,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>F020</t>
+          <t>F_ACYL_CHLORIDE</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -12575,7 +12575,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>F021</t>
+          <t>F_AMIDE</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -12643,7 +12643,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>F022</t>
+          <t>F_NITRILE</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -12703,7 +12703,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>F023</t>
+          <t>F_EPOXIDE</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -12755,7 +12755,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>F024</t>
+          <t>F_ETHER_DIALKYL</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -12811,7 +12811,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>F025</t>
+          <t>F_NITROARENE</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -12855,7 +12855,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>F026</t>
+          <t>F_ARYLAMINE</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -12919,7 +12919,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>F027</t>
+          <t>F_ARYL_DIAZONIUM</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -12971,7 +12971,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>F028</t>
+          <t>F_PHENOL</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -13027,7 +13027,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>F029</t>
+          <t>F_GRIGNARD</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -13083,7 +13083,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>F030</t>
+          <t>F_CONJUGATED_DIENE</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -13131,7 +13131,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>F031</t>
+          <t>F_IMINE</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -13183,7 +13183,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>F032</t>
+          <t>F_VICINAL_DIBROMIDE</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -13235,7 +13235,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>F033</t>
+          <t>F_BROMOHYDRIN</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -13287,7 +13287,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>F034</t>
+          <t>F_AMINE_2</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -13347,7 +13347,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>F035</t>
+          <t>F_ARYL_METHYL</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -13407,7 +13407,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>F036</t>
+          <t>F_BENZYLIC_BROMIDE</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -13459,7 +13459,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>F037</t>
+          <t>F_ALLYLIC_CH2</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -13515,7 +13515,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>F038</t>
+          <t>F_ALKYL_ARENE</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -13559,7 +13559,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>F039</t>
+          <t>F_ACETAL_KETAL</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -13603,7 +13603,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>F040</t>
+          <t>F_ENONE</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -13651,7 +13651,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>F043</t>
+          <t>F_METHYL_HALIDE</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -13707,7 +13707,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>F044</t>
+          <t>F_ALKYL_HALIDE_1</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -13763,7 +13763,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>F045</t>
+          <t>F_ALKYL_HALIDE_2</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -13819,7 +13819,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>F046</t>
+          <t>F_ALKYL_HALIDE_3</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -13875,7 +13875,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>F042</t>
+          <t>F_ALUMINIUM_HYDRIDE</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -13931,7 +13931,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>F041</t>
+          <t>F_ANHYDRIDE</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -13979,7 +13979,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>F047</t>
+          <t>F_ARYL_CHLORIDE</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -14031,7 +14031,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>F048</t>
+          <t>F_ARENESULFONIC_ACID</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -14087,7 +14087,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>F049</t>
+          <t>F_OXIME</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -14147,7 +14147,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>F050</t>
+          <t>F_ARYL_ALKYL_ETHER</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -14215,7 +14215,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>F051</t>
+          <t>F_IMIDATE</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -14283,7 +14283,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>F052</t>
+          <t>F_SILYL_ETHER</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -14351,7 +14351,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>F053</t>
+          <t>F_C_SILYL</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -14415,7 +14415,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>F054</t>
+          <t>F_CHLOROSILANE</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -14471,7 +14471,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>F055</t>
+          <t>F_AZIDE</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -14539,7 +14539,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>F056</t>
+          <t>F_NITROALKANE</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -14600,14 +14600,14 @@
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>Reduction goes through the nitroso and hydroxylamine stages. Nitroarenes are F025 [learned from the recorded reactions of templates T000270, T004730; RDKit: consumed (count drops from starting materials to product) in 8 of 8 example reactions of the templates it covers; found in 0.1% of 20,000 recorded products]</t>
+          <t>Reduction goes through the nitroso and hydroxylamine stages. Nitroarenes are F_NITROARENE [learned from the recorded reactions of templates T000270, T004730; RDKit: consumed (count drops from starting materials to product) in 8 of 8 example reactions of the templates it covers; found in 0.1% of 20,000 recorded products]</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>F057</t>
+          <t>F_NITROSO</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -14671,7 +14671,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>F058</t>
+          <t>F_CARBOXYLATE</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -14732,14 +14732,14 @@
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>Li/Na/K salts from saponification are recorded as carboxylates and are often carried forward directly. Resonance (two equal C–O bonds) makes the carbonyl very unreactive. The anionic form is missed by F001 (carboxylic acid). T002523 (salt → 1° alcohol with Na/MeOH) is a data oddity: Na/ROH (Bouveault–Blanc) reduces esters, not carboxylate salts, which do not react under these conditions. The recorded substrate was probably the ester [learned from the recorded reactions of templates T000180, T001902, T002404, T002523, T003623; RDKit: consumed (count drops from starting materials to product) in 20 of 20 example reactions of the templates it covers; found in 0.3% of 20,000 recorded products]</t>
+          <t>Li/Na/K salts from saponification are recorded as carboxylates and are often carried forward directly. Resonance (two equal C–O bonds) makes the carbonyl very unreactive. The anionic form is missed by F_CARBOXYLIC_ACID (carboxylic acid). T002523 (salt → 1° alcohol with Na/MeOH) is a data oddity: Na/ROH (Bouveault–Blanc) reduces esters, not carboxylate salts, which do not react under these conditions. The recorded substrate was probably the ester [learned from the recorded reactions of templates T000180, T001902, T002404, T002523, T003623; RDKit: consumed (count drops from starting materials to product) in 20 of 20 example reactions of the templates it covers; found in 0.3% of 20,000 recorded products]</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>F059</t>
+          <t>F_SULFINATE_SULFONATE</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -14800,14 +14800,14 @@
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>Anionic forms are missed by F048 (arenesulfonic acid). Sulfinic acids are unstable and disproportionate, so sulfinates are stored as Na salts. Carboxylates are a separate fragment [learned from the recorded reactions of templates T004902, T005667, T005812; RDKit: consumed (count drops from starting materials to product) in 12 of 12 example reactions of the templates it covers; found in 0.0% of 20,000 recorded products]</t>
+          <t>Anionic forms are missed by F_ARENESULFONIC_ACID (arenesulfonic acid). Sulfinic acids are unstable and disproportionate, so sulfinates are stored as Na salts. Carboxylates are a separate fragment [learned from the recorded reactions of templates T004902, T005667, T005812; RDKit: consumed (count drops from starting materials to product) in 12 of 12 example reactions of the templates it covers; found in 0.0% of 20,000 recorded products]</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>F060</t>
+          <t>F_HYDROXIDE_ALKOXIDE</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -14867,7 +14867,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>F061</t>
+          <t>F_CYANIDE</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -14931,7 +14931,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>F062</t>
+          <t>F_CYANOGEN_HALIDE</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -14987,7 +14987,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>F063</t>
+          <t>F_PEROXIDE</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -15047,7 +15047,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>F064</t>
+          <t>F_SULFONYL_CHLORIDE</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -15103,7 +15103,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>F065</t>
+          <t>F_ARYL_ENOL_SULFONATE</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -15159,7 +15159,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>F066</t>
+          <t>F_ALKYL_SULFONATE</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -15215,7 +15215,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>F067</t>
+          <t>F_SULFONAMIDE_1</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -15279,7 +15279,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>F068</t>
+          <t>F_SULFONAMIDE_2</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -15347,7 +15347,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>F069</t>
+          <t>F_BIS_SULFONYLAMINE</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -15403,7 +15403,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>F070</t>
+          <t>F_SULFINAMIDE</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -15471,7 +15471,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>F071</t>
+          <t>F_SULFONE_SULFOXIDE</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -15539,7 +15539,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>F072</t>
+          <t>F_THIOL</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -15607,7 +15607,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>F073</t>
+          <t>F_THIOETHER</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -15675,7 +15675,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>F074</t>
+          <t>F_THIOESTER</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -15739,7 +15739,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>F075</t>
+          <t>F_THIOACETATE_ANION</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -15803,7 +15803,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>F076</t>
+          <t>F_THIOCARBONYL</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -15871,7 +15871,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>F077</t>
+          <t>F_CARBAMATE</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -15932,14 +15932,14 @@
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>Covers N-Boc azoles (T000457 and T000566, removed by TFA or HCl) and N-ethoxycarbonyl sulfoximines (T003015, removed by base). An N-Boc group also matches F021 (amide) and the tert-butyl fragment; this one marks the whole N–CO2R unit that is lost on deprotection. Its N–H, when present, is the amide/carbamate N–H fragment [learned from the recorded reactions of templates T000457, T000566, T003015; RDKit: consumed (count drops from starting materials to product) in 12 of 12 example reactions of the templates it covers; found in 10.2% of 20,000 recorded products]</t>
+          <t>Covers N-Boc azoles (T000457 and T000566, removed by TFA or HCl) and N-ethoxycarbonyl sulfoximines (T003015, removed by base). An N-Boc group also matches F_AMIDE (amide) and the tert-butyl fragment; this one marks the whole N–CO2R unit that is lost on deprotection. Its N–H, when present, is the amide/carbamate N–H fragment [learned from the recorded reactions of templates T000457, T000566, T003015; RDKit: consumed (count drops from starting materials to product) in 12 of 12 example reactions of the templates it covers; found in 10.2% of 20,000 recorded products]</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>F078</t>
+          <t>F_TERT_BUTYL_GROUP</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -15996,14 +15996,14 @@
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>Cation scavengers (Et3SiH, anisole) protect electron-rich arenes. Trapping by solvent can give transesterified products (ethyl/isopropyl/methyl ester or carbamate; T001529 records t-Bu ester → methyl ester). Di-t-Bu phosphates (prodrugs) lose both t-Bu groups. On N, only t-Bu groups that leave easily in acid are matched (ring N of azoles, sulfonamide N–H, the N–H of a 2-aminoazine); ordinary t-Bu amines and amides (tBuNH2, tBuNHAc) and C-t-Bu groups are not. N-alkylation of Boc-NH (T007010) keeps the t-Bu and counts under amide/carbamate N–H. Overlaps the carbamate, carbonate and ester (F004) fragments, but this is the group consumed on acid deprotection [learned from the recorded reactions of templates T003260, T004791, T005289, T003156, T005573, T003741…; RDKit: consumed (count drops from starting materials to product) in 88 of 88 example reactions of the templates it covers; found in 8.8% of 20,000 recorded products]</t>
+          <t>Cation scavengers (Et3SiH, anisole) protect electron-rich arenes. Trapping by solvent can give transesterified products (ethyl/isopropyl/methyl ester or carbamate; T001529 records t-Bu ester → methyl ester). Di-t-Bu phosphates (prodrugs) lose both t-Bu groups. On N, only t-Bu groups that leave easily in acid are matched (ring N of azoles, sulfonamide N–H, the N–H of a 2-aminoazine); ordinary t-Bu amines and amides (tBuNH2, tBuNHAc) and C-t-Bu groups are not. N-alkylation of Boc-NH (T007010) keeps the t-Bu and counts under amide/carbamate N–H. Overlaps the carbamate, carbonate and ester (F_ESTER) fragments, but this is the group consumed on acid deprotection [learned from the recorded reactions of templates T003260, T004791, T005289, T003156, T005573, T003741…; RDKit: consumed (count drops from starting materials to product) in 88 of 88 example reactions of the templates it covers; found in 8.8% of 20,000 recorded products]</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>F079</t>
+          <t>F_CARBONATE</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -16059,7 +16059,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>F080</t>
+          <t>F_N_ACYL_AZOLE</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -16123,7 +16123,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>F081</t>
+          <t>F_BORONIC_ACID</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -16187,7 +16187,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>F082</t>
+          <t>F_PINACOL_BORONATE</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -16251,7 +16251,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>F083</t>
+          <t>F_ORGANOSTANNANE</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -16307,7 +16307,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>F084</t>
+          <t>F_ARYL_IODIDE</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -16363,7 +16363,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>F085</t>
+          <t>F_ARYL_FLUORIDE_SNAR</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -16419,7 +16419,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>F086</t>
+          <t>F_HALO_AZINE</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -16483,7 +16483,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>F087</t>
+          <t>F_VINYL_ALKYNYL_HALIDE</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -16539,7 +16539,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>F088</t>
+          <t>F_IMIDOYL_CHLORIDE</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -16591,7 +16591,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>F089</t>
+          <t>F_AZOLE_NH</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -16659,7 +16659,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>F090</t>
+          <t>F_PYRIDONE_NH</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -16720,14 +16720,14 @@
       </c>
       <c r="N91" s="3" t="inlineStr">
         <is>
-          <t>Lactam ⇌ lactim (hydroxy-azine) tautomers: matched only in the lactam form c(=O)[nH], the usual way they are drawn; a structure drawn as the hydroxy-azine (Oc1ccccn1) is not matched and reads as a phenol (F028). Deoxychlorination: POCl3 neat at reflux, often with DIPEA, PhNEt2 or DMF (Vilsmeier). Uracil-type rings carry two N–H, and usually only one reacts. N-substituted pyridones (no N–H) are not matched and cannot be chlorinated this way. 5-ring lactam N–H (benzimidazolone, tetrazolone) belongs to the azole N–H fragment; 2-thiopyridones/thiouracils to the thiol/thione fragment [learned from the recorded reactions of templates T000346, T000421, T000502, T000572, T000855, T000913…; RDKit: consumed (count drops from starting materials to product) in 130 of 148 example reactions of the templates it covers; found in 2.0% of 20,000 recorded products]</t>
+          <t>Lactam ⇌ lactim (hydroxy-azine) tautomers: matched only in the lactam form c(=O)[nH], the usual way they are drawn; a structure drawn as the hydroxy-azine (Oc1ccccn1) is not matched and reads as a phenol (F_PHENOL). Deoxychlorination: POCl3 neat at reflux, often with DIPEA, PhNEt2 or DMF (Vilsmeier). Uracil-type rings carry two N–H, and usually only one reacts. N-substituted pyridones (no N–H) are not matched and cannot be chlorinated this way. 5-ring lactam N–H (benzimidazolone, tetrazolone) belongs to the azole N–H fragment; 2-thiopyridones/thiouracils to the thiol/thione fragment [learned from the recorded reactions of templates T000346, T000421, T000502, T000572, T000855, T000913…; RDKit: consumed (count drops from starting materials to product) in 130 of 148 example reactions of the templates it covers; found in 2.0% of 20,000 recorded products]</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>F091</t>
+          <t>F_AZINE_N</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -16791,7 +16791,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>F092</t>
+          <t>F_AZINE_N_OXIDE</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -16855,7 +16855,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>F093</t>
+          <t>F_AMINE_3</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -16923,7 +16923,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>F094</t>
+          <t>F_ARYLAMINE_2</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -16984,14 +16984,14 @@
       </c>
       <c r="N95" s="3" t="inlineStr">
         <is>
-          <t>The N lone pair is shared with the ring, so it is about 10⁵ times less basic than a dialkylamine, yet it still acylates and sulfonylates readily. Includes indolines, tetrahydroquinolines and 2-(alkylamino)-azines/azoles (F034 covers dialkyl 2° amines; F026 covers ArNH2). N-Nitrosamines are carcinogenic. EDC cyclisation of o-(alkylamino)aryl thioureas (T003860) is not counted: a new ArNH appears in the product [learned from the recorded reactions of templates T001076, T001185, T001521, T001842, T001902, T002544…; RDKit: consumed (count drops from starting materials to product) in 116 of 116 example reactions of the templates it covers; found in 10.5% of 20,000 recorded products]</t>
+          <t>The N lone pair is shared with the ring, so it is about 10⁵ times less basic than a dialkylamine, yet it still acylates and sulfonylates readily. Includes indolines, tetrahydroquinolines and 2-(alkylamino)-azines/azoles (F_AMINE_2 covers dialkyl 2° amines; F_ARYLAMINE covers ArNH2). N-Nitrosamines are carcinogenic. EDC cyclisation of o-(alkylamino)aryl thioureas (T003860) is not counted: a new ArNH appears in the product [learned from the recorded reactions of templates T001076, T001185, T001521, T001842, T001902, T002544…; RDKit: consumed (count drops from starting materials to product) in 116 of 116 example reactions of the templates it covers; found in 10.5% of 20,000 recorded products]</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>F095</t>
+          <t>F_AMIDE_NH</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -17052,14 +17052,14 @@
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
-          <t>Overlaps F021 (amide), which survives these reactions; this fragment marks the N–H that is replaced. Includes anilide, oxindole, lactam, carbamate (Boc-NH), urea, imide and primary amide N–H. An N-sulfonyl lactam (from a sulfonyl chloride) is an activated amide and can over-react (ring-opening by the nucleophile or base). Goldberg arylation of a primary amide (T007479) is not counted: the product still has an amide N–H [learned from the recorded reactions of templates T000589, T001359, T001444, T001683, T002572, T002736…; RDKit: consumed (count drops from starting materials to product) in 64 of 64 example reactions of the templates it covers; found in 26.4% of 20,000 recorded products]</t>
+          <t>Overlaps F_AMIDE (amide), which survives these reactions; this fragment marks the N–H that is replaced. Includes anilide, oxindole, lactam, carbamate (Boc-NH), urea, imide and primary amide N–H. An N-sulfonyl lactam (from a sulfonyl chloride) is an activated amide and can over-react (ring-opening by the nucleophile or base). Goldberg arylation of a primary amide (T007479) is not counted: the product still has an amide N–H [learned from the recorded reactions of templates T000589, T001359, T001444, T001683, T002572, T002736…; RDKit: consumed (count drops from starting materials to product) in 64 of 64 example reactions of the templates it covers; found in 26.4% of 20,000 recorded products]</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>F096</t>
+          <t>F_HYDRAZINE</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -17123,7 +17123,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>F097</t>
+          <t>F_HYDROXYLAMINE</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -17187,7 +17187,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>F098</t>
+          <t>F_AMIDINE</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -17251,7 +17251,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>F099</t>
+          <t>F_AMIDOXIME</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -17315,7 +17315,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>F100</t>
+          <t>F_ISOCYANATE</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -17371,7 +17371,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>F101</t>
+          <t>F_ENOLISABLE_CH</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -17432,14 +17432,14 @@
       </c>
       <c r="N102" s="3" t="inlineStr">
         <is>
-          <t>Counted once per α carbon; marks the α position that changes while the C=O or C≡N (F018/F019/F004/F022) survives. In acid, halogenation stops at one halogen (the halogen slows the next enolisation); in base it goes on to polyhalogenation or the haloform reaction. Excludes α carbons that already carry a halogen (the halogenation products), 1,3-dicarbonyl and cyano-carbonyl CH2 (see active methylene), acids, carboxylates and amides. Mono-alkylation of an α-CH2 (T006533) and Claisen/C-carbamoylation steps that keep an α-C–H (T005625, T004253, T004637) are not counted [learned from the recorded reactions of templates T000196, T000670, T000684, T001549, T002158, T002358…; RDKit: consumed (count drops from starting materials to product) in 84 of 84 example reactions of the templates it covers; found in 15.5% of 20,000 recorded products]</t>
+          <t>Counted once per α carbon; marks the α position that changes while the C=O or C≡N (F_ALDEHYDE/F_KETONE/F_ESTER/F_NITRILE) survives. In acid, halogenation stops at one halogen (the halogen slows the next enolisation); in base it goes on to polyhalogenation or the haloform reaction. Excludes α carbons that already carry a halogen (the halogenation products), 1,3-dicarbonyl and cyano-carbonyl CH2 (see active methylene), acids, carboxylates and amides. Mono-alkylation of an α-CH2 (T006533) and Claisen/C-carbamoylation steps that keep an α-C–H (T005625, T004253, T004637) are not counted [learned from the recorded reactions of templates T000196, T000670, T000684, T001549, T002158, T002358…; RDKit: consumed (count drops from starting materials to product) in 84 of 84 example reactions of the templates it covers; found in 15.5% of 20,000 recorded products]</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>F102</t>
+          <t>F_ACTIVE_METHYLENE</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -17503,7 +17503,7 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>F103</t>
+          <t>F_PHOSPHONATE</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>F001</t>
+          <t>F_CARBOXYLIC_ACID</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -17668,7 +17668,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>F002</t>
+          <t>F_AMINE_1</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -17700,7 +17700,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>F001</t>
+          <t>F_CARBOXYLIC_ACID</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -17732,7 +17732,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>F003</t>
+          <t>F_ALCOHOL_1</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -17764,7 +17764,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>F004</t>
+          <t>F_ESTER</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -17796,7 +17796,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>F005</t>
+          <t>F_ALKENE</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -17828,7 +17828,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>F006</t>
+          <t>F_ALKENE_TERMINAL</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -17860,7 +17860,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>F010</t>
+          <t>F_ALKYL_BROMIDE</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>F014</t>
+          <t>F_ALCOHOL_SP3</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>F016</t>
+          <t>F_ALCOHOL_3</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -17956,7 +17956,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>F033</t>
+          <t>F_BROMOHYDRIN</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -17988,7 +17988,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>F044</t>
+          <t>F_ALKYL_HALIDE_1</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -18020,7 +18020,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>F005</t>
+          <t>F_ALKENE</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -18052,7 +18052,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>F037</t>
+          <t>F_ALLYLIC_CH2</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -18084,7 +18084,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>F037</t>
+          <t>F_ALLYLIC_CH2</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>F010</t>
+          <t>F_ALKYL_BROMIDE</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -18148,7 +18148,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>F010</t>
+          <t>F_ALKYL_BROMIDE</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>F032</t>
+          <t>F_VICINAL_DIBROMIDE</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -18212,7 +18212,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>F045</t>
+          <t>F_ALKYL_HALIDE_2</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -18244,7 +18244,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>F045</t>
+          <t>F_ALKYL_HALIDE_2</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -18276,7 +18276,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>F005</t>
+          <t>F_ALKENE</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -18308,7 +18308,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>F006</t>
+          <t>F_ALKENE_TERMINAL</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -18340,7 +18340,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>F010</t>
+          <t>F_ALKYL_BROMIDE</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -18372,7 +18372,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>F044</t>
+          <t>F_ALKYL_HALIDE_1</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -18404,7 +18404,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>F010</t>
+          <t>F_ALKYL_BROMIDE</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -18436,7 +18436,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>F045</t>
+          <t>F_ALKYL_HALIDE_2</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -18468,7 +18468,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>F014</t>
+          <t>F_ALCOHOL_SP3</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -18500,7 +18500,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>F016</t>
+          <t>F_ALCOHOL_3</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -18532,7 +18532,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>F003</t>
+          <t>F_ALCOHOL_1</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>F014</t>
+          <t>F_ALCOHOL_SP3</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -18596,7 +18596,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -18660,7 +18660,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -18692,7 +18692,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -18724,7 +18724,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>F047</t>
+          <t>F_ARYL_CHLORIDE</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -18756,7 +18756,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>F063</t>
+          <t>F_PEROXIDE</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>F023</t>
+          <t>F_EPOXIDE</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -18820,7 +18820,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>F001</t>
+          <t>F_CARBOXYLIC_ACID</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -18852,7 +18852,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -18884,7 +18884,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -18916,7 +18916,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -18948,7 +18948,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -18980,7 +18980,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>F047</t>
+          <t>F_ARYL_CHLORIDE</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>F014</t>
+          <t>F_ALCOHOL_SP3</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -19044,7 +19044,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>F014</t>
+          <t>F_ALCOHOL_SP3</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -19076,7 +19076,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>F015</t>
+          <t>F_ALCOHOL_2</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -19108,7 +19108,7 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>F015</t>
+          <t>F_ALCOHOL_2</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -19140,7 +19140,7 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>F017</t>
+          <t>F_DIOL_1_2</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -19172,7 +19172,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>F005</t>
+          <t>F_ALKENE</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -19204,7 +19204,7 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>F018</t>
+          <t>F_ALDEHYDE</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -19236,7 +19236,7 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>F101</t>
+          <t>F_ENOLISABLE_CH</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -19268,7 +19268,7 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>F019</t>
+          <t>F_KETONE</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -19300,7 +19300,7 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>F101</t>
+          <t>F_ENOLISABLE_CH</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -19332,7 +19332,7 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>F101</t>
+          <t>F_ENOLISABLE_CH</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -19364,7 +19364,7 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>F021</t>
+          <t>F_AMIDE</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -19396,7 +19396,7 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>F021</t>
+          <t>F_AMIDE</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -19428,7 +19428,7 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>F005</t>
+          <t>F_ALKENE</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -19460,7 +19460,7 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>F010</t>
+          <t>F_ALKYL_BROMIDE</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -19492,7 +19492,7 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>F037</t>
+          <t>F_ALLYLIC_CH2</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -19524,7 +19524,7 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>F045</t>
+          <t>F_ALKYL_HALIDE_2</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -19556,7 +19556,7 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>F021</t>
+          <t>F_AMIDE</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -19588,7 +19588,7 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>F021</t>
+          <t>F_AMIDE</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -19620,7 +19620,7 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>F095</t>
+          <t>F_AMIDE_NH</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -19652,7 +19652,7 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>F095</t>
+          <t>F_AMIDE_NH</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>F007</t>
+          <t>F_ALKYNE</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -19716,7 +19716,7 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>F005</t>
+          <t>F_ALKENE</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>F005</t>
+          <t>F_ALKENE</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -19780,7 +19780,7 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>F007</t>
+          <t>F_ALKYNE</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -19812,7 +19812,7 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>F008</t>
+          <t>F_ALKYNE_TERMINAL</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -19844,7 +19844,7 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -19876,7 +19876,7 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -19908,7 +19908,7 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -19940,7 +19940,7 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
@@ -19972,7 +19972,7 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -20004,7 +20004,7 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -20036,7 +20036,7 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -20068,7 +20068,7 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -20100,7 +20100,7 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -20132,7 +20132,7 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -20164,7 +20164,7 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>F013</t>
+          <t>F_ARYL_BROMIDE</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -20228,7 +20228,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -20260,7 +20260,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -20292,7 +20292,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -20324,7 +20324,7 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -20388,7 +20388,7 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>F025</t>
+          <t>F_NITROARENE</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -20420,7 +20420,7 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>F020</t>
+          <t>F_ACYL_CHLORIDE</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -20452,7 +20452,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -20484,7 +20484,7 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -20516,7 +20516,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -20548,7 +20548,7 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -20580,7 +20580,7 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
@@ -20612,7 +20612,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>F019</t>
+          <t>F_KETONE</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -20644,7 +20644,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>F101</t>
+          <t>F_ENOLISABLE_CH</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -20676,7 +20676,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>F011</t>
+          <t>F_ALKYL_CHLORIDE</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -20708,7 +20708,7 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>F046</t>
+          <t>F_ALKYL_HALIDE_3</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -20772,7 +20772,7 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -20836,7 +20836,7 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
@@ -20868,7 +20868,7 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -20900,7 +20900,7 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>F038</t>
+          <t>F_ALKYL_ARENE</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
@@ -20932,7 +20932,7 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
@@ -20964,7 +20964,7 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
@@ -20996,7 +20996,7 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
@@ -21028,7 +21028,7 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
@@ -21060,7 +21060,7 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
@@ -21092,7 +21092,7 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>F035</t>
+          <t>F_ARYL_METHYL</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
@@ -21124,7 +21124,7 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>F038</t>
+          <t>F_ALKYL_ARENE</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
@@ -21156,7 +21156,7 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
@@ -21188,7 +21188,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
@@ -21220,7 +21220,7 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
@@ -21252,7 +21252,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
@@ -21284,7 +21284,7 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
@@ -21316,7 +21316,7 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>F010</t>
+          <t>F_ALKYL_BROMIDE</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
@@ -21348,7 +21348,7 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>F036</t>
+          <t>F_BENZYLIC_BROMIDE</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
@@ -21380,7 +21380,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>F038</t>
+          <t>F_ALKYL_ARENE</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -21412,7 +21412,7 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>F044</t>
+          <t>F_ALKYL_HALIDE_1</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
@@ -21444,7 +21444,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>F001</t>
+          <t>F_CARBOXYLIC_ACID</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -21476,7 +21476,7 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
@@ -21508,7 +21508,7 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
@@ -21540,7 +21540,7 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
@@ -21572,7 +21572,7 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
@@ -21604,7 +21604,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
@@ -21636,7 +21636,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>F002</t>
+          <t>F_AMINE_1</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
@@ -21668,7 +21668,7 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
@@ -21700,7 +21700,7 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
@@ -21732,7 +21732,7 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
@@ -21764,7 +21764,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -21796,7 +21796,7 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
@@ -21828,7 +21828,7 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>F026</t>
+          <t>F_ARYLAMINE</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
@@ -21860,7 +21860,7 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
@@ -21892,7 +21892,7 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
@@ -21956,7 +21956,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
@@ -21988,7 +21988,7 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
@@ -22020,7 +22020,7 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>F027</t>
+          <t>F_ARYL_DIAZONIUM</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
@@ -22052,7 +22052,7 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>F010</t>
+          <t>F_ALKYL_BROMIDE</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
@@ -22084,7 +22084,7 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>F044</t>
+          <t>F_ALKYL_HALIDE_1</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
@@ -22116,7 +22116,7 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>F061</t>
+          <t>F_CYANIDE</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
@@ -22148,7 +22148,7 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>F022</t>
+          <t>F_NITRILE</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
@@ -22180,7 +22180,7 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>F101</t>
+          <t>F_ENOLISABLE_CH</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
@@ -22212,7 +22212,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>F010</t>
+          <t>F_ALKYL_BROMIDE</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
@@ -22244,7 +22244,7 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>F044</t>
+          <t>F_ALKYL_HALIDE_1</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
@@ -22276,7 +22276,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>F060</t>
+          <t>F_HYDROXIDE_ALKOXIDE</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
@@ -22308,7 +22308,7 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>F024</t>
+          <t>F_ETHER_DIALKYL</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
@@ -22340,7 +22340,7 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>F011</t>
+          <t>F_ALKYL_CHLORIDE</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
@@ -22372,7 +22372,7 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>F044</t>
+          <t>F_ALKYL_HALIDE_1</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
@@ -22404,7 +22404,7 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>F012</t>
+          <t>F_ALKYL_IODIDE</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
@@ -22436,7 +22436,7 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>F044</t>
+          <t>F_ALKYL_HALIDE_1</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
@@ -22468,7 +22468,7 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>F010</t>
+          <t>F_ALKYL_BROMIDE</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
@@ -22500,7 +22500,7 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>F046</t>
+          <t>F_ALKYL_HALIDE_3</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
@@ -22532,7 +22532,7 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>F060</t>
+          <t>F_HYDROXIDE_ALKOXIDE</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
@@ -22564,7 +22564,7 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>F005</t>
+          <t>F_ALKENE</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
@@ -22596,7 +22596,7 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>F006</t>
+          <t>F_ALKENE_TERMINAL</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
@@ -22628,7 +22628,7 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>F037</t>
+          <t>F_ALLYLIC_CH2</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
@@ -22660,7 +22660,7 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>F003</t>
+          <t>F_ALCOHOL_1</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>F014</t>
+          <t>F_ALCOHOL_SP3</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
@@ -22724,7 +22724,7 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
@@ -22756,7 +22756,7 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
@@ -22788,7 +22788,7 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
@@ -22820,7 +22820,7 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
@@ -22852,7 +22852,7 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>F018</t>
+          <t>F_ALDEHYDE</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
@@ -22916,7 +22916,7 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>F101</t>
+          <t>F_ENOLISABLE_CH</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
@@ -22948,7 +22948,7 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>F001</t>
+          <t>F_CARBOXYLIC_ACID</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
@@ -22980,7 +22980,7 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>F014</t>
+          <t>F_ALCOHOL_SP3</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
@@ -23012,7 +23012,7 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>F015</t>
+          <t>F_ALCOHOL_2</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
@@ -23076,7 +23076,7 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
@@ -23108,7 +23108,7 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -23140,7 +23140,7 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
@@ -23172,7 +23172,7 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
@@ -23204,7 +23204,7 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>F020</t>
+          <t>F_ACYL_CHLORIDE</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
@@ -23236,7 +23236,7 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>F019</t>
+          <t>F_KETONE</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
@@ -23268,7 +23268,7 @@
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>F101</t>
+          <t>F_ENOLISABLE_CH</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
@@ -23300,7 +23300,7 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>F101</t>
+          <t>F_ENOLISABLE_CH</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
@@ -23332,7 +23332,7 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>F004</t>
+          <t>F_ESTER</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
@@ -23364,7 +23364,7 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
@@ -23396,7 +23396,7 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
@@ -23428,7 +23428,7 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
@@ -23460,7 +23460,7 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
@@ -23492,7 +23492,7 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
@@ -23524,7 +23524,7 @@
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>F042</t>
+          <t>F_ALUMINIUM_HYDRIDE</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
@@ -23556,7 +23556,7 @@
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>F003</t>
+          <t>F_ALCOHOL_1</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
@@ -23588,7 +23588,7 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
@@ -23620,7 +23620,7 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
@@ -23652,7 +23652,7 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
@@ -23684,7 +23684,7 @@
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
@@ -23716,7 +23716,7 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
@@ -23748,7 +23748,7 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>F014</t>
+          <t>F_ALCOHOL_SP3</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
@@ -23780,7 +23780,7 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>F038</t>
+          <t>F_ALKYL_ARENE</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
@@ -23812,7 +23812,7 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>F014</t>
+          <t>F_ALCOHOL_SP3</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
@@ -23844,7 +23844,7 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>F029</t>
+          <t>F_GRIGNARD</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
@@ -23876,7 +23876,7 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
@@ -23908,7 +23908,7 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
@@ -23940,7 +23940,7 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
@@ -24004,7 +24004,7 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
@@ -24036,7 +24036,7 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>F029</t>
+          <t>F_GRIGNARD</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
@@ -24068,7 +24068,7 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
@@ -24100,7 +24100,7 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
@@ -24132,7 +24132,7 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
@@ -24228,7 +24228,7 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
@@ -24260,7 +24260,7 @@
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
@@ -24292,7 +24292,7 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
@@ -24324,7 +24324,7 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
@@ -24356,7 +24356,7 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
@@ -24388,7 +24388,7 @@
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
@@ -24420,7 +24420,7 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
@@ -24452,7 +24452,7 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
@@ -24484,7 +24484,7 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
@@ -24516,7 +24516,7 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
@@ -24548,7 +24548,7 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>F005</t>
+          <t>F_ALKENE</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
@@ -24580,7 +24580,7 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>F006</t>
+          <t>F_ALKENE_TERMINAL</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
@@ -24612,7 +24612,7 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>F037</t>
+          <t>F_ALLYLIC_CH2</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>F037</t>
+          <t>F_ALLYLIC_CH2</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
@@ -24676,7 +24676,7 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
@@ -24708,7 +24708,7 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
@@ -24740,7 +24740,7 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
@@ -24772,7 +24772,7 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
@@ -24804,7 +24804,7 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
@@ -24836,7 +24836,7 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
@@ -24868,7 +24868,7 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
@@ -24900,7 +24900,7 @@
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
@@ -24932,7 +24932,7 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
@@ -24964,7 +24964,7 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
@@ -24996,7 +24996,7 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
@@ -25028,7 +25028,7 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
@@ -25060,7 +25060,7 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
@@ -25092,7 +25092,7 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
@@ -25124,7 +25124,7 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
@@ -25156,7 +25156,7 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>F003</t>
+          <t>F_ALCOHOL_1</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
@@ -25188,7 +25188,7 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>F003</t>
+          <t>F_ALCOHOL_1</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
@@ -25220,7 +25220,7 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>F014</t>
+          <t>F_ALCOHOL_SP3</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
@@ -25252,7 +25252,7 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>F014</t>
+          <t>F_ALCOHOL_SP3</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>F017</t>
+          <t>F_DIOL_1_2</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
@@ -25316,7 +25316,7 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
@@ -25348,7 +25348,7 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
@@ -25380,7 +25380,7 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
@@ -25412,7 +25412,7 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
@@ -25444,7 +25444,7 @@
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>F035</t>
+          <t>F_ARYL_METHYL</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
@@ -25476,7 +25476,7 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>F038</t>
+          <t>F_ALKYL_ARENE</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
@@ -25508,7 +25508,7 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>F048</t>
+          <t>F_ARENESULFONIC_ACID</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
@@ -25540,7 +25540,7 @@
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>F024</t>
+          <t>F_ETHER_DIALKYL</t>
         </is>
       </c>
       <c r="D249" s="3" t="inlineStr">
@@ -25572,7 +25572,7 @@
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>F024</t>
+          <t>F_ETHER_DIALKYL</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
@@ -25604,7 +25604,7 @@
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>F039</t>
+          <t>F_ACETAL_KETAL</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
@@ -25636,7 +25636,7 @@
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr">
@@ -25668,7 +25668,7 @@
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
@@ -25700,7 +25700,7 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
@@ -25764,7 +25764,7 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
@@ -25796,7 +25796,7 @@
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>F018</t>
+          <t>F_ALDEHYDE</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
@@ -25828,7 +25828,7 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
@@ -25860,7 +25860,7 @@
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
@@ -25892,7 +25892,7 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
@@ -25924,7 +25924,7 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
@@ -25956,7 +25956,7 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
@@ -25988,7 +25988,7 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
@@ -26020,7 +26020,7 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
@@ -26052,7 +26052,7 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
@@ -26084,7 +26084,7 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
@@ -26116,7 +26116,7 @@
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
@@ -26148,7 +26148,7 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>F031</t>
+          <t>F_IMINE</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
@@ -26180,7 +26180,7 @@
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>F002</t>
+          <t>F_AMINE_1</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
@@ -26212,7 +26212,7 @@
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>F022</t>
+          <t>F_NITRILE</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
@@ -26244,7 +26244,7 @@
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>F034</t>
+          <t>F_AMINE_2</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
@@ -26276,7 +26276,7 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>F060</t>
+          <t>F_HYDROXIDE_ALKOXIDE</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
@@ -26308,7 +26308,7 @@
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>F005</t>
+          <t>F_ALKENE</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
@@ -26340,7 +26340,7 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
@@ -26372,7 +26372,7 @@
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
@@ -26436,7 +26436,7 @@
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
@@ -26468,7 +26468,7 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
@@ -26500,7 +26500,7 @@
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>F019</t>
+          <t>F_KETONE</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
@@ -26532,7 +26532,7 @@
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>F040</t>
+          <t>F_ENONE</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
@@ -26564,7 +26564,7 @@
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>F101</t>
+          <t>F_ENOLISABLE_CH</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
@@ -26596,7 +26596,7 @@
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>F004</t>
+          <t>F_ESTER</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
@@ -26628,7 +26628,7 @@
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>F101</t>
+          <t>F_ENOLISABLE_CH</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr">
@@ -26660,7 +26660,7 @@
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>F004</t>
+          <t>F_ESTER</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
@@ -26692,7 +26692,7 @@
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D285" s="3" t="inlineStr">
@@ -26724,7 +26724,7 @@
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
@@ -26756,7 +26756,7 @@
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D287" s="3" t="inlineStr">
@@ -26788,7 +26788,7 @@
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D289" s="3" t="inlineStr">
@@ -26852,7 +26852,7 @@
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
@@ -26884,7 +26884,7 @@
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D291" s="3" t="inlineStr">
@@ -26916,7 +26916,7 @@
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
@@ -26948,7 +26948,7 @@
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D293" s="3" t="inlineStr">
@@ -26980,7 +26980,7 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
@@ -27012,7 +27012,7 @@
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>F091</t>
+          <t>F_AZINE_N</t>
         </is>
       </c>
       <c r="D295" s="3" t="inlineStr">
@@ -27044,7 +27044,7 @@
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D296" s="3" t="inlineStr">
@@ -27076,7 +27076,7 @@
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D297" s="3" t="inlineStr">
@@ -27108,7 +27108,7 @@
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D299" s="3" t="inlineStr">
@@ -27172,7 +27172,7 @@
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D300" s="3" t="inlineStr">
@@ -27204,7 +27204,7 @@
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>F021</t>
+          <t>F_AMIDE</t>
         </is>
       </c>
       <c r="D301" s="3" t="inlineStr">
@@ -27236,7 +27236,7 @@
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>F095</t>
+          <t>F_AMIDE_NH</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr">
@@ -27268,7 +27268,7 @@
       </c>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t>F001</t>
+          <t>F_CARBOXYLIC_ACID</t>
         </is>
       </c>
       <c r="D303" s="3" t="inlineStr">
@@ -27300,7 +27300,7 @@
       </c>
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D304" s="3" t="inlineStr">
@@ -27332,7 +27332,7 @@
       </c>
       <c r="C305" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D305" s="3" t="inlineStr">
@@ -27364,7 +27364,7 @@
       </c>
       <c r="C306" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D306" s="3" t="inlineStr">
@@ -27396,7 +27396,7 @@
       </c>
       <c r="C307" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D307" s="3" t="inlineStr">
@@ -27428,7 +27428,7 @@
       </c>
       <c r="C308" s="3" t="inlineStr">
         <is>
-          <t>F028</t>
+          <t>F_PHENOL</t>
         </is>
       </c>
       <c r="D308" s="3" t="inlineStr">
@@ -27460,7 +27460,7 @@
       </c>
       <c r="C309" s="3" t="inlineStr">
         <is>
-          <t>F004</t>
+          <t>F_ESTER</t>
         </is>
       </c>
       <c r="D309" s="3" t="inlineStr">
@@ -27492,7 +27492,7 @@
       </c>
       <c r="C310" s="3" t="inlineStr">
         <is>
-          <t>F004</t>
+          <t>F_ESTER</t>
         </is>
       </c>
       <c r="D310" s="3" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="C311" s="3" t="inlineStr">
         <is>
-          <t>F041</t>
+          <t>F_ANHYDRIDE</t>
         </is>
       </c>
       <c r="D311" s="3" t="inlineStr">
@@ -27556,7 +27556,7 @@
       </c>
       <c r="C312" s="3" t="inlineStr">
         <is>
-          <t>F101</t>
+          <t>F_ENOLISABLE_CH</t>
         </is>
       </c>
       <c r="D312" s="3" t="inlineStr">
@@ -27588,7 +27588,7 @@
       </c>
       <c r="C313" s="3" t="inlineStr">
         <is>
-          <t>F101</t>
+          <t>F_ENOLISABLE_CH</t>
         </is>
       </c>
       <c r="D313" s="3" t="inlineStr">
@@ -27620,7 +27620,7 @@
       </c>
       <c r="C314" s="3" t="inlineStr">
         <is>
-          <t>F001</t>
+          <t>F_CARBOXYLIC_ACID</t>
         </is>
       </c>
       <c r="D314" s="3" t="inlineStr">
@@ -27652,7 +27652,7 @@
       </c>
       <c r="C315" s="3" t="inlineStr">
         <is>
-          <t>F004</t>
+          <t>F_ESTER</t>
         </is>
       </c>
       <c r="D315" s="3" t="inlineStr">
@@ -27684,7 +27684,7 @@
       </c>
       <c r="C316" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D316" s="3" t="inlineStr">
@@ -27716,7 +27716,7 @@
       </c>
       <c r="C317" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D317" s="3" t="inlineStr">
@@ -27748,7 +27748,7 @@
       </c>
       <c r="C318" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D318" s="3" t="inlineStr">
@@ -27780,7 +27780,7 @@
       </c>
       <c r="C319" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D319" s="3" t="inlineStr">
@@ -27812,7 +27812,7 @@
       </c>
       <c r="C320" s="3" t="inlineStr">
         <is>
-          <t>F101</t>
+          <t>F_ENOLISABLE_CH</t>
         </is>
       </c>
       <c r="D320" s="3" t="inlineStr">
@@ -27844,7 +27844,7 @@
       </c>
       <c r="C321" s="3" t="inlineStr">
         <is>
-          <t>F005</t>
+          <t>F_ALKENE</t>
         </is>
       </c>
       <c r="D321" s="3" t="inlineStr">
@@ -27876,7 +27876,7 @@
       </c>
       <c r="C322" s="3" t="inlineStr">
         <is>
-          <t>F005</t>
+          <t>F_ALKENE</t>
         </is>
       </c>
       <c r="D322" s="3" t="inlineStr">
@@ -27908,7 +27908,7 @@
       </c>
       <c r="C323" s="3" t="inlineStr">
         <is>
-          <t>F006</t>
+          <t>F_ALKENE_TERMINAL</t>
         </is>
       </c>
       <c r="D323" s="3" t="inlineStr">
@@ -27940,7 +27940,7 @@
       </c>
       <c r="C324" s="3" t="inlineStr">
         <is>
-          <t>F006</t>
+          <t>F_ALKENE_TERMINAL</t>
         </is>
       </c>
       <c r="D324" s="3" t="inlineStr">
@@ -27972,7 +27972,7 @@
       </c>
       <c r="C325" s="3" t="inlineStr">
         <is>
-          <t>F030</t>
+          <t>F_CONJUGATED_DIENE</t>
         </is>
       </c>
       <c r="D325" s="3" t="inlineStr">
@@ -28004,7 +28004,7 @@
       </c>
       <c r="C326" s="3" t="inlineStr">
         <is>
-          <t>F004</t>
+          <t>F_ESTER</t>
         </is>
       </c>
       <c r="D326" s="3" t="inlineStr">
@@ -28036,7 +28036,7 @@
       </c>
       <c r="C327" s="3" t="inlineStr">
         <is>
-          <t>F004</t>
+          <t>F_ESTER</t>
         </is>
       </c>
       <c r="D327" s="3" t="inlineStr">
@@ -28068,7 +28068,7 @@
       </c>
       <c r="C328" s="3" t="inlineStr">
         <is>
-          <t>F005</t>
+          <t>F_ALKENE</t>
         </is>
       </c>
       <c r="D328" s="3" t="inlineStr">
@@ -28100,7 +28100,7 @@
       </c>
       <c r="C329" s="3" t="inlineStr">
         <is>
-          <t>F041</t>
+          <t>F_ANHYDRIDE</t>
         </is>
       </c>
       <c r="D329" s="3" t="inlineStr">
@@ -28132,7 +28132,7 @@
       </c>
       <c r="C330" s="3" t="inlineStr">
         <is>
-          <t>F004</t>
+          <t>F_ESTER</t>
         </is>
       </c>
       <c r="D330" s="3" t="inlineStr">
@@ -28164,7 +28164,7 @@
       </c>
       <c r="C331" s="3" t="inlineStr">
         <is>
-          <t>F004</t>
+          <t>F_ESTER</t>
         </is>
       </c>
       <c r="D331" s="3" t="inlineStr">
@@ -28196,7 +28196,7 @@
       </c>
       <c r="C332" s="3" t="inlineStr">
         <is>
-          <t>F005</t>
+          <t>F_ALKENE</t>
         </is>
       </c>
       <c r="D332" s="3" t="inlineStr">
@@ -28228,7 +28228,7 @@
       </c>
       <c r="C333" s="3" t="inlineStr">
         <is>
-          <t>F037</t>
+          <t>F_ALLYLIC_CH2</t>
         </is>
       </c>
       <c r="D333" s="3" t="inlineStr">
@@ -28260,7 +28260,7 @@
       </c>
       <c r="C334" s="3" t="inlineStr">
         <is>
-          <t>F037</t>
+          <t>F_ALLYLIC_CH2</t>
         </is>
       </c>
       <c r="D334" s="3" t="inlineStr">
@@ -28292,7 +28292,7 @@
       </c>
       <c r="C335" s="3" t="inlineStr">
         <is>
-          <t>F041</t>
+          <t>F_ANHYDRIDE</t>
         </is>
       </c>
       <c r="D335" s="3" t="inlineStr">
@@ -28324,7 +28324,7 @@
       </c>
       <c r="C336" s="3" t="inlineStr">
         <is>
-          <t>F101</t>
+          <t>F_ENOLISABLE_CH</t>
         </is>
       </c>
       <c r="D336" s="3" t="inlineStr">
@@ -28356,7 +28356,7 @@
       </c>
       <c r="C337" s="3" t="inlineStr">
         <is>
-          <t>F101</t>
+          <t>F_ENOLISABLE_CH</t>
         </is>
       </c>
       <c r="D337" s="3" t="inlineStr">
@@ -28388,7 +28388,7 @@
       </c>
       <c r="C338" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D338" s="3" t="inlineStr">
@@ -28420,7 +28420,7 @@
       </c>
       <c r="C339" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D339" s="3" t="inlineStr">
@@ -28452,7 +28452,7 @@
       </c>
       <c r="C340" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D340" s="3" t="inlineStr">
@@ -28484,7 +28484,7 @@
       </c>
       <c r="C341" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D341" s="3" t="inlineStr">
@@ -28516,7 +28516,7 @@
       </c>
       <c r="C342" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D342" s="3" t="inlineStr">
@@ -28548,7 +28548,7 @@
       </c>
       <c r="C343" s="3" t="inlineStr">
         <is>
-          <t>F014</t>
+          <t>F_ALCOHOL_SP3</t>
         </is>
       </c>
       <c r="D343" s="3" t="inlineStr">
@@ -28580,7 +28580,7 @@
       </c>
       <c r="C344" s="3" t="inlineStr">
         <is>
-          <t>F016</t>
+          <t>F_ALCOHOL_3</t>
         </is>
       </c>
       <c r="D344" s="3" t="inlineStr">
@@ -28612,7 +28612,7 @@
       </c>
       <c r="C345" s="3" t="inlineStr">
         <is>
-          <t>F038</t>
+          <t>F_ALKYL_ARENE</t>
         </is>
       </c>
       <c r="D345" s="3" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="C346" s="3" t="inlineStr">
         <is>
-          <t>F012</t>
+          <t>F_ALKYL_IODIDE</t>
         </is>
       </c>
       <c r="D346" s="3" t="inlineStr">
@@ -28676,7 +28676,7 @@
       </c>
       <c r="C347" s="3" t="inlineStr">
         <is>
-          <t>F045</t>
+          <t>F_ALKYL_HALIDE_2</t>
         </is>
       </c>
       <c r="D347" s="3" t="inlineStr">
@@ -28708,7 +28708,7 @@
       </c>
       <c r="C348" s="3" t="inlineStr">
         <is>
-          <t>F011</t>
+          <t>F_ALKYL_CHLORIDE</t>
         </is>
       </c>
       <c r="D348" s="3" t="inlineStr">
@@ -28740,7 +28740,7 @@
       </c>
       <c r="C349" s="3" t="inlineStr">
         <is>
-          <t>F011</t>
+          <t>F_ALKYL_CHLORIDE</t>
         </is>
       </c>
       <c r="D349" s="3" t="inlineStr">
@@ -28772,7 +28772,7 @@
       </c>
       <c r="C350" s="3" t="inlineStr">
         <is>
-          <t>F045</t>
+          <t>F_ALKYL_HALIDE_2</t>
         </is>
       </c>
       <c r="D350" s="3" t="inlineStr">
@@ -28804,7 +28804,7 @@
       </c>
       <c r="C351" s="3" t="inlineStr">
         <is>
-          <t>F045</t>
+          <t>F_ALKYL_HALIDE_2</t>
         </is>
       </c>
       <c r="D351" s="3" t="inlineStr">
@@ -28836,7 +28836,7 @@
       </c>
       <c r="C352" s="3" t="inlineStr">
         <is>
-          <t>F010</t>
+          <t>F_ALKYL_BROMIDE</t>
         </is>
       </c>
       <c r="D352" s="3" t="inlineStr">
@@ -28868,7 +28868,7 @@
       </c>
       <c r="C353" s="3" t="inlineStr">
         <is>
-          <t>F010</t>
+          <t>F_ALKYL_BROMIDE</t>
         </is>
       </c>
       <c r="D353" s="3" t="inlineStr">
@@ -28900,7 +28900,7 @@
       </c>
       <c r="C354" s="3" t="inlineStr">
         <is>
-          <t>F010</t>
+          <t>F_ALKYL_BROMIDE</t>
         </is>
       </c>
       <c r="D354" s="3" t="inlineStr">
@@ -28932,7 +28932,7 @@
       </c>
       <c r="C355" s="3" t="inlineStr">
         <is>
-          <t>F010</t>
+          <t>F_ALKYL_BROMIDE</t>
         </is>
       </c>
       <c r="D355" s="3" t="inlineStr">
@@ -28964,7 +28964,7 @@
       </c>
       <c r="C356" s="3" t="inlineStr">
         <is>
-          <t>F032</t>
+          <t>F_VICINAL_DIBROMIDE</t>
         </is>
       </c>
       <c r="D356" s="3" t="inlineStr">
@@ -28996,7 +28996,7 @@
       </c>
       <c r="C357" s="3" t="inlineStr">
         <is>
-          <t>F032</t>
+          <t>F_VICINAL_DIBROMIDE</t>
         </is>
       </c>
       <c r="D357" s="3" t="inlineStr">
@@ -29028,7 +29028,7 @@
       </c>
       <c r="C358" s="3" t="inlineStr">
         <is>
-          <t>F032</t>
+          <t>F_VICINAL_DIBROMIDE</t>
         </is>
       </c>
       <c r="D358" s="3" t="inlineStr">
@@ -29060,7 +29060,7 @@
       </c>
       <c r="C359" s="3" t="inlineStr">
         <is>
-          <t>F032</t>
+          <t>F_VICINAL_DIBROMIDE</t>
         </is>
       </c>
       <c r="D359" s="3" t="inlineStr">
@@ -29092,7 +29092,7 @@
       </c>
       <c r="C360" s="3" t="inlineStr">
         <is>
-          <t>F010</t>
+          <t>F_ALKYL_BROMIDE</t>
         </is>
       </c>
       <c r="D360" s="3" t="inlineStr">
@@ -29124,7 +29124,7 @@
       </c>
       <c r="C361" s="3" t="inlineStr">
         <is>
-          <t>F010</t>
+          <t>F_ALKYL_BROMIDE</t>
         </is>
       </c>
       <c r="D361" s="3" t="inlineStr">
@@ -29156,7 +29156,7 @@
       </c>
       <c r="C362" s="3" t="inlineStr">
         <is>
-          <t>F007</t>
+          <t>F_ALKYNE</t>
         </is>
       </c>
       <c r="D362" s="3" t="inlineStr">
@@ -29188,7 +29188,7 @@
       </c>
       <c r="C363" s="3" t="inlineStr">
         <is>
-          <t>F008</t>
+          <t>F_ALKYNE_TERMINAL</t>
         </is>
       </c>
       <c r="D363" s="3" t="inlineStr">
@@ -29220,7 +29220,7 @@
       </c>
       <c r="C364" s="3" t="inlineStr">
         <is>
-          <t>F018</t>
+          <t>F_ALDEHYDE</t>
         </is>
       </c>
       <c r="D364" s="3" t="inlineStr">
@@ -29252,7 +29252,7 @@
       </c>
       <c r="C365" s="3" t="inlineStr">
         <is>
-          <t>F101</t>
+          <t>F_ENOLISABLE_CH</t>
         </is>
       </c>
       <c r="D365" s="3" t="inlineStr">
@@ -29284,7 +29284,7 @@
       </c>
       <c r="C366" s="3" t="inlineStr">
         <is>
-          <t>F012</t>
+          <t>F_ALKYL_IODIDE</t>
         </is>
       </c>
       <c r="D366" s="3" t="inlineStr">
@@ -29316,7 +29316,7 @@
       </c>
       <c r="C367" s="3" t="inlineStr">
         <is>
-          <t>F012</t>
+          <t>F_ALKYL_IODIDE</t>
         </is>
       </c>
       <c r="D367" s="3" t="inlineStr">
@@ -29348,7 +29348,7 @@
       </c>
       <c r="C368" s="3" t="inlineStr">
         <is>
-          <t>F010</t>
+          <t>F_ALKYL_BROMIDE</t>
         </is>
       </c>
       <c r="D368" s="3" t="inlineStr">
@@ -29380,7 +29380,7 @@
       </c>
       <c r="C369" s="3" t="inlineStr">
         <is>
-          <t>F045</t>
+          <t>F_ALKYL_HALIDE_2</t>
         </is>
       </c>
       <c r="D369" s="3" t="inlineStr">
@@ -29412,7 +29412,7 @@
       </c>
       <c r="C370" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D370" s="3" t="inlineStr">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="C371" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D371" s="3" t="inlineStr">
@@ -29476,7 +29476,7 @@
       </c>
       <c r="C372" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D372" s="3" t="inlineStr">
@@ -29508,7 +29508,7 @@
       </c>
       <c r="C373" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D373" s="3" t="inlineStr">
@@ -29540,7 +29540,7 @@
       </c>
       <c r="C374" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D374" s="3" t="inlineStr">
@@ -29572,7 +29572,7 @@
       </c>
       <c r="C375" s="3" t="inlineStr">
         <is>
-          <t>F047</t>
+          <t>F_ARYL_CHLORIDE</t>
         </is>
       </c>
       <c r="D375" s="3" t="inlineStr">
@@ -29604,7 +29604,7 @@
       </c>
       <c r="C376" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D376" s="3" t="inlineStr">
@@ -29636,7 +29636,7 @@
       </c>
       <c r="C377" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D377" s="3" t="inlineStr">
@@ -29668,7 +29668,7 @@
       </c>
       <c r="C378" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D378" s="3" t="inlineStr">
@@ -29700,7 +29700,7 @@
       </c>
       <c r="C379" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D379" s="3" t="inlineStr">
@@ -29732,7 +29732,7 @@
       </c>
       <c r="C380" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D380" s="3" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="C381" s="3" t="inlineStr">
         <is>
-          <t>F048</t>
+          <t>F_ARENESULFONIC_ACID</t>
         </is>
       </c>
       <c r="D381" s="3" t="inlineStr">
@@ -29796,7 +29796,7 @@
       </c>
       <c r="C382" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D382" s="3" t="inlineStr">
@@ -29828,7 +29828,7 @@
       </c>
       <c r="C383" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D383" s="3" t="inlineStr">
@@ -29860,7 +29860,7 @@
       </c>
       <c r="C384" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D384" s="3" t="inlineStr">
@@ -29892,7 +29892,7 @@
       </c>
       <c r="C385" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D385" s="3" t="inlineStr">
@@ -29924,7 +29924,7 @@
       </c>
       <c r="C386" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D386" s="3" t="inlineStr">
@@ -29956,7 +29956,7 @@
       </c>
       <c r="C387" s="3" t="inlineStr">
         <is>
-          <t>F038</t>
+          <t>F_ALKYL_ARENE</t>
         </is>
       </c>
       <c r="D387" s="3" t="inlineStr">
@@ -29988,7 +29988,7 @@
       </c>
       <c r="C388" s="3" t="inlineStr">
         <is>
-          <t>F060</t>
+          <t>F_HYDROXIDE_ALKOXIDE</t>
         </is>
       </c>
       <c r="D388" s="3" t="inlineStr">
@@ -30020,7 +30020,7 @@
       </c>
       <c r="C389" s="3" t="inlineStr">
         <is>
-          <t>F096</t>
+          <t>F_HYDRAZINE</t>
         </is>
       </c>
       <c r="D389" s="3" t="inlineStr">
@@ -30052,7 +30052,7 @@
       </c>
       <c r="C390" s="3" t="inlineStr">
         <is>
-          <t>F005</t>
+          <t>F_ALKENE</t>
         </is>
       </c>
       <c r="D390" s="3" t="inlineStr">
@@ -30084,7 +30084,7 @@
       </c>
       <c r="C391" s="3" t="inlineStr">
         <is>
-          <t>F005</t>
+          <t>F_ALKENE</t>
         </is>
       </c>
       <c r="D391" s="3" t="inlineStr">
@@ -30116,7 +30116,7 @@
       </c>
       <c r="C392" s="3" t="inlineStr">
         <is>
-          <t>F037</t>
+          <t>F_ALLYLIC_CH2</t>
         </is>
       </c>
       <c r="D392" s="3" t="inlineStr">
@@ -30148,7 +30148,7 @@
       </c>
       <c r="C393" s="3" t="inlineStr">
         <is>
-          <t>F037</t>
+          <t>F_ALLYLIC_CH2</t>
         </is>
       </c>
       <c r="D393" s="3" t="inlineStr">
@@ -30180,7 +30180,7 @@
       </c>
       <c r="C394" s="3" t="inlineStr">
         <is>
-          <t>F037</t>
+          <t>F_ALLYLIC_CH2</t>
         </is>
       </c>
       <c r="D394" s="3" t="inlineStr">
@@ -30212,7 +30212,7 @@
       </c>
       <c r="C395" s="3" t="inlineStr">
         <is>
-          <t>F037</t>
+          <t>F_ALLYLIC_CH2</t>
         </is>
       </c>
       <c r="D395" s="3" t="inlineStr">
@@ -30244,7 +30244,7 @@
       </c>
       <c r="C396" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D396" s="3" t="inlineStr">
@@ -30276,7 +30276,7 @@
       </c>
       <c r="C397" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D397" s="3" t="inlineStr">
@@ -30308,7 +30308,7 @@
       </c>
       <c r="C398" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D398" s="3" t="inlineStr">
@@ -30340,7 +30340,7 @@
       </c>
       <c r="C399" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D399" s="3" t="inlineStr">
@@ -30372,7 +30372,7 @@
       </c>
       <c r="C400" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D400" s="3" t="inlineStr">
@@ -30404,7 +30404,7 @@
       </c>
       <c r="C401" s="3" t="inlineStr">
         <is>
-          <t>F028</t>
+          <t>F_PHENOL</t>
         </is>
       </c>
       <c r="D401" s="3" t="inlineStr">
@@ -30436,7 +30436,7 @@
       </c>
       <c r="C402" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D402" s="3" t="inlineStr">
@@ -30468,7 +30468,7 @@
       </c>
       <c r="C403" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D403" s="3" t="inlineStr">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C404" s="3" t="inlineStr">
         <is>
-          <t>F013</t>
+          <t>F_ARYL_BROMIDE</t>
         </is>
       </c>
       <c r="D404" s="3" t="inlineStr">
@@ -30532,7 +30532,7 @@
       </c>
       <c r="C405" s="3" t="inlineStr">
         <is>
-          <t>F013</t>
+          <t>F_ARYL_BROMIDE</t>
         </is>
       </c>
       <c r="D405" s="3" t="inlineStr">
@@ -30564,7 +30564,7 @@
       </c>
       <c r="C406" s="3" t="inlineStr">
         <is>
-          <t>F013</t>
+          <t>F_ARYL_BROMIDE</t>
         </is>
       </c>
       <c r="D406" s="3" t="inlineStr">
@@ -30596,7 +30596,7 @@
       </c>
       <c r="C407" s="3" t="inlineStr">
         <is>
-          <t>F028</t>
+          <t>F_PHENOL</t>
         </is>
       </c>
       <c r="D407" s="3" t="inlineStr">
@@ -30628,7 +30628,7 @@
       </c>
       <c r="C408" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D408" s="3" t="inlineStr">
@@ -30660,7 +30660,7 @@
       </c>
       <c r="C409" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D409" s="3" t="inlineStr">
@@ -30692,7 +30692,7 @@
       </c>
       <c r="C410" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D410" s="3" t="inlineStr">
@@ -30724,7 +30724,7 @@
       </c>
       <c r="C411" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D411" s="3" t="inlineStr">
@@ -30756,7 +30756,7 @@
       </c>
       <c r="C412" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D412" s="3" t="inlineStr">
@@ -30788,7 +30788,7 @@
       </c>
       <c r="C413" s="3" t="inlineStr">
         <is>
-          <t>F021</t>
+          <t>F_AMIDE</t>
         </is>
       </c>
       <c r="D413" s="3" t="inlineStr">
@@ -30820,7 +30820,7 @@
       </c>
       <c r="C414" s="3" t="inlineStr">
         <is>
-          <t>F095</t>
+          <t>F_AMIDE_NH</t>
         </is>
       </c>
       <c r="D414" s="3" t="inlineStr">
@@ -30852,7 +30852,7 @@
       </c>
       <c r="C415" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D415" s="3" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="C416" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D416" s="3" t="inlineStr">
@@ -30916,7 +30916,7 @@
       </c>
       <c r="C417" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D417" s="3" t="inlineStr">
@@ -30948,7 +30948,7 @@
       </c>
       <c r="C418" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D418" s="3" t="inlineStr">
@@ -30980,7 +30980,7 @@
       </c>
       <c r="C419" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D419" s="3" t="inlineStr">
@@ -31012,7 +31012,7 @@
       </c>
       <c r="C420" s="3" t="inlineStr">
         <is>
-          <t>F022</t>
+          <t>F_NITRILE</t>
         </is>
       </c>
       <c r="D420" s="3" t="inlineStr">
@@ -31044,7 +31044,7 @@
       </c>
       <c r="C421" s="3" t="inlineStr">
         <is>
-          <t>F002</t>
+          <t>F_AMINE_1</t>
         </is>
       </c>
       <c r="D421" s="3" t="inlineStr">
@@ -31076,7 +31076,7 @@
       </c>
       <c r="C422" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D422" s="3" t="inlineStr">
@@ -31108,7 +31108,7 @@
       </c>
       <c r="C423" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D423" s="3" t="inlineStr">
@@ -31140,7 +31140,7 @@
       </c>
       <c r="C424" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D424" s="3" t="inlineStr">
@@ -31172,7 +31172,7 @@
       </c>
       <c r="C425" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D425" s="3" t="inlineStr">
@@ -31204,7 +31204,7 @@
       </c>
       <c r="C426" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D426" s="3" t="inlineStr">
@@ -31236,7 +31236,7 @@
       </c>
       <c r="C427" s="3" t="inlineStr">
         <is>
-          <t>F038</t>
+          <t>F_ALKYL_ARENE</t>
         </is>
       </c>
       <c r="D427" s="3" t="inlineStr">
@@ -31268,7 +31268,7 @@
       </c>
       <c r="C428" s="3" t="inlineStr">
         <is>
-          <t>F021</t>
+          <t>F_AMIDE</t>
         </is>
       </c>
       <c r="D428" s="3" t="inlineStr">
@@ -31300,7 +31300,7 @@
       </c>
       <c r="C429" s="3" t="inlineStr">
         <is>
-          <t>F093</t>
+          <t>F_AMINE_3</t>
         </is>
       </c>
       <c r="D429" s="3" t="inlineStr">
@@ -31332,7 +31332,7 @@
       </c>
       <c r="C430" s="3" t="inlineStr">
         <is>
-          <t>F023</t>
+          <t>F_EPOXIDE</t>
         </is>
       </c>
       <c r="D430" s="3" t="inlineStr">
@@ -31364,7 +31364,7 @@
       </c>
       <c r="C431" s="3" t="inlineStr">
         <is>
-          <t>F003</t>
+          <t>F_ALCOHOL_1</t>
         </is>
       </c>
       <c r="D431" s="3" t="inlineStr">
@@ -31396,7 +31396,7 @@
       </c>
       <c r="C432" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D432" s="3" t="inlineStr">
@@ -31428,7 +31428,7 @@
       </c>
       <c r="C433" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D433" s="3" t="inlineStr">
@@ -31460,7 +31460,7 @@
       </c>
       <c r="C434" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D434" s="3" t="inlineStr">
@@ -31492,7 +31492,7 @@
       </c>
       <c r="C435" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D435" s="3" t="inlineStr">
@@ -31524,7 +31524,7 @@
       </c>
       <c r="C436" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D436" s="3" t="inlineStr">
@@ -31556,7 +31556,7 @@
       </c>
       <c r="C437" s="3" t="inlineStr">
         <is>
-          <t>F014</t>
+          <t>F_ALCOHOL_SP3</t>
         </is>
       </c>
       <c r="D437" s="3" t="inlineStr">
@@ -31588,7 +31588,7 @@
       </c>
       <c r="C438" s="3" t="inlineStr">
         <is>
-          <t>F038</t>
+          <t>F_ALKYL_ARENE</t>
         </is>
       </c>
       <c r="D438" s="3" t="inlineStr">
@@ -31620,7 +31620,7 @@
       </c>
       <c r="C439" s="3" t="inlineStr">
         <is>
-          <t>F014</t>
+          <t>F_ALCOHOL_SP3</t>
         </is>
       </c>
       <c r="D439" s="3" t="inlineStr">
@@ -31652,7 +31652,7 @@
       </c>
       <c r="C440" s="3" t="inlineStr">
         <is>
-          <t>F016</t>
+          <t>F_ALCOHOL_3</t>
         </is>
       </c>
       <c r="D440" s="3" t="inlineStr">
@@ -31684,7 +31684,7 @@
       </c>
       <c r="C441" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D441" s="3" t="inlineStr">
@@ -31716,7 +31716,7 @@
       </c>
       <c r="C442" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D442" s="3" t="inlineStr">
@@ -31748,7 +31748,7 @@
       </c>
       <c r="C443" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D443" s="3" t="inlineStr">
@@ -31780,7 +31780,7 @@
       </c>
       <c r="C444" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D444" s="3" t="inlineStr">
@@ -31812,7 +31812,7 @@
       </c>
       <c r="C445" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D445" s="3" t="inlineStr">
@@ -31844,7 +31844,7 @@
       </c>
       <c r="C446" s="3" t="inlineStr">
         <is>
-          <t>F019</t>
+          <t>F_KETONE</t>
         </is>
       </c>
       <c r="D446" s="3" t="inlineStr">
@@ -31876,7 +31876,7 @@
       </c>
       <c r="C447" s="3" t="inlineStr">
         <is>
-          <t>F038</t>
+          <t>F_ALKYL_ARENE</t>
         </is>
       </c>
       <c r="D447" s="3" t="inlineStr">
@@ -31908,7 +31908,7 @@
       </c>
       <c r="C448" s="3" t="inlineStr">
         <is>
-          <t>F101</t>
+          <t>F_ENOLISABLE_CH</t>
         </is>
       </c>
       <c r="D448" s="3" t="inlineStr">
@@ -31940,7 +31940,7 @@
       </c>
       <c r="C449" s="3" t="inlineStr">
         <is>
-          <t>F101</t>
+          <t>F_ENOLISABLE_CH</t>
         </is>
       </c>
       <c r="D449" s="3" t="inlineStr">
@@ -31972,7 +31972,7 @@
       </c>
       <c r="C450" s="3" t="inlineStr">
         <is>
-          <t>F004</t>
+          <t>F_ESTER</t>
         </is>
       </c>
       <c r="D450" s="3" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="C451" s="3" t="inlineStr">
         <is>
-          <t>F004</t>
+          <t>F_ESTER</t>
         </is>
       </c>
       <c r="D451" s="3" t="inlineStr">
@@ -32036,7 +32036,7 @@
       </c>
       <c r="C452" s="3" t="inlineStr">
         <is>
-          <t>F102</t>
+          <t>F_ACTIVE_METHYLENE</t>
         </is>
       </c>
       <c r="D452" s="3" t="inlineStr">
@@ -32068,7 +32068,7 @@
       </c>
       <c r="C453" s="3" t="inlineStr">
         <is>
-          <t>F005</t>
+          <t>F_ALKENE</t>
         </is>
       </c>
       <c r="D453" s="3" t="inlineStr">
@@ -32100,7 +32100,7 @@
       </c>
       <c r="C454" s="3" t="inlineStr">
         <is>
-          <t>F006</t>
+          <t>F_ALKENE_TERMINAL</t>
         </is>
       </c>
       <c r="D454" s="3" t="inlineStr">
@@ -32132,7 +32132,7 @@
       </c>
       <c r="C455" s="3" t="inlineStr">
         <is>
-          <t>F019</t>
+          <t>F_KETONE</t>
         </is>
       </c>
       <c r="D455" s="3" t="inlineStr">
@@ -32164,7 +32164,7 @@
       </c>
       <c r="C456" s="3" t="inlineStr">
         <is>
-          <t>F040</t>
+          <t>F_ENONE</t>
         </is>
       </c>
       <c r="D456" s="3" t="inlineStr">
@@ -32196,7 +32196,7 @@
       </c>
       <c r="C457" s="3" t="inlineStr">
         <is>
-          <t>F101</t>
+          <t>F_ENOLISABLE_CH</t>
         </is>
       </c>
       <c r="D457" s="3" t="inlineStr">
@@ -32228,7 +32228,7 @@
       </c>
       <c r="C458" s="3" t="inlineStr">
         <is>
-          <t>F004</t>
+          <t>F_ESTER</t>
         </is>
       </c>
       <c r="D458" s="3" t="inlineStr">
@@ -32260,7 +32260,7 @@
       </c>
       <c r="C459" s="3" t="inlineStr">
         <is>
-          <t>F004</t>
+          <t>F_ESTER</t>
         </is>
       </c>
       <c r="D459" s="3" t="inlineStr">
@@ -32292,7 +32292,7 @@
       </c>
       <c r="C460" s="3" t="inlineStr">
         <is>
-          <t>F019</t>
+          <t>F_KETONE</t>
         </is>
       </c>
       <c r="D460" s="3" t="inlineStr">
@@ -32324,7 +32324,7 @@
       </c>
       <c r="C461" s="3" t="inlineStr">
         <is>
-          <t>F101</t>
+          <t>F_ENOLISABLE_CH</t>
         </is>
       </c>
       <c r="D461" s="3" t="inlineStr">
@@ -32356,7 +32356,7 @@
       </c>
       <c r="C462" s="3" t="inlineStr">
         <is>
-          <t>F101</t>
+          <t>F_ENOLISABLE_CH</t>
         </is>
       </c>
       <c r="D462" s="3" t="inlineStr">
@@ -32388,7 +32388,7 @@
       </c>
       <c r="C463" s="3" t="inlineStr">
         <is>
-          <t>F004</t>
+          <t>F_ESTER</t>
         </is>
       </c>
       <c r="D463" s="3" t="inlineStr">
@@ -32420,7 +32420,7 @@
       </c>
       <c r="C464" s="3" t="inlineStr">
         <is>
-          <t>F019</t>
+          <t>F_KETONE</t>
         </is>
       </c>
       <c r="D464" s="3" t="inlineStr">
@@ -32452,7 +32452,7 @@
       </c>
       <c r="C465" s="3" t="inlineStr">
         <is>
-          <t>F101</t>
+          <t>F_ENOLISABLE_CH</t>
         </is>
       </c>
       <c r="D465" s="3" t="inlineStr">
@@ -32484,7 +32484,7 @@
       </c>
       <c r="C466" s="3" t="inlineStr">
         <is>
-          <t>F102</t>
+          <t>F_ACTIVE_METHYLENE</t>
         </is>
       </c>
       <c r="D466" s="3" t="inlineStr">
@@ -32516,7 +32516,7 @@
       </c>
       <c r="C467" s="3" t="inlineStr">
         <is>
-          <t>F060</t>
+          <t>F_HYDROXIDE_ALKOXIDE</t>
         </is>
       </c>
       <c r="D467" s="3" t="inlineStr">
@@ -32548,7 +32548,7 @@
       </c>
       <c r="C468" s="3" t="inlineStr">
         <is>
-          <t>F012</t>
+          <t>F_ALKYL_IODIDE</t>
         </is>
       </c>
       <c r="D468" s="3" t="inlineStr">
@@ -32580,7 +32580,7 @@
       </c>
       <c r="C469" s="3" t="inlineStr">
         <is>
-          <t>F012</t>
+          <t>F_ALKYL_IODIDE</t>
         </is>
       </c>
       <c r="D469" s="3" t="inlineStr">
@@ -32612,7 +32612,7 @@
       </c>
       <c r="C470" s="3" t="inlineStr">
         <is>
-          <t>F012</t>
+          <t>F_ALKYL_IODIDE</t>
         </is>
       </c>
       <c r="D470" s="3" t="inlineStr">
@@ -32644,7 +32644,7 @@
       </c>
       <c r="C471" s="3" t="inlineStr">
         <is>
-          <t>F010</t>
+          <t>F_ALKYL_BROMIDE</t>
         </is>
       </c>
       <c r="D471" s="3" t="inlineStr">
@@ -32676,7 +32676,7 @@
       </c>
       <c r="C472" s="3" t="inlineStr">
         <is>
-          <t>F019</t>
+          <t>F_KETONE</t>
         </is>
       </c>
       <c r="D472" s="3" t="inlineStr">
@@ -32708,7 +32708,7 @@
       </c>
       <c r="C473" s="3" t="inlineStr">
         <is>
-          <t>F045</t>
+          <t>F_ALKYL_HALIDE_2</t>
         </is>
       </c>
       <c r="D473" s="3" t="inlineStr">
@@ -32740,7 +32740,7 @@
       </c>
       <c r="C474" s="3" t="inlineStr">
         <is>
-          <t>F101</t>
+          <t>F_ENOLISABLE_CH</t>
         </is>
       </c>
       <c r="D474" s="3" t="inlineStr">
@@ -32772,7 +32772,7 @@
       </c>
       <c r="C475" s="3" t="inlineStr">
         <is>
-          <t>F001</t>
+          <t>F_CARBOXYLIC_ACID</t>
         </is>
       </c>
       <c r="D475" s="3" t="inlineStr">
@@ -32804,7 +32804,7 @@
       </c>
       <c r="C476" s="3" t="inlineStr">
         <is>
-          <t>F010</t>
+          <t>F_ALKYL_BROMIDE</t>
         </is>
       </c>
       <c r="D476" s="3" t="inlineStr">
@@ -32836,7 +32836,7 @@
       </c>
       <c r="C477" s="3" t="inlineStr">
         <is>
-          <t>F045</t>
+          <t>F_ALKYL_HALIDE_2</t>
         </is>
       </c>
       <c r="D477" s="3" t="inlineStr">
@@ -32868,7 +32868,7 @@
       </c>
       <c r="C478" s="3" t="inlineStr">
         <is>
-          <t>F060</t>
+          <t>F_HYDROXIDE_ALKOXIDE</t>
         </is>
       </c>
       <c r="D478" s="3" t="inlineStr">
@@ -32900,7 +32900,7 @@
       </c>
       <c r="C479" s="3" t="inlineStr">
         <is>
-          <t>F020</t>
+          <t>F_ACYL_CHLORIDE</t>
         </is>
       </c>
       <c r="D479" s="3" t="inlineStr">
@@ -32932,7 +32932,7 @@
       </c>
       <c r="C480" s="3" t="inlineStr">
         <is>
-          <t>F020</t>
+          <t>F_ACYL_CHLORIDE</t>
         </is>
       </c>
       <c r="D480" s="3" t="inlineStr">
@@ -32964,7 +32964,7 @@
       </c>
       <c r="C481" s="3" t="inlineStr">
         <is>
-          <t>F071</t>
+          <t>F_SULFONE_SULFOXIDE</t>
         </is>
       </c>
       <c r="D481" s="3" t="inlineStr">
@@ -32996,7 +32996,7 @@
       </c>
       <c r="C482" s="3" t="inlineStr">
         <is>
-          <t>F073</t>
+          <t>F_THIOETHER</t>
         </is>
       </c>
       <c r="D482" s="3" t="inlineStr">
@@ -33028,7 +33028,7 @@
       </c>
       <c r="C483" s="3" t="inlineStr">
         <is>
-          <t>F014</t>
+          <t>F_ALCOHOL_SP3</t>
         </is>
       </c>
       <c r="D483" s="3" t="inlineStr">
@@ -33060,7 +33060,7 @@
       </c>
       <c r="C484" s="3" t="inlineStr">
         <is>
-          <t>F014</t>
+          <t>F_ALCOHOL_SP3</t>
         </is>
       </c>
       <c r="D484" s="3" t="inlineStr">
@@ -33092,7 +33092,7 @@
       </c>
       <c r="C485" s="3" t="inlineStr">
         <is>
-          <t>F016</t>
+          <t>F_ALCOHOL_3</t>
         </is>
       </c>
       <c r="D485" s="3" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="C486" s="3" t="inlineStr">
         <is>
-          <t>F016</t>
+          <t>F_ALCOHOL_3</t>
         </is>
       </c>
       <c r="D486" s="3" t="inlineStr">
@@ -33156,7 +33156,7 @@
       </c>
       <c r="C487" s="3" t="inlineStr">
         <is>
-          <t>F017</t>
+          <t>F_DIOL_1_2</t>
         </is>
       </c>
       <c r="D487" s="3" t="inlineStr">
@@ -33188,7 +33188,7 @@
       </c>
       <c r="C488" s="3" t="inlineStr">
         <is>
-          <t>F019</t>
+          <t>F_KETONE</t>
         </is>
       </c>
       <c r="D488" s="3" t="inlineStr">
@@ -33220,7 +33220,7 @@
       </c>
       <c r="C489" s="3" t="inlineStr">
         <is>
-          <t>F101</t>
+          <t>F_ENOLISABLE_CH</t>
         </is>
       </c>
       <c r="D489" s="3" t="inlineStr">
@@ -33252,7 +33252,7 @@
       </c>
       <c r="C490" s="3" t="inlineStr">
         <is>
-          <t>F031</t>
+          <t>F_IMINE</t>
         </is>
       </c>
       <c r="D490" s="3" t="inlineStr">
@@ -33284,7 +33284,7 @@
       </c>
       <c r="C491" s="3" t="inlineStr">
         <is>
-          <t>F049</t>
+          <t>F_OXIME</t>
         </is>
       </c>
       <c r="D491" s="3" t="inlineStr">
@@ -33316,7 +33316,7 @@
       </c>
       <c r="C492" s="3" t="inlineStr">
         <is>
-          <t>F021</t>
+          <t>F_AMIDE</t>
         </is>
       </c>
       <c r="D492" s="3" t="inlineStr">
@@ -33348,7 +33348,7 @@
       </c>
       <c r="C493" s="3" t="inlineStr">
         <is>
-          <t>F095</t>
+          <t>F_AMIDE_NH</t>
         </is>
       </c>
       <c r="D493" s="3" t="inlineStr">
@@ -33380,7 +33380,7 @@
       </c>
       <c r="C494" s="3" t="inlineStr">
         <is>
-          <t>F097</t>
+          <t>F_HYDROXYLAMINE</t>
         </is>
       </c>
       <c r="D494" s="3" t="inlineStr">
@@ -33412,7 +33412,7 @@
       </c>
       <c r="C495" s="3" t="inlineStr">
         <is>
-          <t>F022</t>
+          <t>F_NITRILE</t>
         </is>
       </c>
       <c r="D495" s="3" t="inlineStr">
@@ -33444,7 +33444,7 @@
       </c>
       <c r="C496" s="3" t="inlineStr">
         <is>
-          <t>F014</t>
+          <t>F_ALCOHOL_SP3</t>
         </is>
       </c>
       <c r="D496" s="3" t="inlineStr">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="C497" s="3" t="inlineStr">
         <is>
-          <t>F016</t>
+          <t>F_ALCOHOL_3</t>
         </is>
       </c>
       <c r="D497" s="3" t="inlineStr">
@@ -33508,7 +33508,7 @@
       </c>
       <c r="C498" s="3" t="inlineStr">
         <is>
-          <t>F022</t>
+          <t>F_NITRILE</t>
         </is>
       </c>
       <c r="D498" s="3" t="inlineStr">
@@ -33540,7 +33540,7 @@
       </c>
       <c r="C499" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D499" s="3" t="inlineStr">
@@ -33572,7 +33572,7 @@
       </c>
       <c r="C500" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D500" s="3" t="inlineStr">
@@ -33604,7 +33604,7 @@
       </c>
       <c r="C501" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D501" s="3" t="inlineStr">
@@ -33636,7 +33636,7 @@
       </c>
       <c r="C502" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D502" s="3" t="inlineStr">
@@ -33668,7 +33668,7 @@
       </c>
       <c r="C503" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D503" s="3" t="inlineStr">
@@ -33700,7 +33700,7 @@
       </c>
       <c r="C504" s="3" t="inlineStr">
         <is>
-          <t>F021</t>
+          <t>F_AMIDE</t>
         </is>
       </c>
       <c r="D504" s="3" t="inlineStr">
@@ -33732,7 +33732,7 @@
       </c>
       <c r="C505" s="3" t="inlineStr">
         <is>
-          <t>F095</t>
+          <t>F_AMIDE_NH</t>
         </is>
       </c>
       <c r="D505" s="3" t="inlineStr">
@@ -33764,7 +33764,7 @@
       </c>
       <c r="C506" s="3" t="inlineStr">
         <is>
-          <t>F021</t>
+          <t>F_AMIDE</t>
         </is>
       </c>
       <c r="D506" s="3" t="inlineStr">
@@ -33796,7 +33796,7 @@
       </c>
       <c r="C507" s="3" t="inlineStr">
         <is>
-          <t>F021</t>
+          <t>F_AMIDE</t>
         </is>
       </c>
       <c r="D507" s="3" t="inlineStr">
@@ -33828,7 +33828,7 @@
       </c>
       <c r="C508" s="3" t="inlineStr">
         <is>
-          <t>F095</t>
+          <t>F_AMIDE_NH</t>
         </is>
       </c>
       <c r="D508" s="3" t="inlineStr">
@@ -33860,7 +33860,7 @@
       </c>
       <c r="C509" s="3" t="inlineStr">
         <is>
-          <t>F095</t>
+          <t>F_AMIDE_NH</t>
         </is>
       </c>
       <c r="D509" s="3" t="inlineStr">
@@ -33892,7 +33892,7 @@
       </c>
       <c r="C510" s="3" t="inlineStr">
         <is>
-          <t>F012</t>
+          <t>F_ALKYL_IODIDE</t>
         </is>
       </c>
       <c r="D510" s="3" t="inlineStr">
@@ -33924,7 +33924,7 @@
       </c>
       <c r="C511" s="3" t="inlineStr">
         <is>
-          <t>F043</t>
+          <t>F_METHYL_HALIDE</t>
         </is>
       </c>
       <c r="D511" s="3" t="inlineStr">
@@ -33956,7 +33956,7 @@
       </c>
       <c r="C512" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D512" s="3" t="inlineStr">
@@ -33988,7 +33988,7 @@
       </c>
       <c r="C513" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D513" s="3" t="inlineStr">
@@ -34020,7 +34020,7 @@
       </c>
       <c r="C514" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D514" s="3" t="inlineStr">
@@ -34052,7 +34052,7 @@
       </c>
       <c r="C515" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D515" s="3" t="inlineStr">
@@ -34084,7 +34084,7 @@
       </c>
       <c r="C516" s="3" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>F_ARENE_CH</t>
         </is>
       </c>
       <c r="D516" s="3" t="inlineStr">
@@ -34116,7 +34116,7 @@
       </c>
       <c r="C517" s="3" t="inlineStr">
         <is>
-          <t>F050</t>
+          <t>F_ARYL_ALKYL_ETHER</t>
         </is>
       </c>
       <c r="D517" s="3" t="inlineStr">
@@ -34148,7 +34148,7 @@
       </c>
       <c r="C518" s="3" t="inlineStr">
         <is>
-          <t>F023</t>
+          <t>F_EPOXIDE</t>
         </is>
       </c>
       <c r="D518" s="3" t="inlineStr">
@@ -34180,7 +34180,7 @@
       </c>
       <c r="C519" s="3" t="inlineStr">
         <is>
-          <t>F060</t>
+          <t>F_HYDROXIDE_ALKOXIDE</t>
         </is>
       </c>
       <c r="D519" s="3" t="inlineStr">
@@ -34212,7 +34212,7 @@
       </c>
       <c r="C520" s="3" t="inlineStr">
         <is>
-          <t>F014</t>
+          <t>F_ALCOHOL_SP3</t>
         </is>
       </c>
       <c r="D520" s="3" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="C521" s="3" t="inlineStr">
         <is>
-          <t>F015</t>
+          <t>F_ALCOHOL_2</t>
         </is>
       </c>
       <c r="D521" s="3" t="inlineStr">
@@ -34276,7 +34276,7 @@
       </c>
       <c r="C522" s="3" t="inlineStr">
         <is>
-          <t>F024</t>
+          <t>F_ETHER_DIALKYL</t>
         </is>
       </c>
       <c r="D522" s="3" t="inlineStr">
@@ -34308,7 +34308,7 @@
       </c>
       <c r="C523" s="3" t="inlineStr">
         <is>
-          <t>F063</t>
+          <t>F_PEROXIDE</t>
         </is>
       </c>
       <c r="D523" s="3" t="inlineStr">
@@ -34340,7 +34340,7 @@
       </c>
       <c r="C524" s="3" t="inlineStr">
         <is>
-          <t>F010</t>
+          <t>F_ALKYL_BROMIDE</t>
         </is>
       </c>
       <c r="D524" s="3" t="inlineStr">
@@ -34372,7 +34372,7 @@
       </c>
       <c r="C525" s="3" t="inlineStr">
         <is>
-          <t>F010</t>
+          <t>F_ALKYL_BROMIDE</t>
         </is>
       </c>
       <c r="D525" s="3" t="inlineStr">
@@ -34404,7 +34404,7 @@
       </c>
       <c r="C526" s="3" t="inlineStr">
         <is>
-          <t>F032</t>
+          <t>F_VICINAL_DIBROMIDE</t>
         </is>
       </c>
       <c r="D526" s="3" t="inlineStr">
@@ -34436,7 +34436,7 @@
       </c>
       <c r="C527" s="3" t="inlineStr">
         <is>
-          <t>F045</t>
+          <t>F_ALKYL_HALIDE_2</t>
         </is>
       </c>
       <c r="D527" s="3" t="inlineStr">
@@ -34468,7 +34468,7 @@
       </c>
       <c r="C528" s="3" t="inlineStr">
         <is>
-          <t>F045</t>
+          <t>F_ALKYL_HALIDE_2</t>
         </is>
       </c>
       <c r="D528" s="3" t="inlineStr">
@@ -34522,7 +34522,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Fragments: one row per fragment. The SMARTS column is the pattern that finds it; 'Reactive atom(s)' and 'Role' say where and how it reacts; pKa and leaving-group columns say how acidic, how basic, and what can leave. New IDs: F005, F006 …</t>
+          <t>Fragments: one row per fragment. The SMARTS column is the pattern that finds it; 'Reactive atom(s)' and 'Role' say where and how it reacts; pKa and leaving-group columns say how acidic, how basic, and what can leave. Fragment ID rule: every structurally distinct SMARTS pattern gets its own ID, and no two fragments share a pattern or an ID. An ID is F_ followed by a descriptive name in capitals, e.g. F_ALDEHYDE, F_ALKYL_HALIDE_2 (the old F001–F103 numbers are listed in tools/data/fragment_ids.json). tools/run_all_checks.py enforces this.</t>
         </is>
       </c>
     </row>

--- a/molecule_data.xlsx
+++ b/molecule_data.xlsx
@@ -11363,7 +11363,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>F_CARBOXYLIC_ACID</t>
+          <t>F_WH4T6PP5</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -11435,7 +11435,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>F_AMINE_1</t>
+          <t>F_7TP4VNHE</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -11507,7 +11507,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_1</t>
+          <t>F_7WIM5VKY</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -11579,7 +11579,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>F_ESTER</t>
+          <t>F_N4PYCJQX</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -11651,7 +11651,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>F_ALKENE</t>
+          <t>F_43XPC2LW</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -11711,7 +11711,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>F_ALKENE_TERMINAL</t>
+          <t>F_674FQ44T</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -11771,7 +11771,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYNE</t>
+          <t>F_YAW5EFKQ</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -11819,7 +11819,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYNE_TERMINAL</t>
+          <t>F_UNMQWRQR</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -11879,7 +11879,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -11939,7 +11939,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_BROMIDE</t>
+          <t>F_EDNDOOMT</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -11991,7 +11991,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_CHLORIDE</t>
+          <t>F_77XITLZ4</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -12043,7 +12043,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_IODIDE</t>
+          <t>F_OM2L6LN4</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -12095,7 +12095,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>F_ARYL_BROMIDE</t>
+          <t>F_H6H7YAKN</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -12143,7 +12143,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_SP3</t>
+          <t>F_CQJBM3VA</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -12211,7 +12211,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_2</t>
+          <t>F_JIOCZMVT</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -12275,7 +12275,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_3</t>
+          <t>F_Z6ABGO4G</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -12339,7 +12339,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>F_DIOL_1_2</t>
+          <t>F_VHRSWB64</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -12395,7 +12395,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>F_ALDEHYDE</t>
+          <t>F_ADOAMFFM</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -12459,7 +12459,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>F_KETONE</t>
+          <t>F_CFJ46WPI</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -12519,7 +12519,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>F_ACYL_CHLORIDE</t>
+          <t>F_7W5VQUT2</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -12575,7 +12575,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>F_AMIDE</t>
+          <t>F_F3X5X5PO</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -12643,7 +12643,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>F_NITRILE</t>
+          <t>F_OWKLY6DL</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -12703,7 +12703,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>F_EPOXIDE</t>
+          <t>F_GUG35WZM</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -12755,7 +12755,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>F_ETHER_DIALKYL</t>
+          <t>F_GWWY5MAP</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -12811,7 +12811,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>F_NITROARENE</t>
+          <t>F_5J6B3EOP</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -12855,7 +12855,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>F_ARYLAMINE</t>
+          <t>F_UY2ANYI2</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -12919,7 +12919,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>F_ARYL_DIAZONIUM</t>
+          <t>F_UUBBBRAY</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -12971,7 +12971,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>F_PHENOL</t>
+          <t>F_EBFEFTNC</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -13027,7 +13027,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>F_GRIGNARD</t>
+          <t>F_F6IICZMJ</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -13083,7 +13083,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>F_CONJUGATED_DIENE</t>
+          <t>F_DRXF7R5Y</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -13131,7 +13131,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>F_IMINE</t>
+          <t>F_LPMNZ3FU</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -13183,7 +13183,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>F_VICINAL_DIBROMIDE</t>
+          <t>F_D6B2Q4UF</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -13235,7 +13235,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>F_BROMOHYDRIN</t>
+          <t>F_FJ2AGXG4</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -13287,7 +13287,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>F_AMINE_2</t>
+          <t>F_AOQ6WODX</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -13347,7 +13347,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>F_ARYL_METHYL</t>
+          <t>F_W7EG4A5W</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -13407,7 +13407,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>F_BENZYLIC_BROMIDE</t>
+          <t>F_J2RF4BYK</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -13459,7 +13459,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>F_ALLYLIC_CH2</t>
+          <t>F_DHYVCP7A</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -13515,7 +13515,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_ARENE</t>
+          <t>F_W4GPHE3A</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -13559,7 +13559,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>F_ACETAL_KETAL</t>
+          <t>F_Z7L4L6RQ</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -13603,7 +13603,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>F_ENONE</t>
+          <t>F_QTJCKBIJ</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -13651,7 +13651,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>F_METHYL_HALIDE</t>
+          <t>F_KNBZHWVH</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -13707,7 +13707,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_HALIDE_1</t>
+          <t>F_OSWUXBJP</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -13763,7 +13763,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_HALIDE_2</t>
+          <t>F_4KF4VNAH</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -13819,7 +13819,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_HALIDE_3</t>
+          <t>F_YUNA7OOT</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -13875,7 +13875,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>F_ALUMINIUM_HYDRIDE</t>
+          <t>F_WYH6KVDM</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -13931,7 +13931,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>F_ANHYDRIDE</t>
+          <t>F_IOJJ46QM</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -13979,7 +13979,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>F_ARYL_CHLORIDE</t>
+          <t>F_YYVXALOV</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -14031,7 +14031,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>F_ARENESULFONIC_ACID</t>
+          <t>F_TH2DYID6</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -14087,7 +14087,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>F_OXIME</t>
+          <t>F_KKIIQEFP</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -14147,7 +14147,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>F_ARYL_ALKYL_ETHER</t>
+          <t>F_UHD3N3ZP</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -14215,7 +14215,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>F_IMIDATE</t>
+          <t>F_EERNJGZA</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -14283,7 +14283,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>F_SILYL_ETHER</t>
+          <t>F_J2K7DGKF</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -14351,7 +14351,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>F_C_SILYL</t>
+          <t>F_6OE4YDC3</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -14415,7 +14415,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>F_CHLOROSILANE</t>
+          <t>F_UCXTN7QM</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -14471,7 +14471,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>F_AZIDE</t>
+          <t>F_ELZWELDO</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -14539,7 +14539,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>F_NITROALKANE</t>
+          <t>F_E6XU5RMC</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -14600,14 +14600,14 @@
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>Reduction goes through the nitroso and hydroxylamine stages. Nitroarenes are F_NITROARENE [learned from the recorded reactions of templates T000270, T004730; RDKit: consumed (count drops from starting materials to product) in 8 of 8 example reactions of the templates it covers; found in 0.1% of 20,000 recorded products]</t>
+          <t>Reduction goes through the nitroso and hydroxylamine stages. Nitroarenes are F_5J6B3EOP [learned from the recorded reactions of templates T000270, T004730; RDKit: consumed (count drops from starting materials to product) in 8 of 8 example reactions of the templates it covers; found in 0.1% of 20,000 recorded products]</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>F_NITROSO</t>
+          <t>F_S7TAL57S</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -14671,7 +14671,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>F_CARBOXYLATE</t>
+          <t>F_3UVA2HDQ</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -14732,14 +14732,14 @@
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>Li/Na/K salts from saponification are recorded as carboxylates and are often carried forward directly. Resonance (two equal C–O bonds) makes the carbonyl very unreactive. The anionic form is missed by F_CARBOXYLIC_ACID (carboxylic acid). T002523 (salt → 1° alcohol with Na/MeOH) is a data oddity: Na/ROH (Bouveault–Blanc) reduces esters, not carboxylate salts, which do not react under these conditions. The recorded substrate was probably the ester [learned from the recorded reactions of templates T000180, T001902, T002404, T002523, T003623; RDKit: consumed (count drops from starting materials to product) in 20 of 20 example reactions of the templates it covers; found in 0.3% of 20,000 recorded products]</t>
+          <t>Li/Na/K salts from saponification are recorded as carboxylates and are often carried forward directly. Resonance (two equal C–O bonds) makes the carbonyl very unreactive. The anionic form is missed by F_WH4T6PP5 (carboxylic acid). T002523 (salt → 1° alcohol with Na/MeOH) is a data oddity: Na/ROH (Bouveault–Blanc) reduces esters, not carboxylate salts, which do not react under these conditions. The recorded substrate was probably the ester [learned from the recorded reactions of templates T000180, T001902, T002404, T002523, T003623; RDKit: consumed (count drops from starting materials to product) in 20 of 20 example reactions of the templates it covers; found in 0.3% of 20,000 recorded products]</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>F_SULFINATE_SULFONATE</t>
+          <t>F_NATCGA6A</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -14800,14 +14800,14 @@
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>Anionic forms are missed by F_ARENESULFONIC_ACID (arenesulfonic acid). Sulfinic acids are unstable and disproportionate, so sulfinates are stored as Na salts. Carboxylates are a separate fragment [learned from the recorded reactions of templates T004902, T005667, T005812; RDKit: consumed (count drops from starting materials to product) in 12 of 12 example reactions of the templates it covers; found in 0.0% of 20,000 recorded products]</t>
+          <t>Anionic forms are missed by F_TH2DYID6 (arenesulfonic acid). Sulfinic acids are unstable and disproportionate, so sulfinates are stored as Na salts. Carboxylates are a separate fragment [learned from the recorded reactions of templates T004902, T005667, T005812; RDKit: consumed (count drops from starting materials to product) in 12 of 12 example reactions of the templates it covers; found in 0.0% of 20,000 recorded products]</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>F_HYDROXIDE_ALKOXIDE</t>
+          <t>F_BLUS3XKO</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -14867,7 +14867,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>F_CYANIDE</t>
+          <t>F_NY7AYBRA</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -14931,7 +14931,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>F_CYANOGEN_HALIDE</t>
+          <t>F_VOBBL45A</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -14987,7 +14987,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>F_PEROXIDE</t>
+          <t>F_NBVC3ZK3</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -15047,7 +15047,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>F_SULFONYL_CHLORIDE</t>
+          <t>F_L6MZYAQB</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -15103,7 +15103,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>F_ARYL_ENOL_SULFONATE</t>
+          <t>F_L6VTMA27</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -15159,7 +15159,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_SULFONATE</t>
+          <t>F_Y7BIL7MW</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -15215,7 +15215,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>F_SULFONAMIDE_1</t>
+          <t>F_PURMGXG6</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -15279,7 +15279,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>F_SULFONAMIDE_2</t>
+          <t>F_3SKBXPIY</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -15347,7 +15347,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>F_BIS_SULFONYLAMINE</t>
+          <t>F_7YSU7T4D</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -15403,7 +15403,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>F_SULFINAMIDE</t>
+          <t>F_3Y23J4GX</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -15471,7 +15471,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>F_SULFONE_SULFOXIDE</t>
+          <t>F_66D4FM65</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -15539,7 +15539,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>F_THIOL</t>
+          <t>F_RTHLR62E</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -15607,7 +15607,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>F_THIOETHER</t>
+          <t>F_WUYH6XV3</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -15675,7 +15675,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>F_THIOESTER</t>
+          <t>F_NNHZ2V7J</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -15739,7 +15739,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>F_THIOACETATE_ANION</t>
+          <t>F_54IEU5KA</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -15803,7 +15803,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>F_THIOCARBONYL</t>
+          <t>F_GQ7G2E2T</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -15871,7 +15871,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>F_CARBAMATE</t>
+          <t>F_OE4EQYFD</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -15932,14 +15932,14 @@
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>Covers N-Boc azoles (T000457 and T000566, removed by TFA or HCl) and N-ethoxycarbonyl sulfoximines (T003015, removed by base). An N-Boc group also matches F_AMIDE (amide) and the tert-butyl fragment; this one marks the whole N–CO2R unit that is lost on deprotection. Its N–H, when present, is the amide/carbamate N–H fragment [learned from the recorded reactions of templates T000457, T000566, T003015; RDKit: consumed (count drops from starting materials to product) in 12 of 12 example reactions of the templates it covers; found in 10.2% of 20,000 recorded products]</t>
+          <t>Covers N-Boc azoles (T000457 and T000566, removed by TFA or HCl) and N-ethoxycarbonyl sulfoximines (T003015, removed by base). An N-Boc group also matches F_F3X5X5PO (amide) and the tert-butyl fragment; this one marks the whole N–CO2R unit that is lost on deprotection. Its N–H, when present, is the amide/carbamate N–H fragment [learned from the recorded reactions of templates T000457, T000566, T003015; RDKit: consumed (count drops from starting materials to product) in 12 of 12 example reactions of the templates it covers; found in 10.2% of 20,000 recorded products]</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>F_TERT_BUTYL_GROUP</t>
+          <t>F_EKZKEVUW</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -15996,14 +15996,14 @@
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>Cation scavengers (Et3SiH, anisole) protect electron-rich arenes. Trapping by solvent can give transesterified products (ethyl/isopropyl/methyl ester or carbamate; T001529 records t-Bu ester → methyl ester). Di-t-Bu phosphates (prodrugs) lose both t-Bu groups. On N, only t-Bu groups that leave easily in acid are matched (ring N of azoles, sulfonamide N–H, the N–H of a 2-aminoazine); ordinary t-Bu amines and amides (tBuNH2, tBuNHAc) and C-t-Bu groups are not. N-alkylation of Boc-NH (T007010) keeps the t-Bu and counts under amide/carbamate N–H. Overlaps the carbamate, carbonate and ester (F_ESTER) fragments, but this is the group consumed on acid deprotection [learned from the recorded reactions of templates T003260, T004791, T005289, T003156, T005573, T003741…; RDKit: consumed (count drops from starting materials to product) in 88 of 88 example reactions of the templates it covers; found in 8.8% of 20,000 recorded products]</t>
+          <t>Cation scavengers (Et3SiH, anisole) protect electron-rich arenes. Trapping by solvent can give transesterified products (ethyl/isopropyl/methyl ester or carbamate; T001529 records t-Bu ester → methyl ester). Di-t-Bu phosphates (prodrugs) lose both t-Bu groups. On N, only t-Bu groups that leave easily in acid are matched (ring N of azoles, sulfonamide N–H, the N–H of a 2-aminoazine); ordinary t-Bu amines and amides (tBuNH2, tBuNHAc) and C-t-Bu groups are not. N-alkylation of Boc-NH (T007010) keeps the t-Bu and counts under amide/carbamate N–H. Overlaps the carbamate, carbonate and ester (F_N4PYCJQX) fragments, but this is the group consumed on acid deprotection [learned from the recorded reactions of templates T003260, T004791, T005289, T003156, T005573, T003741…; RDKit: consumed (count drops from starting materials to product) in 88 of 88 example reactions of the templates it covers; found in 8.8% of 20,000 recorded products]</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>F_CARBONATE</t>
+          <t>F_BPZQSOZQ</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -16059,7 +16059,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>F_N_ACYL_AZOLE</t>
+          <t>F_R65BRROR</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -16123,7 +16123,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>F_BORONIC_ACID</t>
+          <t>F_ZQNACBZ5</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -16187,7 +16187,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>F_PINACOL_BORONATE</t>
+          <t>F_D6D2SHBS</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -16251,7 +16251,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>F_ORGANOSTANNANE</t>
+          <t>F_MZ5ZIRZW</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -16307,7 +16307,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>F_ARYL_IODIDE</t>
+          <t>F_EITZ3KQK</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -16363,7 +16363,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>F_ARYL_FLUORIDE_SNAR</t>
+          <t>F_JXENEJS4</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -16419,7 +16419,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>F_HALO_AZINE</t>
+          <t>F_IT7SFBHB</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -16483,7 +16483,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>F_VINYL_ALKYNYL_HALIDE</t>
+          <t>F_QRDE5U55</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -16539,7 +16539,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>F_IMIDOYL_CHLORIDE</t>
+          <t>F_SZF3ZRNG</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -16591,7 +16591,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>F_AZOLE_NH</t>
+          <t>F_CRK5A7KB</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -16659,7 +16659,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>F_PYRIDONE_NH</t>
+          <t>F_6UCNUCGB</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -16720,14 +16720,14 @@
       </c>
       <c r="N91" s="3" t="inlineStr">
         <is>
-          <t>Lactam ⇌ lactim (hydroxy-azine) tautomers: matched only in the lactam form c(=O)[nH], the usual way they are drawn; a structure drawn as the hydroxy-azine (Oc1ccccn1) is not matched and reads as a phenol (F_PHENOL). Deoxychlorination: POCl3 neat at reflux, often with DIPEA, PhNEt2 or DMF (Vilsmeier). Uracil-type rings carry two N–H, and usually only one reacts. N-substituted pyridones (no N–H) are not matched and cannot be chlorinated this way. 5-ring lactam N–H (benzimidazolone, tetrazolone) belongs to the azole N–H fragment; 2-thiopyridones/thiouracils to the thiol/thione fragment [learned from the recorded reactions of templates T000346, T000421, T000502, T000572, T000855, T000913…; RDKit: consumed (count drops from starting materials to product) in 130 of 148 example reactions of the templates it covers; found in 2.0% of 20,000 recorded products]</t>
+          <t>Lactam ⇌ lactim (hydroxy-azine) tautomers: matched only in the lactam form c(=O)[nH], the usual way they are drawn; a structure drawn as the hydroxy-azine (Oc1ccccn1) is not matched and reads as a phenol (F_EBFEFTNC). Deoxychlorination: POCl3 neat at reflux, often with DIPEA, PhNEt2 or DMF (Vilsmeier). Uracil-type rings carry two N–H, and usually only one reacts. N-substituted pyridones (no N–H) are not matched and cannot be chlorinated this way. 5-ring lactam N–H (benzimidazolone, tetrazolone) belongs to the azole N–H fragment; 2-thiopyridones/thiouracils to the thiol/thione fragment [learned from the recorded reactions of templates T000346, T000421, T000502, T000572, T000855, T000913…; RDKit: consumed (count drops from starting materials to product) in 130 of 148 example reactions of the templates it covers; found in 2.0% of 20,000 recorded products]</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>F_AZINE_N</t>
+          <t>F_WR22PQX5</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -16791,7 +16791,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>F_AZINE_N_OXIDE</t>
+          <t>F_RU2YM6UG</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -16855,7 +16855,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>F_AMINE_3</t>
+          <t>F_RF6WHWKN</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -16923,7 +16923,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>F_ARYLAMINE_2</t>
+          <t>F_GHNV6FIP</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -16984,14 +16984,14 @@
       </c>
       <c r="N95" s="3" t="inlineStr">
         <is>
-          <t>The N lone pair is shared with the ring, so it is about 10⁵ times less basic than a dialkylamine, yet it still acylates and sulfonylates readily. Includes indolines, tetrahydroquinolines and 2-(alkylamino)-azines/azoles (F_AMINE_2 covers dialkyl 2° amines; F_ARYLAMINE covers ArNH2). N-Nitrosamines are carcinogenic. EDC cyclisation of o-(alkylamino)aryl thioureas (T003860) is not counted: a new ArNH appears in the product [learned from the recorded reactions of templates T001076, T001185, T001521, T001842, T001902, T002544…; RDKit: consumed (count drops from starting materials to product) in 116 of 116 example reactions of the templates it covers; found in 10.5% of 20,000 recorded products]</t>
+          <t>The N lone pair is shared with the ring, so it is about 10⁵ times less basic than a dialkylamine, yet it still acylates and sulfonylates readily. Includes indolines, tetrahydroquinolines and 2-(alkylamino)-azines/azoles (F_AOQ6WODX covers dialkyl 2° amines; F_UY2ANYI2 covers ArNH2). N-Nitrosamines are carcinogenic. EDC cyclisation of o-(alkylamino)aryl thioureas (T003860) is not counted: a new ArNH appears in the product [learned from the recorded reactions of templates T001076, T001185, T001521, T001842, T001902, T002544…; RDKit: consumed (count drops from starting materials to product) in 116 of 116 example reactions of the templates it covers; found in 10.5% of 20,000 recorded products]</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>F_AMIDE_NH</t>
+          <t>F_ZTFQ2FCA</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -17052,14 +17052,14 @@
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
-          <t>Overlaps F_AMIDE (amide), which survives these reactions; this fragment marks the N–H that is replaced. Includes anilide, oxindole, lactam, carbamate (Boc-NH), urea, imide and primary amide N–H. An N-sulfonyl lactam (from a sulfonyl chloride) is an activated amide and can over-react (ring-opening by the nucleophile or base). Goldberg arylation of a primary amide (T007479) is not counted: the product still has an amide N–H [learned from the recorded reactions of templates T000589, T001359, T001444, T001683, T002572, T002736…; RDKit: consumed (count drops from starting materials to product) in 64 of 64 example reactions of the templates it covers; found in 26.4% of 20,000 recorded products]</t>
+          <t>Overlaps F_F3X5X5PO (amide), which survives these reactions; this fragment marks the N–H that is replaced. Includes anilide, oxindole, lactam, carbamate (Boc-NH), urea, imide and primary amide N–H. An N-sulfonyl lactam (from a sulfonyl chloride) is an activated amide and can over-react (ring-opening by the nucleophile or base). Goldberg arylation of a primary amide (T007479) is not counted: the product still has an amide N–H [learned from the recorded reactions of templates T000589, T001359, T001444, T001683, T002572, T002736…; RDKit: consumed (count drops from starting materials to product) in 64 of 64 example reactions of the templates it covers; found in 26.4% of 20,000 recorded products]</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>F_HYDRAZINE</t>
+          <t>F_RNHVSGOQ</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -17123,7 +17123,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>F_HYDROXYLAMINE</t>
+          <t>F_IV5D5PBX</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -17187,7 +17187,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>F_AMIDINE</t>
+          <t>F_RCVURP73</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -17251,7 +17251,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>F_AMIDOXIME</t>
+          <t>F_TYND2WUY</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -17315,7 +17315,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>F_ISOCYANATE</t>
+          <t>F_DF5HIJE7</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -17371,7 +17371,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>F_ENOLISABLE_CH</t>
+          <t>F_5T3LDTFX</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -17432,14 +17432,14 @@
       </c>
       <c r="N102" s="3" t="inlineStr">
         <is>
-          <t>Counted once per α carbon; marks the α position that changes while the C=O or C≡N (F_ALDEHYDE/F_KETONE/F_ESTER/F_NITRILE) survives. In acid, halogenation stops at one halogen (the halogen slows the next enolisation); in base it goes on to polyhalogenation or the haloform reaction. Excludes α carbons that already carry a halogen (the halogenation products), 1,3-dicarbonyl and cyano-carbonyl CH2 (see active methylene), acids, carboxylates and amides. Mono-alkylation of an α-CH2 (T006533) and Claisen/C-carbamoylation steps that keep an α-C–H (T005625, T004253, T004637) are not counted [learned from the recorded reactions of templates T000196, T000670, T000684, T001549, T002158, T002358…; RDKit: consumed (count drops from starting materials to product) in 84 of 84 example reactions of the templates it covers; found in 15.5% of 20,000 recorded products]</t>
+          <t>Counted once per α carbon; marks the α position that changes while the C=O or C≡N (F_ADOAMFFM/F_CFJ46WPI/F_N4PYCJQX/F_OWKLY6DL) survives. In acid, halogenation stops at one halogen (the halogen slows the next enolisation); in base it goes on to polyhalogenation or the haloform reaction. Excludes α carbons that already carry a halogen (the halogenation products), 1,3-dicarbonyl and cyano-carbonyl CH2 (see active methylene), acids, carboxylates and amides. Mono-alkylation of an α-CH2 (T006533) and Claisen/C-carbamoylation steps that keep an α-C–H (T005625, T004253, T004637) are not counted [learned from the recorded reactions of templates T000196, T000670, T000684, T001549, T002158, T002358…; RDKit: consumed (count drops from starting materials to product) in 84 of 84 example reactions of the templates it covers; found in 15.5% of 20,000 recorded products]</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>F_ACTIVE_METHYLENE</t>
+          <t>F_EJHA2TYP</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -17503,7 +17503,7 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>F_PHOSPHONATE</t>
+          <t>F_QE3E5NK3</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>F_CARBOXYLIC_ACID</t>
+          <t>F_WH4T6PP5</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -17668,7 +17668,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>F_AMINE_1</t>
+          <t>F_7TP4VNHE</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -17700,7 +17700,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>F_CARBOXYLIC_ACID</t>
+          <t>F_WH4T6PP5</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -17732,7 +17732,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_1</t>
+          <t>F_7WIM5VKY</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -17764,7 +17764,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>F_ESTER</t>
+          <t>F_N4PYCJQX</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -17796,7 +17796,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>F_ALKENE</t>
+          <t>F_43XPC2LW</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -17828,7 +17828,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>F_ALKENE_TERMINAL</t>
+          <t>F_674FQ44T</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -17860,7 +17860,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_BROMIDE</t>
+          <t>F_EDNDOOMT</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_SP3</t>
+          <t>F_CQJBM3VA</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_3</t>
+          <t>F_Z6ABGO4G</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -17956,7 +17956,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>F_BROMOHYDRIN</t>
+          <t>F_FJ2AGXG4</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -17988,7 +17988,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_HALIDE_1</t>
+          <t>F_OSWUXBJP</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -18020,7 +18020,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>F_ALKENE</t>
+          <t>F_43XPC2LW</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -18052,7 +18052,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>F_ALLYLIC_CH2</t>
+          <t>F_DHYVCP7A</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -18084,7 +18084,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>F_ALLYLIC_CH2</t>
+          <t>F_DHYVCP7A</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_BROMIDE</t>
+          <t>F_EDNDOOMT</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -18148,7 +18148,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_BROMIDE</t>
+          <t>F_EDNDOOMT</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>F_VICINAL_DIBROMIDE</t>
+          <t>F_D6B2Q4UF</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -18212,7 +18212,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_HALIDE_2</t>
+          <t>F_4KF4VNAH</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -18244,7 +18244,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_HALIDE_2</t>
+          <t>F_4KF4VNAH</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -18276,7 +18276,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>F_ALKENE</t>
+          <t>F_43XPC2LW</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -18308,7 +18308,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>F_ALKENE_TERMINAL</t>
+          <t>F_674FQ44T</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -18340,7 +18340,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_BROMIDE</t>
+          <t>F_EDNDOOMT</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -18372,7 +18372,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_HALIDE_1</t>
+          <t>F_OSWUXBJP</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -18404,7 +18404,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_BROMIDE</t>
+          <t>F_EDNDOOMT</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -18436,7 +18436,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_HALIDE_2</t>
+          <t>F_4KF4VNAH</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -18468,7 +18468,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_SP3</t>
+          <t>F_CQJBM3VA</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -18500,7 +18500,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_3</t>
+          <t>F_Z6ABGO4G</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -18532,7 +18532,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_1</t>
+          <t>F_7WIM5VKY</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_SP3</t>
+          <t>F_CQJBM3VA</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -18596,7 +18596,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -18660,7 +18660,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -18692,7 +18692,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -18724,7 +18724,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>F_ARYL_CHLORIDE</t>
+          <t>F_YYVXALOV</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -18756,7 +18756,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>F_PEROXIDE</t>
+          <t>F_NBVC3ZK3</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>F_EPOXIDE</t>
+          <t>F_GUG35WZM</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -18820,7 +18820,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>F_CARBOXYLIC_ACID</t>
+          <t>F_WH4T6PP5</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -18852,7 +18852,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -18884,7 +18884,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -18916,7 +18916,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -18948,7 +18948,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -18980,7 +18980,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>F_ARYL_CHLORIDE</t>
+          <t>F_YYVXALOV</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_SP3</t>
+          <t>F_CQJBM3VA</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -19044,7 +19044,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_SP3</t>
+          <t>F_CQJBM3VA</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -19076,7 +19076,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_2</t>
+          <t>F_JIOCZMVT</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -19108,7 +19108,7 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_2</t>
+          <t>F_JIOCZMVT</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -19140,7 +19140,7 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>F_DIOL_1_2</t>
+          <t>F_VHRSWB64</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -19172,7 +19172,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>F_ALKENE</t>
+          <t>F_43XPC2LW</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -19204,7 +19204,7 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>F_ALDEHYDE</t>
+          <t>F_ADOAMFFM</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -19236,7 +19236,7 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>F_ENOLISABLE_CH</t>
+          <t>F_5T3LDTFX</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -19268,7 +19268,7 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>F_KETONE</t>
+          <t>F_CFJ46WPI</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -19300,7 +19300,7 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>F_ENOLISABLE_CH</t>
+          <t>F_5T3LDTFX</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -19332,7 +19332,7 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>F_ENOLISABLE_CH</t>
+          <t>F_5T3LDTFX</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -19364,7 +19364,7 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>F_AMIDE</t>
+          <t>F_F3X5X5PO</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -19396,7 +19396,7 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>F_AMIDE</t>
+          <t>F_F3X5X5PO</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -19428,7 +19428,7 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>F_ALKENE</t>
+          <t>F_43XPC2LW</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -19460,7 +19460,7 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_BROMIDE</t>
+          <t>F_EDNDOOMT</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -19492,7 +19492,7 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>F_ALLYLIC_CH2</t>
+          <t>F_DHYVCP7A</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -19524,7 +19524,7 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_HALIDE_2</t>
+          <t>F_4KF4VNAH</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -19556,7 +19556,7 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>F_AMIDE</t>
+          <t>F_F3X5X5PO</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -19588,7 +19588,7 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>F_AMIDE</t>
+          <t>F_F3X5X5PO</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -19620,7 +19620,7 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>F_AMIDE_NH</t>
+          <t>F_ZTFQ2FCA</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -19652,7 +19652,7 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>F_AMIDE_NH</t>
+          <t>F_ZTFQ2FCA</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYNE</t>
+          <t>F_YAW5EFKQ</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -19716,7 +19716,7 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>F_ALKENE</t>
+          <t>F_43XPC2LW</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>F_ALKENE</t>
+          <t>F_43XPC2LW</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -19780,7 +19780,7 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYNE</t>
+          <t>F_YAW5EFKQ</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -19812,7 +19812,7 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYNE_TERMINAL</t>
+          <t>F_UNMQWRQR</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -19844,7 +19844,7 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -19876,7 +19876,7 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -19908,7 +19908,7 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -19940,7 +19940,7 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
@@ -19972,7 +19972,7 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -20004,7 +20004,7 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -20036,7 +20036,7 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -20068,7 +20068,7 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -20100,7 +20100,7 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -20132,7 +20132,7 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -20164,7 +20164,7 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>F_ARYL_BROMIDE</t>
+          <t>F_H6H7YAKN</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -20228,7 +20228,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -20260,7 +20260,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -20292,7 +20292,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -20324,7 +20324,7 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -20388,7 +20388,7 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>F_NITROARENE</t>
+          <t>F_5J6B3EOP</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -20420,7 +20420,7 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>F_ACYL_CHLORIDE</t>
+          <t>F_7W5VQUT2</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -20452,7 +20452,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -20484,7 +20484,7 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -20516,7 +20516,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -20548,7 +20548,7 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -20580,7 +20580,7 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
@@ -20612,7 +20612,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>F_KETONE</t>
+          <t>F_CFJ46WPI</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -20644,7 +20644,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>F_ENOLISABLE_CH</t>
+          <t>F_5T3LDTFX</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -20676,7 +20676,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_CHLORIDE</t>
+          <t>F_77XITLZ4</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -20708,7 +20708,7 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_HALIDE_3</t>
+          <t>F_YUNA7OOT</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -20772,7 +20772,7 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -20836,7 +20836,7 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
@@ -20868,7 +20868,7 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -20900,7 +20900,7 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_ARENE</t>
+          <t>F_W4GPHE3A</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
@@ -20932,7 +20932,7 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
@@ -20964,7 +20964,7 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
@@ -20996,7 +20996,7 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
@@ -21028,7 +21028,7 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
@@ -21060,7 +21060,7 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
@@ -21092,7 +21092,7 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>F_ARYL_METHYL</t>
+          <t>F_W7EG4A5W</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
@@ -21124,7 +21124,7 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_ARENE</t>
+          <t>F_W4GPHE3A</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
@@ -21156,7 +21156,7 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
@@ -21188,7 +21188,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
@@ -21220,7 +21220,7 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
@@ -21252,7 +21252,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
@@ -21284,7 +21284,7 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
@@ -21316,7 +21316,7 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_BROMIDE</t>
+          <t>F_EDNDOOMT</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
@@ -21348,7 +21348,7 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>F_BENZYLIC_BROMIDE</t>
+          <t>F_J2RF4BYK</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
@@ -21380,7 +21380,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_ARENE</t>
+          <t>F_W4GPHE3A</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -21412,7 +21412,7 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_HALIDE_1</t>
+          <t>F_OSWUXBJP</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
@@ -21444,7 +21444,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>F_CARBOXYLIC_ACID</t>
+          <t>F_WH4T6PP5</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -21476,7 +21476,7 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
@@ -21508,7 +21508,7 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
@@ -21540,7 +21540,7 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
@@ -21572,7 +21572,7 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
@@ -21604,7 +21604,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
@@ -21636,7 +21636,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>F_AMINE_1</t>
+          <t>F_7TP4VNHE</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
@@ -21668,7 +21668,7 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
@@ -21700,7 +21700,7 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
@@ -21732,7 +21732,7 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
@@ -21764,7 +21764,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -21796,7 +21796,7 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
@@ -21828,7 +21828,7 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>F_ARYLAMINE</t>
+          <t>F_UY2ANYI2</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
@@ -21860,7 +21860,7 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
@@ -21892,7 +21892,7 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
@@ -21956,7 +21956,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
@@ -21988,7 +21988,7 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
@@ -22020,7 +22020,7 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>F_ARYL_DIAZONIUM</t>
+          <t>F_UUBBBRAY</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
@@ -22052,7 +22052,7 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_BROMIDE</t>
+          <t>F_EDNDOOMT</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
@@ -22084,7 +22084,7 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_HALIDE_1</t>
+          <t>F_OSWUXBJP</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
@@ -22116,7 +22116,7 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>F_CYANIDE</t>
+          <t>F_NY7AYBRA</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
@@ -22148,7 +22148,7 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>F_NITRILE</t>
+          <t>F_OWKLY6DL</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
@@ -22180,7 +22180,7 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>F_ENOLISABLE_CH</t>
+          <t>F_5T3LDTFX</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
@@ -22212,7 +22212,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_BROMIDE</t>
+          <t>F_EDNDOOMT</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
@@ -22244,7 +22244,7 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_HALIDE_1</t>
+          <t>F_OSWUXBJP</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
@@ -22276,7 +22276,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>F_HYDROXIDE_ALKOXIDE</t>
+          <t>F_BLUS3XKO</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
@@ -22308,7 +22308,7 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>F_ETHER_DIALKYL</t>
+          <t>F_GWWY5MAP</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
@@ -22340,7 +22340,7 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_CHLORIDE</t>
+          <t>F_77XITLZ4</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
@@ -22372,7 +22372,7 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_HALIDE_1</t>
+          <t>F_OSWUXBJP</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
@@ -22404,7 +22404,7 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_IODIDE</t>
+          <t>F_OM2L6LN4</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
@@ -22436,7 +22436,7 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_HALIDE_1</t>
+          <t>F_OSWUXBJP</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
@@ -22468,7 +22468,7 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_BROMIDE</t>
+          <t>F_EDNDOOMT</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
@@ -22500,7 +22500,7 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_HALIDE_3</t>
+          <t>F_YUNA7OOT</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
@@ -22532,7 +22532,7 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>F_HYDROXIDE_ALKOXIDE</t>
+          <t>F_BLUS3XKO</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
@@ -22564,7 +22564,7 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>F_ALKENE</t>
+          <t>F_43XPC2LW</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
@@ -22596,7 +22596,7 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>F_ALKENE_TERMINAL</t>
+          <t>F_674FQ44T</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
@@ -22628,7 +22628,7 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>F_ALLYLIC_CH2</t>
+          <t>F_DHYVCP7A</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
@@ -22660,7 +22660,7 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_1</t>
+          <t>F_7WIM5VKY</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_SP3</t>
+          <t>F_CQJBM3VA</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
@@ -22724,7 +22724,7 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
@@ -22756,7 +22756,7 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
@@ -22788,7 +22788,7 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
@@ -22820,7 +22820,7 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
@@ -22852,7 +22852,7 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>F_ALDEHYDE</t>
+          <t>F_ADOAMFFM</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
@@ -22916,7 +22916,7 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>F_ENOLISABLE_CH</t>
+          <t>F_5T3LDTFX</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
@@ -22948,7 +22948,7 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>F_CARBOXYLIC_ACID</t>
+          <t>F_WH4T6PP5</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
@@ -22980,7 +22980,7 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_SP3</t>
+          <t>F_CQJBM3VA</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
@@ -23012,7 +23012,7 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_2</t>
+          <t>F_JIOCZMVT</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
@@ -23076,7 +23076,7 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
@@ -23108,7 +23108,7 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -23140,7 +23140,7 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
@@ -23172,7 +23172,7 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
@@ -23204,7 +23204,7 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>F_ACYL_CHLORIDE</t>
+          <t>F_7W5VQUT2</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
@@ -23236,7 +23236,7 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>F_KETONE</t>
+          <t>F_CFJ46WPI</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
@@ -23268,7 +23268,7 @@
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>F_ENOLISABLE_CH</t>
+          <t>F_5T3LDTFX</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
@@ -23300,7 +23300,7 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>F_ENOLISABLE_CH</t>
+          <t>F_5T3LDTFX</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
@@ -23332,7 +23332,7 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>F_ESTER</t>
+          <t>F_N4PYCJQX</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
@@ -23364,7 +23364,7 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
@@ -23396,7 +23396,7 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
@@ -23428,7 +23428,7 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
@@ -23460,7 +23460,7 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
@@ -23492,7 +23492,7 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
@@ -23524,7 +23524,7 @@
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>F_ALUMINIUM_HYDRIDE</t>
+          <t>F_WYH6KVDM</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
@@ -23556,7 +23556,7 @@
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_1</t>
+          <t>F_7WIM5VKY</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
@@ -23588,7 +23588,7 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
@@ -23620,7 +23620,7 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
@@ -23652,7 +23652,7 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
@@ -23684,7 +23684,7 @@
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
@@ -23716,7 +23716,7 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
@@ -23748,7 +23748,7 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_SP3</t>
+          <t>F_CQJBM3VA</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
@@ -23780,7 +23780,7 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_ARENE</t>
+          <t>F_W4GPHE3A</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
@@ -23812,7 +23812,7 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_SP3</t>
+          <t>F_CQJBM3VA</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
@@ -23844,7 +23844,7 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>F_GRIGNARD</t>
+          <t>F_F6IICZMJ</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
@@ -23876,7 +23876,7 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
@@ -23908,7 +23908,7 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
@@ -23940,7 +23940,7 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
@@ -24004,7 +24004,7 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
@@ -24036,7 +24036,7 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>F_GRIGNARD</t>
+          <t>F_F6IICZMJ</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
@@ -24068,7 +24068,7 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
@@ -24100,7 +24100,7 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
@@ -24132,7 +24132,7 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
@@ -24228,7 +24228,7 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
@@ -24260,7 +24260,7 @@
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
@@ -24292,7 +24292,7 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
@@ -24324,7 +24324,7 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
@@ -24356,7 +24356,7 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
@@ -24388,7 +24388,7 @@
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
@@ -24420,7 +24420,7 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
@@ -24452,7 +24452,7 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
@@ -24484,7 +24484,7 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
@@ -24516,7 +24516,7 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
@@ -24548,7 +24548,7 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>F_ALKENE</t>
+          <t>F_43XPC2LW</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
@@ -24580,7 +24580,7 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>F_ALKENE_TERMINAL</t>
+          <t>F_674FQ44T</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
@@ -24612,7 +24612,7 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>F_ALLYLIC_CH2</t>
+          <t>F_DHYVCP7A</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>F_ALLYLIC_CH2</t>
+          <t>F_DHYVCP7A</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
@@ -24676,7 +24676,7 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
@@ -24708,7 +24708,7 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
@@ -24740,7 +24740,7 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
@@ -24772,7 +24772,7 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
@@ -24804,7 +24804,7 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
@@ -24836,7 +24836,7 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
@@ -24868,7 +24868,7 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
@@ -24900,7 +24900,7 @@
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
@@ -24932,7 +24932,7 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
@@ -24964,7 +24964,7 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
@@ -24996,7 +24996,7 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
@@ -25028,7 +25028,7 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
@@ -25060,7 +25060,7 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
@@ -25092,7 +25092,7 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
@@ -25124,7 +25124,7 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
@@ -25156,7 +25156,7 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_1</t>
+          <t>F_7WIM5VKY</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
@@ -25188,7 +25188,7 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_1</t>
+          <t>F_7WIM5VKY</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
@@ -25220,7 +25220,7 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_SP3</t>
+          <t>F_CQJBM3VA</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
@@ -25252,7 +25252,7 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_SP3</t>
+          <t>F_CQJBM3VA</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>F_DIOL_1_2</t>
+          <t>F_VHRSWB64</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
@@ -25316,7 +25316,7 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
@@ -25348,7 +25348,7 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
@@ -25380,7 +25380,7 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
@@ -25412,7 +25412,7 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
@@ -25444,7 +25444,7 @@
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>F_ARYL_METHYL</t>
+          <t>F_W7EG4A5W</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
@@ -25476,7 +25476,7 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_ARENE</t>
+          <t>F_W4GPHE3A</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
@@ -25508,7 +25508,7 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>F_ARENESULFONIC_ACID</t>
+          <t>F_TH2DYID6</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
@@ -25540,7 +25540,7 @@
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>F_ETHER_DIALKYL</t>
+          <t>F_GWWY5MAP</t>
         </is>
       </c>
       <c r="D249" s="3" t="inlineStr">
@@ -25572,7 +25572,7 @@
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>F_ETHER_DIALKYL</t>
+          <t>F_GWWY5MAP</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
@@ -25604,7 +25604,7 @@
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>F_ACETAL_KETAL</t>
+          <t>F_Z7L4L6RQ</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
@@ -25636,7 +25636,7 @@
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr">
@@ -25668,7 +25668,7 @@
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
@@ -25700,7 +25700,7 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
@@ -25764,7 +25764,7 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
@@ -25796,7 +25796,7 @@
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>F_ALDEHYDE</t>
+          <t>F_ADOAMFFM</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
@@ -25828,7 +25828,7 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
@@ -25860,7 +25860,7 @@
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
@@ -25892,7 +25892,7 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
@@ -25924,7 +25924,7 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
@@ -25956,7 +25956,7 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
@@ -25988,7 +25988,7 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
@@ -26020,7 +26020,7 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
@@ -26052,7 +26052,7 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
@@ -26084,7 +26084,7 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
@@ -26116,7 +26116,7 @@
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
@@ -26148,7 +26148,7 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>F_IMINE</t>
+          <t>F_LPMNZ3FU</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
@@ -26180,7 +26180,7 @@
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>F_AMINE_1</t>
+          <t>F_7TP4VNHE</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
@@ -26212,7 +26212,7 @@
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>F_NITRILE</t>
+          <t>F_OWKLY6DL</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
@@ -26244,7 +26244,7 @@
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>F_AMINE_2</t>
+          <t>F_AOQ6WODX</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
@@ -26276,7 +26276,7 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>F_HYDROXIDE_ALKOXIDE</t>
+          <t>F_BLUS3XKO</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
@@ -26308,7 +26308,7 @@
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>F_ALKENE</t>
+          <t>F_43XPC2LW</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
@@ -26340,7 +26340,7 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
@@ -26372,7 +26372,7 @@
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
@@ -26436,7 +26436,7 @@
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
@@ -26468,7 +26468,7 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
@@ -26500,7 +26500,7 @@
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>F_KETONE</t>
+          <t>F_CFJ46WPI</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
@@ -26532,7 +26532,7 @@
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>F_ENONE</t>
+          <t>F_QTJCKBIJ</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
@@ -26564,7 +26564,7 @@
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>F_ENOLISABLE_CH</t>
+          <t>F_5T3LDTFX</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
@@ -26596,7 +26596,7 @@
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>F_ESTER</t>
+          <t>F_N4PYCJQX</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
@@ -26628,7 +26628,7 @@
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>F_ENOLISABLE_CH</t>
+          <t>F_5T3LDTFX</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr">
@@ -26660,7 +26660,7 @@
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>F_ESTER</t>
+          <t>F_N4PYCJQX</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
@@ -26692,7 +26692,7 @@
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D285" s="3" t="inlineStr">
@@ -26724,7 +26724,7 @@
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
@@ -26756,7 +26756,7 @@
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D287" s="3" t="inlineStr">
@@ -26788,7 +26788,7 @@
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D289" s="3" t="inlineStr">
@@ -26852,7 +26852,7 @@
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
@@ -26884,7 +26884,7 @@
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D291" s="3" t="inlineStr">
@@ -26916,7 +26916,7 @@
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
@@ -26948,7 +26948,7 @@
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D293" s="3" t="inlineStr">
@@ -26980,7 +26980,7 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
@@ -27012,7 +27012,7 @@
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>F_AZINE_N</t>
+          <t>F_WR22PQX5</t>
         </is>
       </c>
       <c r="D295" s="3" t="inlineStr">
@@ -27044,7 +27044,7 @@
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D296" s="3" t="inlineStr">
@@ -27076,7 +27076,7 @@
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D297" s="3" t="inlineStr">
@@ -27108,7 +27108,7 @@
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D299" s="3" t="inlineStr">
@@ -27172,7 +27172,7 @@
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D300" s="3" t="inlineStr">
@@ -27204,7 +27204,7 @@
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>F_AMIDE</t>
+          <t>F_F3X5X5PO</t>
         </is>
       </c>
       <c r="D301" s="3" t="inlineStr">
@@ -27236,7 +27236,7 @@
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>F_AMIDE_NH</t>
+          <t>F_ZTFQ2FCA</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr">
@@ -27268,7 +27268,7 @@
       </c>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t>F_CARBOXYLIC_ACID</t>
+          <t>F_WH4T6PP5</t>
         </is>
       </c>
       <c r="D303" s="3" t="inlineStr">
@@ -27300,7 +27300,7 @@
       </c>
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D304" s="3" t="inlineStr">
@@ -27332,7 +27332,7 @@
       </c>
       <c r="C305" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D305" s="3" t="inlineStr">
@@ -27364,7 +27364,7 @@
       </c>
       <c r="C306" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D306" s="3" t="inlineStr">
@@ -27396,7 +27396,7 @@
       </c>
       <c r="C307" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D307" s="3" t="inlineStr">
@@ -27428,7 +27428,7 @@
       </c>
       <c r="C308" s="3" t="inlineStr">
         <is>
-          <t>F_PHENOL</t>
+          <t>F_EBFEFTNC</t>
         </is>
       </c>
       <c r="D308" s="3" t="inlineStr">
@@ -27460,7 +27460,7 @@
       </c>
       <c r="C309" s="3" t="inlineStr">
         <is>
-          <t>F_ESTER</t>
+          <t>F_N4PYCJQX</t>
         </is>
       </c>
       <c r="D309" s="3" t="inlineStr">
@@ -27492,7 +27492,7 @@
       </c>
       <c r="C310" s="3" t="inlineStr">
         <is>
-          <t>F_ESTER</t>
+          <t>F_N4PYCJQX</t>
         </is>
       </c>
       <c r="D310" s="3" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="C311" s="3" t="inlineStr">
         <is>
-          <t>F_ANHYDRIDE</t>
+          <t>F_IOJJ46QM</t>
         </is>
       </c>
       <c r="D311" s="3" t="inlineStr">
@@ -27556,7 +27556,7 @@
       </c>
       <c r="C312" s="3" t="inlineStr">
         <is>
-          <t>F_ENOLISABLE_CH</t>
+          <t>F_5T3LDTFX</t>
         </is>
       </c>
       <c r="D312" s="3" t="inlineStr">
@@ -27588,7 +27588,7 @@
       </c>
       <c r="C313" s="3" t="inlineStr">
         <is>
-          <t>F_ENOLISABLE_CH</t>
+          <t>F_5T3LDTFX</t>
         </is>
       </c>
       <c r="D313" s="3" t="inlineStr">
@@ -27620,7 +27620,7 @@
       </c>
       <c r="C314" s="3" t="inlineStr">
         <is>
-          <t>F_CARBOXYLIC_ACID</t>
+          <t>F_WH4T6PP5</t>
         </is>
       </c>
       <c r="D314" s="3" t="inlineStr">
@@ -27652,7 +27652,7 @@
       </c>
       <c r="C315" s="3" t="inlineStr">
         <is>
-          <t>F_ESTER</t>
+          <t>F_N4PYCJQX</t>
         </is>
       </c>
       <c r="D315" s="3" t="inlineStr">
@@ -27684,7 +27684,7 @@
       </c>
       <c r="C316" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D316" s="3" t="inlineStr">
@@ -27716,7 +27716,7 @@
       </c>
       <c r="C317" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D317" s="3" t="inlineStr">
@@ -27748,7 +27748,7 @@
       </c>
       <c r="C318" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D318" s="3" t="inlineStr">
@@ -27780,7 +27780,7 @@
       </c>
       <c r="C319" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D319" s="3" t="inlineStr">
@@ -27812,7 +27812,7 @@
       </c>
       <c r="C320" s="3" t="inlineStr">
         <is>
-          <t>F_ENOLISABLE_CH</t>
+          <t>F_5T3LDTFX</t>
         </is>
       </c>
       <c r="D320" s="3" t="inlineStr">
@@ -27844,7 +27844,7 @@
       </c>
       <c r="C321" s="3" t="inlineStr">
         <is>
-          <t>F_ALKENE</t>
+          <t>F_43XPC2LW</t>
         </is>
       </c>
       <c r="D321" s="3" t="inlineStr">
@@ -27876,7 +27876,7 @@
       </c>
       <c r="C322" s="3" t="inlineStr">
         <is>
-          <t>F_ALKENE</t>
+          <t>F_43XPC2LW</t>
         </is>
       </c>
       <c r="D322" s="3" t="inlineStr">
@@ -27908,7 +27908,7 @@
       </c>
       <c r="C323" s="3" t="inlineStr">
         <is>
-          <t>F_ALKENE_TERMINAL</t>
+          <t>F_674FQ44T</t>
         </is>
       </c>
       <c r="D323" s="3" t="inlineStr">
@@ -27940,7 +27940,7 @@
       </c>
       <c r="C324" s="3" t="inlineStr">
         <is>
-          <t>F_ALKENE_TERMINAL</t>
+          <t>F_674FQ44T</t>
         </is>
       </c>
       <c r="D324" s="3" t="inlineStr">
@@ -27972,7 +27972,7 @@
       </c>
       <c r="C325" s="3" t="inlineStr">
         <is>
-          <t>F_CONJUGATED_DIENE</t>
+          <t>F_DRXF7R5Y</t>
         </is>
       </c>
       <c r="D325" s="3" t="inlineStr">
@@ -28004,7 +28004,7 @@
       </c>
       <c r="C326" s="3" t="inlineStr">
         <is>
-          <t>F_ESTER</t>
+          <t>F_N4PYCJQX</t>
         </is>
       </c>
       <c r="D326" s="3" t="inlineStr">
@@ -28036,7 +28036,7 @@
       </c>
       <c r="C327" s="3" t="inlineStr">
         <is>
-          <t>F_ESTER</t>
+          <t>F_N4PYCJQX</t>
         </is>
       </c>
       <c r="D327" s="3" t="inlineStr">
@@ -28068,7 +28068,7 @@
       </c>
       <c r="C328" s="3" t="inlineStr">
         <is>
-          <t>F_ALKENE</t>
+          <t>F_43XPC2LW</t>
         </is>
       </c>
       <c r="D328" s="3" t="inlineStr">
@@ -28100,7 +28100,7 @@
       </c>
       <c r="C329" s="3" t="inlineStr">
         <is>
-          <t>F_ANHYDRIDE</t>
+          <t>F_IOJJ46QM</t>
         </is>
       </c>
       <c r="D329" s="3" t="inlineStr">
@@ -28132,7 +28132,7 @@
       </c>
       <c r="C330" s="3" t="inlineStr">
         <is>
-          <t>F_ESTER</t>
+          <t>F_N4PYCJQX</t>
         </is>
       </c>
       <c r="D330" s="3" t="inlineStr">
@@ -28164,7 +28164,7 @@
       </c>
       <c r="C331" s="3" t="inlineStr">
         <is>
-          <t>F_ESTER</t>
+          <t>F_N4PYCJQX</t>
         </is>
       </c>
       <c r="D331" s="3" t="inlineStr">
@@ -28196,7 +28196,7 @@
       </c>
       <c r="C332" s="3" t="inlineStr">
         <is>
-          <t>F_ALKENE</t>
+          <t>F_43XPC2LW</t>
         </is>
       </c>
       <c r="D332" s="3" t="inlineStr">
@@ -28228,7 +28228,7 @@
       </c>
       <c r="C333" s="3" t="inlineStr">
         <is>
-          <t>F_ALLYLIC_CH2</t>
+          <t>F_DHYVCP7A</t>
         </is>
       </c>
       <c r="D333" s="3" t="inlineStr">
@@ -28260,7 +28260,7 @@
       </c>
       <c r="C334" s="3" t="inlineStr">
         <is>
-          <t>F_ALLYLIC_CH2</t>
+          <t>F_DHYVCP7A</t>
         </is>
       </c>
       <c r="D334" s="3" t="inlineStr">
@@ -28292,7 +28292,7 @@
       </c>
       <c r="C335" s="3" t="inlineStr">
         <is>
-          <t>F_ANHYDRIDE</t>
+          <t>F_IOJJ46QM</t>
         </is>
       </c>
       <c r="D335" s="3" t="inlineStr">
@@ -28324,7 +28324,7 @@
       </c>
       <c r="C336" s="3" t="inlineStr">
         <is>
-          <t>F_ENOLISABLE_CH</t>
+          <t>F_5T3LDTFX</t>
         </is>
       </c>
       <c r="D336" s="3" t="inlineStr">
@@ -28356,7 +28356,7 @@
       </c>
       <c r="C337" s="3" t="inlineStr">
         <is>
-          <t>F_ENOLISABLE_CH</t>
+          <t>F_5T3LDTFX</t>
         </is>
       </c>
       <c r="D337" s="3" t="inlineStr">
@@ -28388,7 +28388,7 @@
       </c>
       <c r="C338" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D338" s="3" t="inlineStr">
@@ -28420,7 +28420,7 @@
       </c>
       <c r="C339" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D339" s="3" t="inlineStr">
@@ -28452,7 +28452,7 @@
       </c>
       <c r="C340" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D340" s="3" t="inlineStr">
@@ -28484,7 +28484,7 @@
       </c>
       <c r="C341" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D341" s="3" t="inlineStr">
@@ -28516,7 +28516,7 @@
       </c>
       <c r="C342" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D342" s="3" t="inlineStr">
@@ -28548,7 +28548,7 @@
       </c>
       <c r="C343" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_SP3</t>
+          <t>F_CQJBM3VA</t>
         </is>
       </c>
       <c r="D343" s="3" t="inlineStr">
@@ -28580,7 +28580,7 @@
       </c>
       <c r="C344" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_3</t>
+          <t>F_Z6ABGO4G</t>
         </is>
       </c>
       <c r="D344" s="3" t="inlineStr">
@@ -28612,7 +28612,7 @@
       </c>
       <c r="C345" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_ARENE</t>
+          <t>F_W4GPHE3A</t>
         </is>
       </c>
       <c r="D345" s="3" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="C346" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_IODIDE</t>
+          <t>F_OM2L6LN4</t>
         </is>
       </c>
       <c r="D346" s="3" t="inlineStr">
@@ -28676,7 +28676,7 @@
       </c>
       <c r="C347" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_HALIDE_2</t>
+          <t>F_4KF4VNAH</t>
         </is>
       </c>
       <c r="D347" s="3" t="inlineStr">
@@ -28708,7 +28708,7 @@
       </c>
       <c r="C348" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_CHLORIDE</t>
+          <t>F_77XITLZ4</t>
         </is>
       </c>
       <c r="D348" s="3" t="inlineStr">
@@ -28740,7 +28740,7 @@
       </c>
       <c r="C349" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_CHLORIDE</t>
+          <t>F_77XITLZ4</t>
         </is>
       </c>
       <c r="D349" s="3" t="inlineStr">
@@ -28772,7 +28772,7 @@
       </c>
       <c r="C350" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_HALIDE_2</t>
+          <t>F_4KF4VNAH</t>
         </is>
       </c>
       <c r="D350" s="3" t="inlineStr">
@@ -28804,7 +28804,7 @@
       </c>
       <c r="C351" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_HALIDE_2</t>
+          <t>F_4KF4VNAH</t>
         </is>
       </c>
       <c r="D351" s="3" t="inlineStr">
@@ -28836,7 +28836,7 @@
       </c>
       <c r="C352" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_BROMIDE</t>
+          <t>F_EDNDOOMT</t>
         </is>
       </c>
       <c r="D352" s="3" t="inlineStr">
@@ -28868,7 +28868,7 @@
       </c>
       <c r="C353" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_BROMIDE</t>
+          <t>F_EDNDOOMT</t>
         </is>
       </c>
       <c r="D353" s="3" t="inlineStr">
@@ -28900,7 +28900,7 @@
       </c>
       <c r="C354" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_BROMIDE</t>
+          <t>F_EDNDOOMT</t>
         </is>
       </c>
       <c r="D354" s="3" t="inlineStr">
@@ -28932,7 +28932,7 @@
       </c>
       <c r="C355" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_BROMIDE</t>
+          <t>F_EDNDOOMT</t>
         </is>
       </c>
       <c r="D355" s="3" t="inlineStr">
@@ -28964,7 +28964,7 @@
       </c>
       <c r="C356" s="3" t="inlineStr">
         <is>
-          <t>F_VICINAL_DIBROMIDE</t>
+          <t>F_D6B2Q4UF</t>
         </is>
       </c>
       <c r="D356" s="3" t="inlineStr">
@@ -28996,7 +28996,7 @@
       </c>
       <c r="C357" s="3" t="inlineStr">
         <is>
-          <t>F_VICINAL_DIBROMIDE</t>
+          <t>F_D6B2Q4UF</t>
         </is>
       </c>
       <c r="D357" s="3" t="inlineStr">
@@ -29028,7 +29028,7 @@
       </c>
       <c r="C358" s="3" t="inlineStr">
         <is>
-          <t>F_VICINAL_DIBROMIDE</t>
+          <t>F_D6B2Q4UF</t>
         </is>
       </c>
       <c r="D358" s="3" t="inlineStr">
@@ -29060,7 +29060,7 @@
       </c>
       <c r="C359" s="3" t="inlineStr">
         <is>
-          <t>F_VICINAL_DIBROMIDE</t>
+          <t>F_D6B2Q4UF</t>
         </is>
       </c>
       <c r="D359" s="3" t="inlineStr">
@@ -29092,7 +29092,7 @@
       </c>
       <c r="C360" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_BROMIDE</t>
+          <t>F_EDNDOOMT</t>
         </is>
       </c>
       <c r="D360" s="3" t="inlineStr">
@@ -29124,7 +29124,7 @@
       </c>
       <c r="C361" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_BROMIDE</t>
+          <t>F_EDNDOOMT</t>
         </is>
       </c>
       <c r="D361" s="3" t="inlineStr">
@@ -29156,7 +29156,7 @@
       </c>
       <c r="C362" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYNE</t>
+          <t>F_YAW5EFKQ</t>
         </is>
       </c>
       <c r="D362" s="3" t="inlineStr">
@@ -29188,7 +29188,7 @@
       </c>
       <c r="C363" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYNE_TERMINAL</t>
+          <t>F_UNMQWRQR</t>
         </is>
       </c>
       <c r="D363" s="3" t="inlineStr">
@@ -29220,7 +29220,7 @@
       </c>
       <c r="C364" s="3" t="inlineStr">
         <is>
-          <t>F_ALDEHYDE</t>
+          <t>F_ADOAMFFM</t>
         </is>
       </c>
       <c r="D364" s="3" t="inlineStr">
@@ -29252,7 +29252,7 @@
       </c>
       <c r="C365" s="3" t="inlineStr">
         <is>
-          <t>F_ENOLISABLE_CH</t>
+          <t>F_5T3LDTFX</t>
         </is>
       </c>
       <c r="D365" s="3" t="inlineStr">
@@ -29284,7 +29284,7 @@
       </c>
       <c r="C366" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_IODIDE</t>
+          <t>F_OM2L6LN4</t>
         </is>
       </c>
       <c r="D366" s="3" t="inlineStr">
@@ -29316,7 +29316,7 @@
       </c>
       <c r="C367" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_IODIDE</t>
+          <t>F_OM2L6LN4</t>
         </is>
       </c>
       <c r="D367" s="3" t="inlineStr">
@@ -29348,7 +29348,7 @@
       </c>
       <c r="C368" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_BROMIDE</t>
+          <t>F_EDNDOOMT</t>
         </is>
       </c>
       <c r="D368" s="3" t="inlineStr">
@@ -29380,7 +29380,7 @@
       </c>
       <c r="C369" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_HALIDE_2</t>
+          <t>F_4KF4VNAH</t>
         </is>
       </c>
       <c r="D369" s="3" t="inlineStr">
@@ -29412,7 +29412,7 @@
       </c>
       <c r="C370" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D370" s="3" t="inlineStr">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="C371" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D371" s="3" t="inlineStr">
@@ -29476,7 +29476,7 @@
       </c>
       <c r="C372" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D372" s="3" t="inlineStr">
@@ -29508,7 +29508,7 @@
       </c>
       <c r="C373" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D373" s="3" t="inlineStr">
@@ -29540,7 +29540,7 @@
       </c>
       <c r="C374" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D374" s="3" t="inlineStr">
@@ -29572,7 +29572,7 @@
       </c>
       <c r="C375" s="3" t="inlineStr">
         <is>
-          <t>F_ARYL_CHLORIDE</t>
+          <t>F_YYVXALOV</t>
         </is>
       </c>
       <c r="D375" s="3" t="inlineStr">
@@ -29604,7 +29604,7 @@
       </c>
       <c r="C376" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D376" s="3" t="inlineStr">
@@ -29636,7 +29636,7 @@
       </c>
       <c r="C377" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D377" s="3" t="inlineStr">
@@ -29668,7 +29668,7 @@
       </c>
       <c r="C378" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D378" s="3" t="inlineStr">
@@ -29700,7 +29700,7 @@
       </c>
       <c r="C379" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D379" s="3" t="inlineStr">
@@ -29732,7 +29732,7 @@
       </c>
       <c r="C380" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D380" s="3" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="C381" s="3" t="inlineStr">
         <is>
-          <t>F_ARENESULFONIC_ACID</t>
+          <t>F_TH2DYID6</t>
         </is>
       </c>
       <c r="D381" s="3" t="inlineStr">
@@ -29796,7 +29796,7 @@
       </c>
       <c r="C382" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D382" s="3" t="inlineStr">
@@ -29828,7 +29828,7 @@
       </c>
       <c r="C383" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D383" s="3" t="inlineStr">
@@ -29860,7 +29860,7 @@
       </c>
       <c r="C384" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D384" s="3" t="inlineStr">
@@ -29892,7 +29892,7 @@
       </c>
       <c r="C385" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D385" s="3" t="inlineStr">
@@ -29924,7 +29924,7 @@
       </c>
       <c r="C386" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D386" s="3" t="inlineStr">
@@ -29956,7 +29956,7 @@
       </c>
       <c r="C387" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_ARENE</t>
+          <t>F_W4GPHE3A</t>
         </is>
       </c>
       <c r="D387" s="3" t="inlineStr">
@@ -29988,7 +29988,7 @@
       </c>
       <c r="C388" s="3" t="inlineStr">
         <is>
-          <t>F_HYDROXIDE_ALKOXIDE</t>
+          <t>F_BLUS3XKO</t>
         </is>
       </c>
       <c r="D388" s="3" t="inlineStr">
@@ -30020,7 +30020,7 @@
       </c>
       <c r="C389" s="3" t="inlineStr">
         <is>
-          <t>F_HYDRAZINE</t>
+          <t>F_RNHVSGOQ</t>
         </is>
       </c>
       <c r="D389" s="3" t="inlineStr">
@@ -30052,7 +30052,7 @@
       </c>
       <c r="C390" s="3" t="inlineStr">
         <is>
-          <t>F_ALKENE</t>
+          <t>F_43XPC2LW</t>
         </is>
       </c>
       <c r="D390" s="3" t="inlineStr">
@@ -30084,7 +30084,7 @@
       </c>
       <c r="C391" s="3" t="inlineStr">
         <is>
-          <t>F_ALKENE</t>
+          <t>F_43XPC2LW</t>
         </is>
       </c>
       <c r="D391" s="3" t="inlineStr">
@@ -30116,7 +30116,7 @@
       </c>
       <c r="C392" s="3" t="inlineStr">
         <is>
-          <t>F_ALLYLIC_CH2</t>
+          <t>F_DHYVCP7A</t>
         </is>
       </c>
       <c r="D392" s="3" t="inlineStr">
@@ -30148,7 +30148,7 @@
       </c>
       <c r="C393" s="3" t="inlineStr">
         <is>
-          <t>F_ALLYLIC_CH2</t>
+          <t>F_DHYVCP7A</t>
         </is>
       </c>
       <c r="D393" s="3" t="inlineStr">
@@ -30180,7 +30180,7 @@
       </c>
       <c r="C394" s="3" t="inlineStr">
         <is>
-          <t>F_ALLYLIC_CH2</t>
+          <t>F_DHYVCP7A</t>
         </is>
       </c>
       <c r="D394" s="3" t="inlineStr">
@@ -30212,7 +30212,7 @@
       </c>
       <c r="C395" s="3" t="inlineStr">
         <is>
-          <t>F_ALLYLIC_CH2</t>
+          <t>F_DHYVCP7A</t>
         </is>
       </c>
       <c r="D395" s="3" t="inlineStr">
@@ -30244,7 +30244,7 @@
       </c>
       <c r="C396" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D396" s="3" t="inlineStr">
@@ -30276,7 +30276,7 @@
       </c>
       <c r="C397" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D397" s="3" t="inlineStr">
@@ -30308,7 +30308,7 @@
       </c>
       <c r="C398" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D398" s="3" t="inlineStr">
@@ -30340,7 +30340,7 @@
       </c>
       <c r="C399" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D399" s="3" t="inlineStr">
@@ -30372,7 +30372,7 @@
       </c>
       <c r="C400" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D400" s="3" t="inlineStr">
@@ -30404,7 +30404,7 @@
       </c>
       <c r="C401" s="3" t="inlineStr">
         <is>
-          <t>F_PHENOL</t>
+          <t>F_EBFEFTNC</t>
         </is>
       </c>
       <c r="D401" s="3" t="inlineStr">
@@ -30436,7 +30436,7 @@
       </c>
       <c r="C402" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D402" s="3" t="inlineStr">
@@ -30468,7 +30468,7 @@
       </c>
       <c r="C403" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D403" s="3" t="inlineStr">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C404" s="3" t="inlineStr">
         <is>
-          <t>F_ARYL_BROMIDE</t>
+          <t>F_H6H7YAKN</t>
         </is>
       </c>
       <c r="D404" s="3" t="inlineStr">
@@ -30532,7 +30532,7 @@
       </c>
       <c r="C405" s="3" t="inlineStr">
         <is>
-          <t>F_ARYL_BROMIDE</t>
+          <t>F_H6H7YAKN</t>
         </is>
       </c>
       <c r="D405" s="3" t="inlineStr">
@@ -30564,7 +30564,7 @@
       </c>
       <c r="C406" s="3" t="inlineStr">
         <is>
-          <t>F_ARYL_BROMIDE</t>
+          <t>F_H6H7YAKN</t>
         </is>
       </c>
       <c r="D406" s="3" t="inlineStr">
@@ -30596,7 +30596,7 @@
       </c>
       <c r="C407" s="3" t="inlineStr">
         <is>
-          <t>F_PHENOL</t>
+          <t>F_EBFEFTNC</t>
         </is>
       </c>
       <c r="D407" s="3" t="inlineStr">
@@ -30628,7 +30628,7 @@
       </c>
       <c r="C408" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D408" s="3" t="inlineStr">
@@ -30660,7 +30660,7 @@
       </c>
       <c r="C409" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D409" s="3" t="inlineStr">
@@ -30692,7 +30692,7 @@
       </c>
       <c r="C410" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D410" s="3" t="inlineStr">
@@ -30724,7 +30724,7 @@
       </c>
       <c r="C411" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D411" s="3" t="inlineStr">
@@ -30756,7 +30756,7 @@
       </c>
       <c r="C412" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D412" s="3" t="inlineStr">
@@ -30788,7 +30788,7 @@
       </c>
       <c r="C413" s="3" t="inlineStr">
         <is>
-          <t>F_AMIDE</t>
+          <t>F_F3X5X5PO</t>
         </is>
       </c>
       <c r="D413" s="3" t="inlineStr">
@@ -30820,7 +30820,7 @@
       </c>
       <c r="C414" s="3" t="inlineStr">
         <is>
-          <t>F_AMIDE_NH</t>
+          <t>F_ZTFQ2FCA</t>
         </is>
       </c>
       <c r="D414" s="3" t="inlineStr">
@@ -30852,7 +30852,7 @@
       </c>
       <c r="C415" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D415" s="3" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="C416" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D416" s="3" t="inlineStr">
@@ -30916,7 +30916,7 @@
       </c>
       <c r="C417" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D417" s="3" t="inlineStr">
@@ -30948,7 +30948,7 @@
       </c>
       <c r="C418" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D418" s="3" t="inlineStr">
@@ -30980,7 +30980,7 @@
       </c>
       <c r="C419" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D419" s="3" t="inlineStr">
@@ -31012,7 +31012,7 @@
       </c>
       <c r="C420" s="3" t="inlineStr">
         <is>
-          <t>F_NITRILE</t>
+          <t>F_OWKLY6DL</t>
         </is>
       </c>
       <c r="D420" s="3" t="inlineStr">
@@ -31044,7 +31044,7 @@
       </c>
       <c r="C421" s="3" t="inlineStr">
         <is>
-          <t>F_AMINE_1</t>
+          <t>F_7TP4VNHE</t>
         </is>
       </c>
       <c r="D421" s="3" t="inlineStr">
@@ -31076,7 +31076,7 @@
       </c>
       <c r="C422" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D422" s="3" t="inlineStr">
@@ -31108,7 +31108,7 @@
       </c>
       <c r="C423" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D423" s="3" t="inlineStr">
@@ -31140,7 +31140,7 @@
       </c>
       <c r="C424" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D424" s="3" t="inlineStr">
@@ -31172,7 +31172,7 @@
       </c>
       <c r="C425" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D425" s="3" t="inlineStr">
@@ -31204,7 +31204,7 @@
       </c>
       <c r="C426" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D426" s="3" t="inlineStr">
@@ -31236,7 +31236,7 @@
       </c>
       <c r="C427" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_ARENE</t>
+          <t>F_W4GPHE3A</t>
         </is>
       </c>
       <c r="D427" s="3" t="inlineStr">
@@ -31268,7 +31268,7 @@
       </c>
       <c r="C428" s="3" t="inlineStr">
         <is>
-          <t>F_AMIDE</t>
+          <t>F_F3X5X5PO</t>
         </is>
       </c>
       <c r="D428" s="3" t="inlineStr">
@@ -31300,7 +31300,7 @@
       </c>
       <c r="C429" s="3" t="inlineStr">
         <is>
-          <t>F_AMINE_3</t>
+          <t>F_RF6WHWKN</t>
         </is>
       </c>
       <c r="D429" s="3" t="inlineStr">
@@ -31332,7 +31332,7 @@
       </c>
       <c r="C430" s="3" t="inlineStr">
         <is>
-          <t>F_EPOXIDE</t>
+          <t>F_GUG35WZM</t>
         </is>
       </c>
       <c r="D430" s="3" t="inlineStr">
@@ -31364,7 +31364,7 @@
       </c>
       <c r="C431" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_1</t>
+          <t>F_7WIM5VKY</t>
         </is>
       </c>
       <c r="D431" s="3" t="inlineStr">
@@ -31396,7 +31396,7 @@
       </c>
       <c r="C432" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D432" s="3" t="inlineStr">
@@ -31428,7 +31428,7 @@
       </c>
       <c r="C433" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D433" s="3" t="inlineStr">
@@ -31460,7 +31460,7 @@
       </c>
       <c r="C434" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D434" s="3" t="inlineStr">
@@ -31492,7 +31492,7 @@
       </c>
       <c r="C435" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D435" s="3" t="inlineStr">
@@ -31524,7 +31524,7 @@
       </c>
       <c r="C436" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D436" s="3" t="inlineStr">
@@ -31556,7 +31556,7 @@
       </c>
       <c r="C437" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_SP3</t>
+          <t>F_CQJBM3VA</t>
         </is>
       </c>
       <c r="D437" s="3" t="inlineStr">
@@ -31588,7 +31588,7 @@
       </c>
       <c r="C438" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_ARENE</t>
+          <t>F_W4GPHE3A</t>
         </is>
       </c>
       <c r="D438" s="3" t="inlineStr">
@@ -31620,7 +31620,7 @@
       </c>
       <c r="C439" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_SP3</t>
+          <t>F_CQJBM3VA</t>
         </is>
       </c>
       <c r="D439" s="3" t="inlineStr">
@@ -31652,7 +31652,7 @@
       </c>
       <c r="C440" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_3</t>
+          <t>F_Z6ABGO4G</t>
         </is>
       </c>
       <c r="D440" s="3" t="inlineStr">
@@ -31684,7 +31684,7 @@
       </c>
       <c r="C441" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D441" s="3" t="inlineStr">
@@ -31716,7 +31716,7 @@
       </c>
       <c r="C442" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D442" s="3" t="inlineStr">
@@ -31748,7 +31748,7 @@
       </c>
       <c r="C443" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D443" s="3" t="inlineStr">
@@ -31780,7 +31780,7 @@
       </c>
       <c r="C444" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D444" s="3" t="inlineStr">
@@ -31812,7 +31812,7 @@
       </c>
       <c r="C445" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D445" s="3" t="inlineStr">
@@ -31844,7 +31844,7 @@
       </c>
       <c r="C446" s="3" t="inlineStr">
         <is>
-          <t>F_KETONE</t>
+          <t>F_CFJ46WPI</t>
         </is>
       </c>
       <c r="D446" s="3" t="inlineStr">
@@ -31876,7 +31876,7 @@
       </c>
       <c r="C447" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_ARENE</t>
+          <t>F_W4GPHE3A</t>
         </is>
       </c>
       <c r="D447" s="3" t="inlineStr">
@@ -31908,7 +31908,7 @@
       </c>
       <c r="C448" s="3" t="inlineStr">
         <is>
-          <t>F_ENOLISABLE_CH</t>
+          <t>F_5T3LDTFX</t>
         </is>
       </c>
       <c r="D448" s="3" t="inlineStr">
@@ -31940,7 +31940,7 @@
       </c>
       <c r="C449" s="3" t="inlineStr">
         <is>
-          <t>F_ENOLISABLE_CH</t>
+          <t>F_5T3LDTFX</t>
         </is>
       </c>
       <c r="D449" s="3" t="inlineStr">
@@ -31972,7 +31972,7 @@
       </c>
       <c r="C450" s="3" t="inlineStr">
         <is>
-          <t>F_ESTER</t>
+          <t>F_N4PYCJQX</t>
         </is>
       </c>
       <c r="D450" s="3" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="C451" s="3" t="inlineStr">
         <is>
-          <t>F_ESTER</t>
+          <t>F_N4PYCJQX</t>
         </is>
       </c>
       <c r="D451" s="3" t="inlineStr">
@@ -32036,7 +32036,7 @@
       </c>
       <c r="C452" s="3" t="inlineStr">
         <is>
-          <t>F_ACTIVE_METHYLENE</t>
+          <t>F_EJHA2TYP</t>
         </is>
       </c>
       <c r="D452" s="3" t="inlineStr">
@@ -32068,7 +32068,7 @@
       </c>
       <c r="C453" s="3" t="inlineStr">
         <is>
-          <t>F_ALKENE</t>
+          <t>F_43XPC2LW</t>
         </is>
       </c>
       <c r="D453" s="3" t="inlineStr">
@@ -32100,7 +32100,7 @@
       </c>
       <c r="C454" s="3" t="inlineStr">
         <is>
-          <t>F_ALKENE_TERMINAL</t>
+          <t>F_674FQ44T</t>
         </is>
       </c>
       <c r="D454" s="3" t="inlineStr">
@@ -32132,7 +32132,7 @@
       </c>
       <c r="C455" s="3" t="inlineStr">
         <is>
-          <t>F_KETONE</t>
+          <t>F_CFJ46WPI</t>
         </is>
       </c>
       <c r="D455" s="3" t="inlineStr">
@@ -32164,7 +32164,7 @@
       </c>
       <c r="C456" s="3" t="inlineStr">
         <is>
-          <t>F_ENONE</t>
+          <t>F_QTJCKBIJ</t>
         </is>
       </c>
       <c r="D456" s="3" t="inlineStr">
@@ -32196,7 +32196,7 @@
       </c>
       <c r="C457" s="3" t="inlineStr">
         <is>
-          <t>F_ENOLISABLE_CH</t>
+          <t>F_5T3LDTFX</t>
         </is>
       </c>
       <c r="D457" s="3" t="inlineStr">
@@ -32228,7 +32228,7 @@
       </c>
       <c r="C458" s="3" t="inlineStr">
         <is>
-          <t>F_ESTER</t>
+          <t>F_N4PYCJQX</t>
         </is>
       </c>
       <c r="D458" s="3" t="inlineStr">
@@ -32260,7 +32260,7 @@
       </c>
       <c r="C459" s="3" t="inlineStr">
         <is>
-          <t>F_ESTER</t>
+          <t>F_N4PYCJQX</t>
         </is>
       </c>
       <c r="D459" s="3" t="inlineStr">
@@ -32292,7 +32292,7 @@
       </c>
       <c r="C460" s="3" t="inlineStr">
         <is>
-          <t>F_KETONE</t>
+          <t>F_CFJ46WPI</t>
         </is>
       </c>
       <c r="D460" s="3" t="inlineStr">
@@ -32324,7 +32324,7 @@
       </c>
       <c r="C461" s="3" t="inlineStr">
         <is>
-          <t>F_ENOLISABLE_CH</t>
+          <t>F_5T3LDTFX</t>
         </is>
       </c>
       <c r="D461" s="3" t="inlineStr">
@@ -32356,7 +32356,7 @@
       </c>
       <c r="C462" s="3" t="inlineStr">
         <is>
-          <t>F_ENOLISABLE_CH</t>
+          <t>F_5T3LDTFX</t>
         </is>
       </c>
       <c r="D462" s="3" t="inlineStr">
@@ -32388,7 +32388,7 @@
       </c>
       <c r="C463" s="3" t="inlineStr">
         <is>
-          <t>F_ESTER</t>
+          <t>F_N4PYCJQX</t>
         </is>
       </c>
       <c r="D463" s="3" t="inlineStr">
@@ -32420,7 +32420,7 @@
       </c>
       <c r="C464" s="3" t="inlineStr">
         <is>
-          <t>F_KETONE</t>
+          <t>F_CFJ46WPI</t>
         </is>
       </c>
       <c r="D464" s="3" t="inlineStr">
@@ -32452,7 +32452,7 @@
       </c>
       <c r="C465" s="3" t="inlineStr">
         <is>
-          <t>F_ENOLISABLE_CH</t>
+          <t>F_5T3LDTFX</t>
         </is>
       </c>
       <c r="D465" s="3" t="inlineStr">
@@ -32484,7 +32484,7 @@
       </c>
       <c r="C466" s="3" t="inlineStr">
         <is>
-          <t>F_ACTIVE_METHYLENE</t>
+          <t>F_EJHA2TYP</t>
         </is>
       </c>
       <c r="D466" s="3" t="inlineStr">
@@ -32516,7 +32516,7 @@
       </c>
       <c r="C467" s="3" t="inlineStr">
         <is>
-          <t>F_HYDROXIDE_ALKOXIDE</t>
+          <t>F_BLUS3XKO</t>
         </is>
       </c>
       <c r="D467" s="3" t="inlineStr">
@@ -32548,7 +32548,7 @@
       </c>
       <c r="C468" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_IODIDE</t>
+          <t>F_OM2L6LN4</t>
         </is>
       </c>
       <c r="D468" s="3" t="inlineStr">
@@ -32580,7 +32580,7 @@
       </c>
       <c r="C469" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_IODIDE</t>
+          <t>F_OM2L6LN4</t>
         </is>
       </c>
       <c r="D469" s="3" t="inlineStr">
@@ -32612,7 +32612,7 @@
       </c>
       <c r="C470" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_IODIDE</t>
+          <t>F_OM2L6LN4</t>
         </is>
       </c>
       <c r="D470" s="3" t="inlineStr">
@@ -32644,7 +32644,7 @@
       </c>
       <c r="C471" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_BROMIDE</t>
+          <t>F_EDNDOOMT</t>
         </is>
       </c>
       <c r="D471" s="3" t="inlineStr">
@@ -32676,7 +32676,7 @@
       </c>
       <c r="C472" s="3" t="inlineStr">
         <is>
-          <t>F_KETONE</t>
+          <t>F_CFJ46WPI</t>
         </is>
       </c>
       <c r="D472" s="3" t="inlineStr">
@@ -32708,7 +32708,7 @@
       </c>
       <c r="C473" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_HALIDE_2</t>
+          <t>F_4KF4VNAH</t>
         </is>
       </c>
       <c r="D473" s="3" t="inlineStr">
@@ -32740,7 +32740,7 @@
       </c>
       <c r="C474" s="3" t="inlineStr">
         <is>
-          <t>F_ENOLISABLE_CH</t>
+          <t>F_5T3LDTFX</t>
         </is>
       </c>
       <c r="D474" s="3" t="inlineStr">
@@ -32772,7 +32772,7 @@
       </c>
       <c r="C475" s="3" t="inlineStr">
         <is>
-          <t>F_CARBOXYLIC_ACID</t>
+          <t>F_WH4T6PP5</t>
         </is>
       </c>
       <c r="D475" s="3" t="inlineStr">
@@ -32804,7 +32804,7 @@
       </c>
       <c r="C476" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_BROMIDE</t>
+          <t>F_EDNDOOMT</t>
         </is>
       </c>
       <c r="D476" s="3" t="inlineStr">
@@ -32836,7 +32836,7 @@
       </c>
       <c r="C477" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_HALIDE_2</t>
+          <t>F_4KF4VNAH</t>
         </is>
       </c>
       <c r="D477" s="3" t="inlineStr">
@@ -32868,7 +32868,7 @@
       </c>
       <c r="C478" s="3" t="inlineStr">
         <is>
-          <t>F_HYDROXIDE_ALKOXIDE</t>
+          <t>F_BLUS3XKO</t>
         </is>
       </c>
       <c r="D478" s="3" t="inlineStr">
@@ -32900,7 +32900,7 @@
       </c>
       <c r="C479" s="3" t="inlineStr">
         <is>
-          <t>F_ACYL_CHLORIDE</t>
+          <t>F_7W5VQUT2</t>
         </is>
       </c>
       <c r="D479" s="3" t="inlineStr">
@@ -32932,7 +32932,7 @@
       </c>
       <c r="C480" s="3" t="inlineStr">
         <is>
-          <t>F_ACYL_CHLORIDE</t>
+          <t>F_7W5VQUT2</t>
         </is>
       </c>
       <c r="D480" s="3" t="inlineStr">
@@ -32964,7 +32964,7 @@
       </c>
       <c r="C481" s="3" t="inlineStr">
         <is>
-          <t>F_SULFONE_SULFOXIDE</t>
+          <t>F_66D4FM65</t>
         </is>
       </c>
       <c r="D481" s="3" t="inlineStr">
@@ -32996,7 +32996,7 @@
       </c>
       <c r="C482" s="3" t="inlineStr">
         <is>
-          <t>F_THIOETHER</t>
+          <t>F_WUYH6XV3</t>
         </is>
       </c>
       <c r="D482" s="3" t="inlineStr">
@@ -33028,7 +33028,7 @@
       </c>
       <c r="C483" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_SP3</t>
+          <t>F_CQJBM3VA</t>
         </is>
       </c>
       <c r="D483" s="3" t="inlineStr">
@@ -33060,7 +33060,7 @@
       </c>
       <c r="C484" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_SP3</t>
+          <t>F_CQJBM3VA</t>
         </is>
       </c>
       <c r="D484" s="3" t="inlineStr">
@@ -33092,7 +33092,7 @@
       </c>
       <c r="C485" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_3</t>
+          <t>F_Z6ABGO4G</t>
         </is>
       </c>
       <c r="D485" s="3" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="C486" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_3</t>
+          <t>F_Z6ABGO4G</t>
         </is>
       </c>
       <c r="D486" s="3" t="inlineStr">
@@ -33156,7 +33156,7 @@
       </c>
       <c r="C487" s="3" t="inlineStr">
         <is>
-          <t>F_DIOL_1_2</t>
+          <t>F_VHRSWB64</t>
         </is>
       </c>
       <c r="D487" s="3" t="inlineStr">
@@ -33188,7 +33188,7 @@
       </c>
       <c r="C488" s="3" t="inlineStr">
         <is>
-          <t>F_KETONE</t>
+          <t>F_CFJ46WPI</t>
         </is>
       </c>
       <c r="D488" s="3" t="inlineStr">
@@ -33220,7 +33220,7 @@
       </c>
       <c r="C489" s="3" t="inlineStr">
         <is>
-          <t>F_ENOLISABLE_CH</t>
+          <t>F_5T3LDTFX</t>
         </is>
       </c>
       <c r="D489" s="3" t="inlineStr">
@@ -33252,7 +33252,7 @@
       </c>
       <c r="C490" s="3" t="inlineStr">
         <is>
-          <t>F_IMINE</t>
+          <t>F_LPMNZ3FU</t>
         </is>
       </c>
       <c r="D490" s="3" t="inlineStr">
@@ -33284,7 +33284,7 @@
       </c>
       <c r="C491" s="3" t="inlineStr">
         <is>
-          <t>F_OXIME</t>
+          <t>F_KKIIQEFP</t>
         </is>
       </c>
       <c r="D491" s="3" t="inlineStr">
@@ -33316,7 +33316,7 @@
       </c>
       <c r="C492" s="3" t="inlineStr">
         <is>
-          <t>F_AMIDE</t>
+          <t>F_F3X5X5PO</t>
         </is>
       </c>
       <c r="D492" s="3" t="inlineStr">
@@ -33348,7 +33348,7 @@
       </c>
       <c r="C493" s="3" t="inlineStr">
         <is>
-          <t>F_AMIDE_NH</t>
+          <t>F_ZTFQ2FCA</t>
         </is>
       </c>
       <c r="D493" s="3" t="inlineStr">
@@ -33380,7 +33380,7 @@
       </c>
       <c r="C494" s="3" t="inlineStr">
         <is>
-          <t>F_HYDROXYLAMINE</t>
+          <t>F_IV5D5PBX</t>
         </is>
       </c>
       <c r="D494" s="3" t="inlineStr">
@@ -33412,7 +33412,7 @@
       </c>
       <c r="C495" s="3" t="inlineStr">
         <is>
-          <t>F_NITRILE</t>
+          <t>F_OWKLY6DL</t>
         </is>
       </c>
       <c r="D495" s="3" t="inlineStr">
@@ -33444,7 +33444,7 @@
       </c>
       <c r="C496" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_SP3</t>
+          <t>F_CQJBM3VA</t>
         </is>
       </c>
       <c r="D496" s="3" t="inlineStr">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="C497" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_3</t>
+          <t>F_Z6ABGO4G</t>
         </is>
       </c>
       <c r="D497" s="3" t="inlineStr">
@@ -33508,7 +33508,7 @@
       </c>
       <c r="C498" s="3" t="inlineStr">
         <is>
-          <t>F_NITRILE</t>
+          <t>F_OWKLY6DL</t>
         </is>
       </c>
       <c r="D498" s="3" t="inlineStr">
@@ -33540,7 +33540,7 @@
       </c>
       <c r="C499" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D499" s="3" t="inlineStr">
@@ -33572,7 +33572,7 @@
       </c>
       <c r="C500" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D500" s="3" t="inlineStr">
@@ -33604,7 +33604,7 @@
       </c>
       <c r="C501" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D501" s="3" t="inlineStr">
@@ -33636,7 +33636,7 @@
       </c>
       <c r="C502" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D502" s="3" t="inlineStr">
@@ -33668,7 +33668,7 @@
       </c>
       <c r="C503" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D503" s="3" t="inlineStr">
@@ -33700,7 +33700,7 @@
       </c>
       <c r="C504" s="3" t="inlineStr">
         <is>
-          <t>F_AMIDE</t>
+          <t>F_F3X5X5PO</t>
         </is>
       </c>
       <c r="D504" s="3" t="inlineStr">
@@ -33732,7 +33732,7 @@
       </c>
       <c r="C505" s="3" t="inlineStr">
         <is>
-          <t>F_AMIDE_NH</t>
+          <t>F_ZTFQ2FCA</t>
         </is>
       </c>
       <c r="D505" s="3" t="inlineStr">
@@ -33764,7 +33764,7 @@
       </c>
       <c r="C506" s="3" t="inlineStr">
         <is>
-          <t>F_AMIDE</t>
+          <t>F_F3X5X5PO</t>
         </is>
       </c>
       <c r="D506" s="3" t="inlineStr">
@@ -33796,7 +33796,7 @@
       </c>
       <c r="C507" s="3" t="inlineStr">
         <is>
-          <t>F_AMIDE</t>
+          <t>F_F3X5X5PO</t>
         </is>
       </c>
       <c r="D507" s="3" t="inlineStr">
@@ -33828,7 +33828,7 @@
       </c>
       <c r="C508" s="3" t="inlineStr">
         <is>
-          <t>F_AMIDE_NH</t>
+          <t>F_ZTFQ2FCA</t>
         </is>
       </c>
       <c r="D508" s="3" t="inlineStr">
@@ -33860,7 +33860,7 @@
       </c>
       <c r="C509" s="3" t="inlineStr">
         <is>
-          <t>F_AMIDE_NH</t>
+          <t>F_ZTFQ2FCA</t>
         </is>
       </c>
       <c r="D509" s="3" t="inlineStr">
@@ -33892,7 +33892,7 @@
       </c>
       <c r="C510" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_IODIDE</t>
+          <t>F_OM2L6LN4</t>
         </is>
       </c>
       <c r="D510" s="3" t="inlineStr">
@@ -33924,7 +33924,7 @@
       </c>
       <c r="C511" s="3" t="inlineStr">
         <is>
-          <t>F_METHYL_HALIDE</t>
+          <t>F_KNBZHWVH</t>
         </is>
       </c>
       <c r="D511" s="3" t="inlineStr">
@@ -33956,7 +33956,7 @@
       </c>
       <c r="C512" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D512" s="3" t="inlineStr">
@@ -33988,7 +33988,7 @@
       </c>
       <c r="C513" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D513" s="3" t="inlineStr">
@@ -34020,7 +34020,7 @@
       </c>
       <c r="C514" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D514" s="3" t="inlineStr">
@@ -34052,7 +34052,7 @@
       </c>
       <c r="C515" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D515" s="3" t="inlineStr">
@@ -34084,7 +34084,7 @@
       </c>
       <c r="C516" s="3" t="inlineStr">
         <is>
-          <t>F_ARENE_CH</t>
+          <t>F_7GV2Y2WW</t>
         </is>
       </c>
       <c r="D516" s="3" t="inlineStr">
@@ -34116,7 +34116,7 @@
       </c>
       <c r="C517" s="3" t="inlineStr">
         <is>
-          <t>F_ARYL_ALKYL_ETHER</t>
+          <t>F_UHD3N3ZP</t>
         </is>
       </c>
       <c r="D517" s="3" t="inlineStr">
@@ -34148,7 +34148,7 @@
       </c>
       <c r="C518" s="3" t="inlineStr">
         <is>
-          <t>F_EPOXIDE</t>
+          <t>F_GUG35WZM</t>
         </is>
       </c>
       <c r="D518" s="3" t="inlineStr">
@@ -34180,7 +34180,7 @@
       </c>
       <c r="C519" s="3" t="inlineStr">
         <is>
-          <t>F_HYDROXIDE_ALKOXIDE</t>
+          <t>F_BLUS3XKO</t>
         </is>
       </c>
       <c r="D519" s="3" t="inlineStr">
@@ -34212,7 +34212,7 @@
       </c>
       <c r="C520" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_SP3</t>
+          <t>F_CQJBM3VA</t>
         </is>
       </c>
       <c r="D520" s="3" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="C521" s="3" t="inlineStr">
         <is>
-          <t>F_ALCOHOL_2</t>
+          <t>F_JIOCZMVT</t>
         </is>
       </c>
       <c r="D521" s="3" t="inlineStr">
@@ -34276,7 +34276,7 @@
       </c>
       <c r="C522" s="3" t="inlineStr">
         <is>
-          <t>F_ETHER_DIALKYL</t>
+          <t>F_GWWY5MAP</t>
         </is>
       </c>
       <c r="D522" s="3" t="inlineStr">
@@ -34308,7 +34308,7 @@
       </c>
       <c r="C523" s="3" t="inlineStr">
         <is>
-          <t>F_PEROXIDE</t>
+          <t>F_NBVC3ZK3</t>
         </is>
       </c>
       <c r="D523" s="3" t="inlineStr">
@@ -34340,7 +34340,7 @@
       </c>
       <c r="C524" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_BROMIDE</t>
+          <t>F_EDNDOOMT</t>
         </is>
       </c>
       <c r="D524" s="3" t="inlineStr">
@@ -34372,7 +34372,7 @@
       </c>
       <c r="C525" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_BROMIDE</t>
+          <t>F_EDNDOOMT</t>
         </is>
       </c>
       <c r="D525" s="3" t="inlineStr">
@@ -34404,7 +34404,7 @@
       </c>
       <c r="C526" s="3" t="inlineStr">
         <is>
-          <t>F_VICINAL_DIBROMIDE</t>
+          <t>F_D6B2Q4UF</t>
         </is>
       </c>
       <c r="D526" s="3" t="inlineStr">
@@ -34436,7 +34436,7 @@
       </c>
       <c r="C527" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_HALIDE_2</t>
+          <t>F_4KF4VNAH</t>
         </is>
       </c>
       <c r="D527" s="3" t="inlineStr">
@@ -34468,7 +34468,7 @@
       </c>
       <c r="C528" s="3" t="inlineStr">
         <is>
-          <t>F_ALKYL_HALIDE_2</t>
+          <t>F_4KF4VNAH</t>
         </is>
       </c>
       <c r="D528" s="3" t="inlineStr">
@@ -34522,7 +34522,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Fragments: one row per fragment. The SMARTS column is the pattern that finds it; 'Reactive atom(s)' and 'Role' say where and how it reacts; pKa and leaving-group columns say how acidic, how basic, and what can leave. Fragment ID rule: every structurally distinct SMARTS pattern gets its own ID, and no two fragments share a pattern or an ID. An ID is F_ followed by a descriptive name in capitals, e.g. F_ALDEHYDE, F_ALKYL_HALIDE_2 (the old F001–F103 numbers are listed in tools/data/fragment_ids.json). tools/run_all_checks.py enforces this.</t>
+          <t>Fragments: one row per fragment. The SMARTS column is the pattern that finds it; 'Reactive atom(s)' and 'Role' say where and how it reacts; pKa and leaving-group columns say how acidic, how basic, and what can leave. Fragment ID rule: the ID is generated from the SMARTS pattern (F_ + 8 characters of its SHA-1 hash, see tools/fragment_id.py); never type one by hand. Give the fragment a readable Fragment name instead. The same pattern always gives the same ID, so two fragments with one pattern are rejected. If you edit a SMARTS, run python tools/fragment_id.py --fix to re-ID it everywhere. The old F001–F103 numbers are in tools/data/fragment_ids.json.</t>
         </is>
       </c>
     </row>

--- a/molecule_data.xlsx
+++ b/molecule_data.xlsx
@@ -11269,7 +11269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N104"/>
+  <dimension ref="A1:N206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -17565,6 +17565,6502 @@
       <c r="N104" s="3" t="inlineStr">
         <is>
           <t>TMSBr is chemoselective: amides, esters and Boc usually survive. NaI or LiBr removes only one alkyl group, because the resulting P–O⁻ no longer activates the other. Covers phosphonates RP(O)(OR′)2, phosphinates and phosphate triesters such as ArOP(O)(OtBu)2 [learned from the recorded reactions of templates T000816, T001990, T002434, T003474, T004327, T004699…; RDKit: consumed (count drops from starting materials to product) in 56 of 56 example reactions of the templates it covers; found in 0.4% of 20,000 recorded products]</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>F104</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>thiophene / benzothiophene ring C–H</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>[cH;$(c1:c:c:c:s:1),$(c1:c:c:s:c:1)]</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>the ring C–H (C2/C5 first, then C3/C4)</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>nucleophile: electrophilic aromatic substitution, much faster than on benzene and at C2/C5 (NBS or Br2 bromination, Vilsmeier–Haack formylation POCl3/DMF, Friedel–Crafts acylation with SnCl4 or TiCl4, nitration with Ac2O/HNO3). C2–H is lithiated by n-BuLi (THF, −78 °C → 0 °C) and trapped with DMF, I2, R3SiCl or B(OR)3; direct Pd-catalysed C–H arylation (Pd(OAc)2, PivOH, K2CO3)</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>ring C–H ≈ 33 (C2–H, DMSO estimate); not a useful acid without a strong base</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="n"/>
+      <c r="H105" s="3" t="n"/>
+      <c r="I105" s="3" t="n"/>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>C2/C5 are open; a 2-substituent sends electrophiles to C5, and C3 reacts only when both α positions are blocked or by directed lithiation</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
+          <t>Covers thiophene, benzothiophene and thienopyridines. The ring C–H a generic arene C–H (F009) cannot tell apart from a benzene C–H. [learned from the recorded reactions: found in 2.2% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 8% of those (126 of 1,532); 69 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>F105</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>furan / benzofuran ring C–H</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>[cH;$(c1:c:c:c:o:1),$(c1:c:c:o:c:1)]</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>the ring C–H (C2/C5 first)</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>nucleophile: electrophilic substitution (Vilsmeier–Haack formylation, mild halogenation NBS/DMF, Friedel–Crafts acylation with mild Lewis acids BF3·OEt2) at C2/C5; lithiated at C2 by n-BuLi. The ring is a diene (Diels–Alder with maleimides) and opens in strong aqueous acid</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>ring C–H ≈ 35 (C2–H, estimate)</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="n"/>
+      <c r="H106" s="3" t="n"/>
+      <c r="I106" s="3" t="n"/>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>C2/C5 are open; avoid strong aqueous acid, which opens the ring to a 1,4-dicarbonyl</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
+          <t>Covers furan and benzofuran. More acid-sensitive than thiophene. [learned from the recorded reactions: found in 0.9% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 9% of those (58 of 659); 43 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>F106</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>pyrrole / indole ring C–H</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>[cH;$(c1:c:c:c:[nX3]:1),$(c1:c:c:[nX3]:c:1)]</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>the ring C–H (C2 of pyrrole, C3 of indole)</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>nucleophile: the most reactive common arene toward electrophiles: Vilsmeier–Haack formylation (POCl3/DMF) , Mannich (CH2O + R2NH, AcOH), halogenation (NBS or NIS, 0 °C, DMF), Friedel–Crafts acylation with Et2AlCl or acid chlorides, azo coupling, Michael addition to enones (indole C3, Lewis acid). Strong acid polymerises pyrrole; an N-sulfonyl or N-Boc group tames it</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>ring C–H ≈ 39 (estimate)</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>protonates on carbon: ≈ −3.8 (pyrrole) / −3.6 (indole)</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="n"/>
+      <c r="I107" s="3" t="n"/>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>indole C3 is open; a 3-substituent sends electrophiles to C2, 2,3-disubstituted indoles to C6 or N</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
+          <t>Covers N–H and N-substituted pyrroles and indoles. Reactions at the ring N–H are in F089 and the pyrrole N–H fragments. [learned from the recorded reactions: found in 3.4% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 11% of those (256 of 2,396); 194 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>F107</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>azole C–H between two ring heteroatoms (imidazole C2–H, thiazole C2–H, oxazole C2–H)</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>[cH;r5;$(c(:[n,o,s]):[n,o,s])]</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>the ring C–H between the two heteroatoms (C2)</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>the most acidic ring C–H of an azole: lithiated at C2 by n-BuLi or LDA (THF, −78 °C) and trapped (DMF, I2, R3SiCl, ZnCl2 then Negishi); direct Pd/Cu C–H arylation (Pd(OAc)2, CuI, Cs2CO3, PivOH); N-heterocyclic carbene precursor after N-alkylation at N3 (imidazolium C2–H ≈ 21 in DMSO); electrophilic substitution is slow here (it goes to C4/C5)</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>≈ 30 (C2–H of 1-methylimidazole and thiazole, DMSO estimates); imidazolium C2–H ≈ 21 (DMSO)</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="n"/>
+      <c r="H108" s="3" t="n"/>
+      <c r="I108" s="3" t="n"/>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>open unless C4/C5 carry large groups</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
+          <t>Covers imidazole, benzimidazole, thiazole, benzothiazole, oxazole and benzoxazole C2–H, and 1,2,4-triazole C–H. [learned from the recorded reactions: found in 2.2% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 16% of those (255 of 1,560); 198 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>F108</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>azine ring C–H (pyridine, pyrimidine, quinoline: the ring that carries the N)</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>[cH;r6;$(c1:n:*:*:*:*:1),$(c1:*:n:*:*:*:1),$(c1:*:*:n:*:*:1)]</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>the ring C–H (C2/C4/C6 attacked by nucleophiles and radicals, C3/C5 by electrophiles)</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>an electron-poor ring: electrophilic substitution needs forcing conditions and goes to C3/C5 (nitration, halogenation at 150–300 °C), while radicals attack C2/C4 (Minisci: R• from RCO2H/AgNO3/(NH4)2S2O8 or alkyl halides, in acid) and organolithiums add at C2 (Chichibabin: NaNH2 gives the 2-amine). Deprotonated ortho to a directing group with LDA, LiTMP or TMPMgCl·LiCl; the N-oxide opens C2 to POCl3 (2-chloropyridine) and Pd C–H arylation</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>ring C–H ≈ 40 (estimate)</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="n"/>
+      <c r="H109" s="3" t="n"/>
+      <c r="I109" s="3" t="n"/>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>positions next to the ring N or a substituent are crowded</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
+          <t>Covers pyridine, pyrimidine, pyrazine, pyridazine, quinoline and isoquinoline ring C–H (the ring that carries the N). Benzo-ring C–H of quinoline is an ordinary arene C–H (F009). [learned from the recorded reactions: found in 20.4% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 6% of those (846 of 14,402); 382 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>F109</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>pyrazole / indazole N–H (N–H next to another ring N)</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>[nH;r5;$([nH]:n)]</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>the ring N–H (after deprotonation, N1 or N2)</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>N–H acid, then N-nucleophile: N-alkylation (R–X or R–OMs with K2CO3/Cs2CO3 in DMF or MeCN, or NaH in THF/DMF), Mitsunobu, Michael addition to acrylates, N-arylation (Chan–Lam Cu(OAc)2/ArB(OH)2/air; Ullmann CuI/diamine/K3PO4; SNAr on activated ArF), N-protection (SEM-Cl, THP by DHP/TsOH, Boc2O, trityl, PMB-Cl). Unsymmetrical pyrazoles and indazoles give N1/N2 mixtures</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>pyrazole 14.2 (19.8 in DMSO); indazole 13.9; 1,2,3-triazole 9.3; 4-nitropyrazole 9.6</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>pyrazole 2.5; indazole 1.3 (the ring N lone pair)</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>none here (the azolide is a good leaving group in N-acyl and N-sulfonyl azoles)</t>
+        </is>
+      </c>
+      <c r="I110" s="3" t="n"/>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>alkylation goes mostly to the N next to the smaller neighbour (the less hindered N); a 3-substituent on pyrazole favours N1 alkylation, indazole N1 (thermodynamic, NaH/THF) vs N2 (kinetic, Mitsunobu, acidic alkylation)</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
+          <t>N–H next to another ring N. A narrower split of F089. [learned from the recorded reactions: found in 1.5% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 36% of those (368 of 1,027); 307 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>F110</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>imidazole / benzimidazole / purine / azaindole N–H (N–H next to a C=N)</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>[nH;r5;$([nH]:c:[nX2])]</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>the ring N–H (after deprotonation, either N)</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>N–H acid, then N-nucleophile: N-alkylation (R–X, K2CO3 or Cs2CO3 in DMF/MeCN or NaH), N-arylation (Ullmann CuI/ligand, Buchwald Pd, SNAr), N-acylation and N-sulfonylation (gives the activated azolides used as acyl transfer agents: CDI, N-acylbenzotriazoles), N-protection (trityl, SEM, Boc). Unsymmetrical imidazoles and benzimidazoles give N1/N3 mixtures</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>imidazole 14.5; benzimidazole 12.8; purine 8.9; 7-azaindole ≈ 15</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>imidazole 7.0; benzimidazole 5.5; 7-azaindole 4.6 (the pyridine-type N)</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>none here (the azolide is a good leaving group in N-acyl azoles)</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="n"/>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>alkylation of an unsymmetrical imidazole goes mostly to the N far from the bulkier substituent (and the more basic N under neutral conditions)</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
+          <t>N–H next to a C=N: imidazole, benzimidazole, purine, azaindole, 1,2,4-triazole. A narrower split of F089. [learned from the recorded reactions: found in 1.8% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 25% of those (313 of 1,264); 268 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>F111</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>pyrrole / indole / carbazole N–H (no second ring N next to it)</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>[nH;r5;!$([nH]:n);!$([nH]:c:[nX2])]</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>the ring N–H (after deprotonation)</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>weaker N–H acid than the azoles, so it needs a stronger base: NaH or KOtBu or KOH/DMSO or Cs2CO3 (heated) for N-alkylation, N-sulfonylation (ArSO2Cl/NaH or Bu4NHSO4/NaOH), N-acylation, N-Boc (Boc2O/DMAP), N-arylation (Ullmann, Buchwald, Chan–Lam). Under neutral or acidic conditions the C-nucleophilic positions react instead (indole C3)</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>pyrrole 17.5 (23 in DMSO); indole 16.2 (21 in DMSO); carbazole ≈ 20 (DMSO)</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>protonates on carbon: ≈ −3.8 (pyrrole) / −3.6 (indole), not a base</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="n"/>
+      <c r="I112" s="3" t="n"/>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>groups at C2 (pyrrole) or C2/C7 (indole) slow N-alkylation and N-arylation</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
+          <t>N–H with no second ring N next to it: pyrrole, indole, carbazole. A narrower split of F089. [learned from the recorded reactions: found in 2.1% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 26% of those (386 of 1,467); 333 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>F112</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>imidazole-type ring N (sp2 N of imidazole, benzimidazole, purine: next to a C bonded to the substituted ring N)</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>[nX2;r5;+0;$([nX2]:c:[nX3;r5])]</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>the ring N lone pair (sp2, in the ring plane)</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>base and nucleophile: N-alkylation to imidazolium salts (R–X in MeCN, heated), N-acylation (the intermediate of CDI and DMAP-type catalysis), metal ligand (Zn, Cu, Fe, Pd), and the proton acceptor in general base catalysis; the less hindered N of an unsymmetrical imidazole is alkylated</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>imidazole 7.0; benzimidazole 5.5; purine N 2.4; 1-methylimidazole 7.1</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="n"/>
+      <c r="I113" s="3" t="n"/>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>a substituent at C2 or C4/C5 next to the N slows alkylation</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
+          <t>sp2 N of imidazole, benzimidazole and purine (next to a C that carries the substituted ring N). A narrower view of what F091 does for 6-ring azines. [learned from the recorded reactions: found in 5.4% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 9% of those (352 of 3,787); 221 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>F113</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>other azole ring N (sp2 N of pyrazole, thiazole, oxazole, triazole, tetrazole)</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>[nX2;r5;+0;!$([nX2]:c:[nX3;r5])]</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>the ring N lone pair (sp2, in the ring plane)</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>weak base and nucleophile, metal ligand: N-alkylation (R–X, Me3O⁺ BF4⁻), N-oxidation is rare, coordination to Pd/Cu directs C–H activation next to it; protonation at this N activates C2 of thiazole/oxazole to nucleophiles; the ring N of a 2-substituted thiazole or oxazole is not alkylated easily</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>pyrazole 2.5; thiazole 2.5; 1,2,4-triazole 2.2; 1,2,3-triazole 1.2; oxazole 0.8; tetrazole ≈ −3</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="n"/>
+      <c r="I114" s="3" t="n"/>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>substituents at the carbons next to the N slow alkylation and metal binding</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
+          <t>sp2 N of pyrazole, thiazole, oxazole, triazole and tetrazole rings. [learned from the recorded reactions: found in 10.4% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 8% of those (571 of 7,347); 316 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>F114</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>tetrazole (N–H acid, pKa ≈ 5: carboxylic-acid isostere)</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>c1nnnn1</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>the ring N–H (acid) and the ring N atoms (alkylation)</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>carboxylic-acid isostere: the N–H is as acidic as a carboxylic acid. Made from a nitrile and NaN3 (NH4Cl or ZnBr2 or Et3N·HCl, DMF or water, 100–130 °C) by [3+2]; alkylation gives N1/N2 mixtures (N2 favoured for bulky electrophiles), protected as N-trityl, N-PMB or N-cyanoethyl; stable to most reagents (not to strong reducing conditions)</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>tetrazole N–H 4.9 (5-aryltetrazoles ≈ 4.5)</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>≈ −3 (very weak base)</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="n"/>
+      <c r="I115" s="3" t="n"/>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>alkylation at N1 is hindered by a 5-substituent, so N2 products dominate for 5-aryl tetrazoles</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
+          <t>The aromatic 1,2,3,4-tetrazole ring. [learned from the recorded reactions: found in 0.4% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 22% of those (62 of 279); 44 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>F115</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>heteroaryl NH2 (2-aminopyridine, aminopyrimidine, aminothiazole: NH2 on a carbon next to a ring N)</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>[nX2]:c-[NX3;H2;+0]</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>the ring N (protonation, alkylation) and the NH2 N</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>a much weaker nucleophile than an aniline or alkylamine, because the NH2 lone pair is delocalised into the amidine-like N–C=N: amide coupling needs acid chlorides, HATU or T3P with heat or a stronger base (NaH, LiHMDS, pyridine/DMAP); Buchwald–Hartwig N-arylation (Pd2dba3, Xantphos or BINAP, Cs2CO3); diazotisation (NaNO2/HCl or t-BuONO/CuBr) to the halide; alkyl halides react on the ring N first</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>N–H ≈ 28 (2-aminopyridine, DMSO)</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>about 6.9 for 2-aminopyridine; 5.4 for 2-aminothiazole; 3.5 for 2-aminopyrimidine; 3.1 for 2-aminopyrazine (the ring N is the basic site)</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="n"/>
+      <c r="I116" s="3" t="n"/>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>a substituent next to the NH2 (position 3 of a 2-aminopyridine) slows acylation and arylation</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
+          <t>NH2 on a carbon next to a ring N (2-aminopyridine, aminopyrimidine, aminothiazole, aminopyrazine). The aniline NH2 (F026) reacts quite differently. [learned from the recorded reactions: found in 2.4% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 46% of those (789 of 1,711); 7 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>F116</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>aryl ketone (acetophenone, benzophenone: Ar–C(=O)–C)</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>c[CX3](=[OX1])[#6]</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>the carbonyl C (electrophile) and the α C–H</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>electrophile less reactive than a dialkyl ketone (conjugated): NaBH4 reduction (MeOH, 0 °C), Grignard/RLi addition, reductive amination (Ti(OiPr)4 then NaBH4), Wolff–Kishner (N2H4, KOH) or Et3SiH/TFA to the CH2, Baeyer–Villiger (the aryl group migrates less than a tertiary alkyl), α-bromination (CuBr2, Br2/AcOH, NBS/TsOH), Claisen–Schmidt aldol with ArCHO (NaOH/EtOH), Willgerodt; the enolate (LDA, LiHMDS) alkylates</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>α C–H 18.3 (acetophenone; 24.7 in DMSO)</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>≈ −6 (O-protonated ketone)</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="n"/>
+      <c r="I117" s="3" t="n"/>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>an ortho substituent twists the carbonyl out of conjugation and slows additions</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
+          <t>Ar–C(=O)–C: acetophenones, aryl ketones, benzophenones (diaryl). A narrower split of F019. [learned from the recorded reactions: found in 3.6% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 56% of those (1,447 of 2,563); 0 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>F117</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>aromatic aldehyde (ArCHO)</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>c[CX3H1]=[OX1]</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>the carbonyl C (electrophile)</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>electrophile with no α C–H (cannot enolise): reductive amination (NaBH(OAc)3 or NaBH3CN, AcOH, DCE/MeOH), Wittig and Horner–Wadsworth–Emmons olefination, Knoevenagel (malononitrile, piperidine), Claisen–Schmidt aldol with ketones, Henry (MeNO2), imine, oxime and hydrazone formation, reduction (NaBH4, 0 °C), oxidation to the acid (NaClO2/NaH2PO4 Pinnick; KMnO4), Cannizzaro in conc. NaOH, acetal formation (HC(OMe)3/TsOH)</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H (no α C–H)</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>≈ −7 (O-protonated aldehyde)</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="n"/>
+      <c r="I118" s="3" t="n"/>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>ortho substituents slow additions; electron-poor aldehydes (4-nitro, pyridine-carbaldehyde) are more reactive and hydrate</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
+          <t>Ar–CHO: benzaldehydes and heteroaryl aldehydes. A narrower split of F018. [learned from the recorded reactions: found in 2.7% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 81% of those (1,558 of 1,926); 0 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>F118</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>aromatic carboxylic acid (ArCO2H, ArCO2⁻)</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>c[CX3](=[OX1])[OX2H1,OX1-]</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>the carboxylic acid C (after activation) and the O–H</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>acylating agent after activation: amide coupling (HATU/DIPEA, EDC/HOBt, T3P, SOCl2 or (COCl)2/DMF to the acid chloride), esterification (MeOH/H2SO4, MeI/K2CO3, TMSCHN2), Curtius (DPPA, Et3N then t-BuOH or amine), reduction (BH3·THF, LiAlH4), Weinreb amide; salts (ArCO2⁻) direct ortho-lithiation (s-BuLi/TMEDA); decarboxylation needs ortho EWG or heat/Cu (quinoline, 200 °C)</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>benzoic acid 4.2; 4-nitro 3.4; 4-methoxy 4.5; nicotinic acid 4.8</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>≈ −7 (O-protonated acid)</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>OH is made a leaving group by activation (EDC, HATU, SOCl2); the carboxylate itself is not</t>
+        </is>
+      </c>
+      <c r="I119" s="3" t="n"/>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>ortho substituents slow coupling and esterification</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
+          <t>Ar–CO2H and Ar–CO2⁻. A narrower split of F001. [learned from the recorded reactions: found in 4.4% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 84% of those (2,604 of 3,091); 1 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>F119</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>α-amino acid / N-protected α-amino acid (N–CH–CO2H)</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>[NX3][CX4;H1,H2][CX3](=[OX1])[OX2H1,OX1-]</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>the amine N (nucleophile), the carboxylic acid C (after activation) and the α C–H (racemisation)</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>peptide building block: N-protection (Boc2O/NaOH or Et3N, Fmoc-OSu or Fmoc-Cl/NaHCO3, CbzCl/Na2CO3), amide coupling of the CO2H (EDC/HOBt, HATU/DIPEA, PyBOP, T3P), esterification (SOCl2/MeOH, TMSCl/MeOH), reduction to the amino alcohol (LiAlH4, BH3·SMe2). The α C–H racemises through the oxazolone or enolate with excess base or over-activation (use HOAt/Oxyma, collidine, 0 °C)</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>α-carboxylic acid ≈ 3.6 (N-acyl and N-carbamate amino acids; the free zwitterion 2.3)</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="n"/>
+      <c r="H120" s="3" t="n"/>
+      <c r="I120" s="3" t="n"/>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>α,α-disubstituted and N-methyl amino acids couple slowly (use HATU/HOAt, PyBrOP, acid fluorides)</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
+          <t>N–CH–CO2H, free or N-protected (Boc, Cbz, Fmoc, acetyl); includes proline. The amine of a free amino acid is also F002/F034 (its pKaH ≈ 9.6). [learned from the recorded reactions: found in 1.2% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 91% of those (746 of 817); 1 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>F120</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>primary amide (C(=O)NH2)</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>[#6][CX3](=[OX1])[NX3;H2]</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>the carbonyl C, the N–H and the N</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>dehydration to the nitrile (POCl3, SOCl2, TFAA/pyridine, Burgess reagent, cyanuric chloride), Hofmann rearrangement to the amine or carbamate (NaOBr, PIDA or PIFA, Br2/NaOMe), hydrolysis to the acid (6 M HCl heat, NaOH/H2O2), reduction to the amine (LiAlH4, BH3), N-arylation (Goldberg CuI/DMEDA, Buchwald), conversion to the N-acylsulfonamide</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>N–H ≈ 17 (25.5 in DMSO)</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>≈ −0.5 (O-protonated amide)</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="n"/>
+      <c r="I121" s="3" t="n"/>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
+          <t>C(=O)NH2 on carbon. A narrower split of F021 and F095. [learned from the recorded reactions: found in 1.2% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 40% of those (341 of 863); 5 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>F121</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>imide (phthalimide, succinimide, glutarimide: C(=O)–N–C(=O))</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>[CX3](=[OX1])[NX3;+0][CX3]=[OX1]</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>the carbonyl C (ring opening), the N–H (acid) and the N</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>N–H acid: the potassium salt of phthalimide alkylates with R–Br (K2CO3 or KOH, DMF) in the Gabriel synthesis, and the N-alkylphthalimide releases the primary amine with hydrazine hydrate (EtOH, reflux) or MeNH2 (Ing–Manske). Also Mitsunobu on the N–H, ring opening by NaOH/MeOH, NaBH4 reduction of one C=O to the hydroxylactam, N-bromosuccinimide and N-hydroxysuccinimide chemistry</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>phthalimide 8.3; succinimide 9.6; glutarimide 11.4</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>≈ −2 (O-protonated imide)</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>the imide N⁻ (pKa 8–10) leaves from acyl imides</t>
+        </is>
+      </c>
+      <c r="I122" s="3" t="n"/>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>open at the N–H; N-substituents slow the ring opening</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
+          <t>C(=O)–N–C(=O): phthalimide, succinimide, glutarimide, maleimide, hydantoin-type imides. A narrower split of F021 and F095. [learned from the recorded reactions: found in 1.7% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 62% of those (747 of 1,207); 0 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>F122</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>urea (N–C(=O)–N: ureas, carbamoyl-ureas)</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>[NX3;+0][CX3](=[OX1])[NX3;+0]</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>the N–H and the carbonyl C</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>formed from isocyanates and amines, or CDI/triphosgene/phosgene-equivalent and two amines; very stable to hydrolysis; N-alkylation of the N–H (NaH, R–X), cyclic ureas (imidazolidin-2-ones) from 1,2-diamines and CDI, intramolecular cyclisations to hydantoins and dihydrouracils; ureas are good H-bond donors (organocatalysis)</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>N–H ≈ 27 (urea, DMSO)</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>protonates on O, not on N</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="n"/>
+      <c r="I123" s="3" t="n"/>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>N,N-disubstituted ureas are twisted and unreactive</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
+          <t>N–C(=O)–N: ureas, cyclic ureas, carbamoyl ureas. Overlaps F021 and F095. [learned from the recorded reactions: found in 1.3% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 24% of those (217 of 920); 0 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>F123</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>hydroxamic acid / hydroxamate (C(=O)–N–OH, C(=O)–N–OR; Weinreb amide)</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>[CX3](=[OX1])[NX3][OX2]</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>the N–OH (acid) and the carbonyl C</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>metal chelator (HDAC and metalloprotease inhibitors). Made from an ester and NH2OH·HCl/KOH (MeOH), or an acid chloride/activated acid and O-protected hydroxylamine (THPONH2, BnONH2, TBSONH2) then deprotected (H2/Pd–C, TFA, TBAF). Lossen rearrangement of an O-activated hydroxamate gives the isocyanate; the Weinreb amide (N-methoxy-N-methyl) adds one RMgX/RLi to give a ketone, or DIBAL/LiAlH4 to give an aldehyde, without over-addition (chelated tetrahedral intermediate)</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>acetohydroxamic acid 9.4; benzohydroxamic acid 8.8 (the O–H)</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="n"/>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>the N–O⁻ after O-activation (Lossen); MeO(Me)N–H leaves from the Weinreb tetrahedral intermediate on work-up</t>
+        </is>
+      </c>
+      <c r="I124" s="3" t="n"/>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>N,N-disubstituted (Weinreb) amides are open at C=O</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L124" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
+          <t>C(=O)–N–OH and C(=O)–N–OR, including Weinreb amides and O-benzyl hydroxamates. [learned from the recorded reactions: found in 0.5% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 70% of those (257 of 365); 38 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>F124</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>activated ester (N-hydroxysuccinimide, HOBt/HOAt, pentafluorophenyl, p-nitrophenyl ester)</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>[CX3](=[OX1])[OX2]-[$([#7]),$(c1c(F)c(F)c(F)c(F)c1F),$(c1ccc([N+](=O)[O-])cc1)]</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>the carbonyl C</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>selective acylating agent: reacts with amines (and hydrazines) at rt in DMF, DMSO, CH2Cl2 or aqueous buffer (pH 7–9) to give amides, much more selectively than acid chlorides and without racemisation; stable enough to isolate (NHS, pentafluorophenyl, p-nitrophenyl esters). HOBt/HOAt esters are the intermediates inside EDC/HATU couplings. Made from the acid with NHS/EDC or DCC, HOBt/EDC, PFP-OH/EDC, or 4-nitrophenyl chloroformate</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>≈ −7 (O-protonated ester)</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>N-hydroxysuccinimide anion (HOSu pKa 6.0); HOBt 4.6; HOAt 3.3; pentafluorophenoxide 5.5; 4-nitrophenoxide 7.1</t>
+        </is>
+      </c>
+      <c r="I125" s="3" t="n"/>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>hindered amines (secondary, α,α-disubstituted) react slowly: heat or use HOAt/HATU</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
+          <t>C(=O)–O–N or C(=O)–O–Ar(EWG): N-hydroxysuccinimide, HOBt/HOAt, pentafluorophenyl and p-nitrophenyl esters. [learned from the recorded reactions: found in 0.2% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 93% of those (139 of 150); 7 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>F125</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>α-halo carbonyl (α-halo ketone, ester, amide)</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>[CX4;!$(C(F)(F))]([Cl,Br,I])[CX3]=[OX1]</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>the halogen-bearing α C (SN2) and the carbonyl C</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>a very reactive SN2 electrophile (the C=O stabilises the transition state): amines (K2CO3 or DIPEA, MeCN or DMF, 0 °C → rt), thiolates, azide, carboxylates (Cs2CO3/DMF) and phenoxides (K2CO3, acetone) displace the halide; Hantzsch thiazole synthesis with thioamides and thioureas (EtOH, reflux), imidazo[1,2-a]pyridines with 2-aminopyridines, Darzens (with aldehydes, base), Favorskii (α-halo ketone + alkoxide), Reformatsky (Zn); lachrymatory and toxic</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>the α C–H next to the halogen ≈ 16–17 (estimate)</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="n"/>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>I⁻ &gt; Br⁻ &gt; Cl⁻ (HI −10, HBr −9, HCl −7)</t>
+        </is>
+      </c>
+      <c r="I126" s="3" t="n"/>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>tertiary α-halo carbonyls (α-bromoisobutyrates) are hindered for SN2 but ionise and eliminate; secondary react more slowly</t>
+        </is>
+      </c>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L126" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
+          <t>X–C–C(=O): α-halo ketones (phenacyl bromide), esters (bromoacetate), amides (chloroacetamide). [learned from the recorded reactions: found in 1.5% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 97% of those (1,023 of 1,052); 0 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>F126</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>enol ether / vinyl ether (C=C–O–R; dihydropyran, dihydrofuran)</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>[CX3]=[CX3]-[OX2]-[#6;!$([#6]=O)]</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>the β C (nucleophile) and the acetal-forming α C</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>an electron-rich alkene and acid-labile: aqueous acid (HCl, TFA, PPTS/MeOH) hydrolyses it to the carbonyl and the alcohol; dihydropyran (DHP) protects alcohols as THP ethers (PPTS or TsOH cat.); also reacts with electrophiles at the β carbon (NBS/H2O to the α-bromo ketone, Vilsmeier, Mukaiyama aldol of silyl enol ethers), Diels–Alder (inverse demand), [2+2], Heck arylation with Pd, ozonolysis. Not covering enol esters (vinyl acetate) or silyl enol ethers</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>protonates on carbon: ≈ −2 (alkyl vinyl ether, estimate)</t>
+        </is>
+      </c>
+      <c r="H127" s="3" t="inlineStr">
+        <is>
+          <t>the alcohol R–OH leaves on hydrolysis</t>
+        </is>
+      </c>
+      <c r="I127" s="3" t="n"/>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L127" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
+          <t>C=C–O–R (not C=C–O–C=O): vinyl ethers, dihydropyran, dihydrofuran, glycals. [learned from the recorded reactions: found in 0.5% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 62% of those (215 of 348); 70 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>F127</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>enamine / enaminone (C=C–N, not an enamide)</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>[CX3]=[CX3]-[NX3;+0;!$(N-C=O);!$(N-S(=O)=O);!$(N-c)]</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>the β C (nucleophile) and the N</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>nucleophilic at carbon (Stork enamine alkylation, acylation and Michael addition) and hydrolysed by aqueous acid back to the carbonyl and amine; enaminones (β-aminoenones, from ketones with DMF-DMA or Bredereck reagent) are 1,3-bielectrophiles that close pyrazoles (hydrazines), isoxazoles (NH2OH), pyrimidines (amidines, guanidine) and pyridones; Vilsmeier–Haack reaction; reduced by NaBH3CN/AcOH to the amine</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>iminium after C-protonation ≈ 9–11 (alkyl enamines); enaminones ≈ 3</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>the amine R2NH leaves in condensations and hydrolysis</t>
+        </is>
+      </c>
+      <c r="I128" s="3" t="n"/>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>open; 2,2-disubstituted enamines are slower</t>
+        </is>
+      </c>
+      <c r="K128" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L128" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
+          <t>C=C–N where N is not an amide or sulfonamide or aniline: enamines, enaminones, DMF-DMA adducts. [learned from the recorded reactions: found in 0.4% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 67% of those (204 of 306); 15 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>F128</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>diazo compound (R2C=N2: diazomethane, TMS-diazomethane, diazoacetate)</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>[#6]=[N+]=[N-]</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>the diazo C</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>carbene or 1,3-dipole precursor: methyl esters of carboxylic acids and phenols (CH2N2 or TMSCHN2 in MeOH/benzene), Arndt–Eistert homologation (ArCOCl + CH2N2 → diazoketone → Wolff rearrangement, Ag2O/H2O), Rh2(OAc)4 or Cu-catalysed cyclopropanation and X–H insertion, 1,3-dipolar cycloaddition to alkenes and alkynes (pyrazolines, pyrazoles), Bamford–Stevens; toxic and explosive (diazomethane): TMS-diazomethane is the safer reagent</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>protonates on carbon: ≈ 10 (CH2N2 → CH3N2⁺, estimate)</t>
+        </is>
+      </c>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>N2 leaves (carbene or diazonium)</t>
+        </is>
+      </c>
+      <c r="I129" s="3" t="n"/>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L129" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
+          <t>R2C=N⁺=N⁻: diazomethane, TMS-diazomethane, ethyl diazoacetate, diazoketones. [learned from the recorded reactions: found in 0.1% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 100% of those (69 of 69); 0 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>F129</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>1,2-amino alcohol (free N–C–C–OH: ethanolamine, amino-alcohols)</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>[NX3;!$(N-C=O);!$(N-S(=O)=O)][CX4][CX4][OX2H1]</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>the amine N (nucleophile) and the O–H</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>N,O-bifunctional: the amine acylates, Boc-protects and sulfonylates before the alcohol (Boc2O, Et3N, 0 °C; CbzCl, NaHCO3); with CDI, triphosgene or diethyl carbonate/K2CO3 it closes the oxazolidin-2-one; with aldehydes/ketones the oxazolidine; with SOCl2 or Mitsunobu the aziridine; with DAST the fluoride; the alcohol oxidises (TEMPO/BAIB, Swern, DMP) once the N is protected. Made by reduction of amino acids (LiAlH4, BH3·SMe2, NaBH4/I2) and epoxide aminolysis</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>O–H ≈ 15.5 (alcohol)</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>ethanolamine 9.5 (the ammonium)</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>OH is made a leaving group by TsCl, MsCl, Mitsunobu</t>
+        </is>
+      </c>
+      <c r="I130" s="3" t="n"/>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>the amine is the more nucleophilic site, so selective N-acylation works even with an unprotected alcohol</t>
+        </is>
+      </c>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
+          <t>free N–C–C–OH (1,2-amino alcohol; also with N-alkyl, not an amide or carbamate N). [learned from the recorded reactions: found in 1.3% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 78% of those (690 of 887); 1 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>F130</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>benzyl group on O, N or S (benzyl ether, N-benzyl amine / amide, benzyl thioether)</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>c-[CH2;X4]-[OX2,NX3,SX2;!$([OX2]-C=O)]</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>the benzylic C–O / C–N / C–S bond (the CH2)</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>protecting group removed by hydrogenolysis (H2, 10% Pd/C or Pd(OH)2/C, MeOH/EtOH/EtOAc, 1 atm, rt; with AcOH or HCl for benzylamines; transfer: ammonium formate or cyclohexadiene), BCl3 or BBr3 (CH2Cl2, −78 °C, with pentamethylbenzene), Na/NH3, DDQ (slow for plain Bn), or ACE-Cl for N-benzyl amines. Put on with BnBr/NaH, BnBr/Ag2O (selective), or benzyl trichloroacetimidate/TfOH (base-sensitive)</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="n"/>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>the alkoxide, amide or thiolate leaves on hydrogenolysis (as the alcohol, amine or thiol)</t>
+        </is>
+      </c>
+      <c r="I131" s="3" t="n"/>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>hindered benzyl ethers hydrogenolyse more slowly; sulfur poisons Pd catalysts</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
+          <t>Ar–CH2–O, Ar–CH2–N, Ar–CH2–S (not benzyl esters, Cbz or benzyl halides). [learned from the recorded reactions: found in 9.6% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 37% of those (2,508 of 6,757); 54 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>F131</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>benzyl ester / benzyl carbamate (Cbz) / benzyl carbonate: Ar–CH2–O–C(=O)</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>c-[CH2;X4]-[OX2]-[CX3]=[OX1]</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>the benzylic C–O bond</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>Cbz carbamate and benzyl ester/carbonate: removed by hydrogenolysis (H2, Pd/C, rt, neutral, gives toluene + CO2 + the amine or acid), HBr/AcOH (33%), TMSI, BCl3, or Na/NH3; stable to TFA and to mild bases; the benzyl ester also saponifies (LiOH). Cbz is put on with CbzCl and Na2CO3 or NaHCO3 (Schotten–Baumann) or Cbz-OSu</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>≈ −6.5 (O-protonated ester)</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>the carboxylate or carbamate anion (leaves as CO2 + amine)</t>
+        </is>
+      </c>
+      <c r="I132" s="3" t="n"/>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="K132" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L132" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
+          <t>Ar–CH2–O–C(=O): benzyl esters, benzyl carbamates (Cbz, Z) and benzyl carbonates. [learned from the recorded reactions: found in 1.5% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 37% of those (388 of 1,043); 3 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>F132</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>4-methoxybenzyl (PMB) group on O, N or S</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>[CH3]-[OX2]-c1ccc(cc1)-[CH2;X4]-[OX2,NX3,SX2]</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>the benzylic C–O / C–N bond and the electron-rich ring</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>protecting group removed oxidatively (DDQ in CH2Cl2/H2O, 0 °C → rt, or CAN in MeCN/H2O), by TFA (with anisole or triethylsilane as cation scavenger) or by hydrogenolysis; stable to bases; put on with PMB-Cl/NaH or PMB trichloroacetimidate/TfOH. Orthogonal to benzyl (DDQ takes PMB and leaves Bn)</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="n"/>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>the alkoxide or amide leaves from the PMB cation</t>
+        </is>
+      </c>
+      <c r="I133" s="3" t="n"/>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L133" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
+          <t>4-MeO–C6H4–CH2–O, –N or –S. [learned from the recorded reactions: found in 0.5% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 50% of those (172 of 346); 0 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>F133</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>allyl group on O, N or S (allyl ether, allyl ester, Alloc)</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>[CH2;X4](-[OX2,NX3,SX2])-[CH]=[CH2]</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>the allylic C–O / C–N bond and the C=C</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>allyl ethers, allyl esters and allyl carbamates (Alloc): removed by Pd(0) (Pd(PPh3)4 with a scavenger: morpholine, dimedone, PhSiH3, Bu3SnH, N,N′-dimethylbarbituric acid) in THF/CH2Cl2 at rt, or isomerised (KOtBu/DMSO, Rh or Ir) to the enol ether and hydrolysed with mild acid; Tsuji–Trost allylic substitution; aryl allyl ethers undergo the Claisen rearrangement (heat, 180–220 °C); the C=C is cleaved by ozonolysis or cross-metathesis</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="n"/>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>the alkoxide, carboxylate or carbamate leaves as the π-allyl palladium complex forms</t>
+        </is>
+      </c>
+      <c r="I134" s="3" t="n"/>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
+          <t>CH2=CH–CH2–O, –N, –S. [learned from the recorded reactions: found in 0.3% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 44% of those (101 of 229); 0 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>F134</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>trityl group (Ph3C–N, Ph3C–O, Ph3C–S)</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>[CX4](-c)(-c)(-c)-[N,O,S]</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>the trityl C–O / C–N bond</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>bulky protecting group for primary OH, NH, SH and the N of imidazoles, pyrazoles and tetrazoles; removed by mild acid (1–5% TFA/CH2Cl2 with Et3SiH, 80% AcOH, HCl/MeOH, formic acid) through the stable, orange trityl cation; put on with TrCl, pyridine or Et3N/DMAP; stable to bases and nucleophiles</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="n"/>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>the alcohol, amine or azole leaves from the trityl cation (pKR+ of Ph3C⁺ ≈ −6.6)</t>
+        </is>
+      </c>
+      <c r="I135" s="3" t="n"/>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>very bulky: selective for primary over secondary alcohols</t>
+        </is>
+      </c>
+      <c r="K135" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L135" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
+          <t>Ph3C–N, Ph3C–O, Ph3C–S. [learned from the recorded reactions: found in 0.2% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 34% of those (50 of 148); 1 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>F135</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>fluorenylmethyl carbamate (Fmoc)</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>[NX3]-C(=O)-O-[CH2]-[CH]1-c2ccccc2-c2ccccc12</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>the fluorenyl C9–H (acidic) and the carbamate C</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>base-labile amine protecting group: 20% piperidine in DMF (rt, 5–20 min), DBU, morpholine or Et2NH eliminate through the fluorenyl anion to dibenzofulvene (trapped by piperidine) + CO2 + the free amine; stable to TFA and, mostly, to H2/Pd; put on with Fmoc-Cl (NaHCO3, dioxane/H2O) or Fmoc-OSu; the basis of solid-phase peptide synthesis</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>fluorenyl C–H ≈ 22.6 (fluorene, DMSO)</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="n"/>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>dibenzofulvene + CO2 + the amine</t>
+        </is>
+      </c>
+      <c r="I136" s="3" t="n"/>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="K136" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L136" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
+          <t>Fmoc carbamate: fluorenyl-CH2–O–C(=O)–N. [learned from the recorded reactions: found in 0.1% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 43% of those (24 of 56); 0 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>F136</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>trifluoroacetyl (trifluoroacetic acid TFA, trifluoroacetamide, trifluoroacetate ester)</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>[CX3](=[OX1])(C(F)(F)F)[N,O]</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>the acid O–H (trifluoroacetic acid) or the carbonyl C (amide, ester)</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>trifluoroacetic acid (TFA): strong organic acid used neat or 20–50% in CH2Cl2 (rt, 0.5–2 h) to remove Boc, tert-butyl esters and ethers and trityl (with scavengers: Et3SiH, anisole, thioanisole, water); salts of amines are trifluoroacetates. The trifluoroacetamide protects amines (TFAA/Et3N or ethyl trifluoroacetate), is removed by K2CO3/MeOH–H2O or NaBH4, and the trifluoroacetate ester is labile to methanol</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>trifluoroacetic acid 0.5 (the O–H)</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>≈ −7 (O-protonated acid)</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>CF3CO2⁻ (pKa of the acid 0.5) is a good leaving group; the trifluoroacetamide N⁻ is a poorer one</t>
+        </is>
+      </c>
+      <c r="I137" s="3" t="n"/>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
+          <t>CF3–C(=O)–O/N: trifluoroacetic acid, trifluoroacetamides, trifluoroacetate esters. [learned from the recorded reactions: found in 0.5% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 83% of those (291 of 349); 3 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>F137</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>acetamide / N-acetyl (CH3–C(=O)–N)</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>[CH3][CX3](=[OX1])[NX3]</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>the carbonyl C and the N–H</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>N-acetyl protecting group or the product of acetylation (Ac2O or AcCl with Et3N/pyridine): robust; removed by 6 M HCl or aqueous NaOH/EtOH at reflux, hydrazine, Boc2O/DMAP then base, or Meerwein salt then hydrolysis; on an aniline it is a moderate ortho/para director (acetanilide) and a weaker activator than NH2</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>N–H ≈ 17 (secondary amide; acetanilide 21.5 in DMSO)</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>≈ −0.5 (O-protonated amide)</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="n"/>
+      <c r="I138" s="3" t="n"/>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>N-aryl and N,N-disubstituted acetamides hydrolyse more slowly</t>
+        </is>
+      </c>
+      <c r="K138" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
+          <t>CH3–C(=O)–N: acetamides and acetanilides. A narrower split of F021. [learned from the recorded reactions: found in 0.9% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 30% of those (197 of 652); 4 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>F138</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>acetate ester (CH3–C(=O)–O–C: acetyl protecting group on an alcohol or phenol)</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>[CH3][CX3](=[OX1])[OX2][#6]</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>the carbonyl C</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>acetyl protecting group on an alcohol or phenol (Ac2O, pyridine, DMAP): removed by K2CO3/MeOH (rt), NaOMe/MeOH (Zemplén), NH3/MeOH, LiOH/THF–H2O or lipases; more labile than benzoate and pivalate (so it can be removed selectively), less than formate; acetyl groups migrate between neighbouring hydroxyls under base; phenyl acetates are cleaved even by mild base or amines</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>α C–H ≈ 25 (ester enolate, DMSO)</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>≈ −6.5 (O-protonated ester)</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>the alkoxide or phenoxide (pKa of the alcohol 15–16, phenol 10)</t>
+        </is>
+      </c>
+      <c r="I139" s="3" t="n"/>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>primary acetates cleave faster than secondary and tertiary</t>
+        </is>
+      </c>
+      <c r="K139" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L139" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
+          <t>CH3–C(=O)–O–C: alkyl and aryl acetates. A narrower split of F004. [learned from the recorded reactions: found in 1.1% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 69% of those (526 of 760); 19 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>F139</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>methyl / ethyl ester (saponified by LiOH, NaOH; the common ester protecting group)</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>[#6][CX3](=[OX1])[OX2][CH3,$([CH2][CH3])]</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>the carbonyl C and the α C–H</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>the common ester protecting group and synthetic intermediate: saponified by LiOH (THF/MeOH/H2O, rt), NaOH, KOH or K2CO3/MeOH–H2O to the acid; aminolysis with AlMe3 (Weinreb) or by heating with amines; reduction to the alcohol (LiAlH4, LiBH4, NaBH4/CaCl2) or to the aldehyde (DIBAL at −78 °C); Grignard double addition to a tertiary alcohol; Claisen and Dieckmann condensations (NaOEt, NaH, KOtBu); α-alkylation (LDA, −78 °C); cleaved with LiI/pyridine, BBr3, Me3SnOH or TMSOK in the presence of other esters. Hydroxide takes Me/Et esters in the presence of tert-butyl and benzyl esters</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>α C–H ≈ 25 (ester enolate, DMSO)</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>≈ −6.5 (O-protonated ester)</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>the alkoxide (MeO⁻, EtO⁻: pKa of the alcohol ≈ 15.5)</t>
+        </is>
+      </c>
+      <c r="I140" s="3" t="n"/>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>methyl esters hydrolyse about 2–3 times faster than ethyl esters; α-branching and ortho substituents slow it</t>
+        </is>
+      </c>
+      <c r="K140" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L140" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
+          <t>C–C(=O)–O–CH3 and C–C(=O)–O–CH2CH3. A narrower split of F004. [learned from the recorded reactions: found in 11.1% of 70,570 sampled starting materials; an atom of it took part in the recorded reaction in 51% of those (4,039 of 7,845); 269 of those reaction centres had no specific fragment on the sheet before]</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>F140</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>organolithium (R–Li: n-BuLi, s-BuLi, t-BuLi, MeLi, PhLi)</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>[Li]-[#6]</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>the C–Li carbon</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>very strong base and carbon nucleophile (n-BuLi in hexanes/THF, s-BuLi, t-BuLi, MeLi, PhLi): halogen–lithium exchange of ArBr/ArI (−78 °C, THF or Et2O; 2 equiv t-BuLi), directed ortho-metalation (s-BuLi/TMEDA; directing groups OMe, CONR2, CO2⁻, oxazoline, F, Cl), deprotonation of terminal alkynes and weak C–H acids, addition to aldehydes, ketones, nitriles, Weinreb amides, CO2, DMF and B(OR)3; n-BuLi slowly cleaves THF above about −20 °C; t-BuLi is pyrophoric</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>conjugate acid, the C–H ≈ 50 (butane)</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="n"/>
+      <c r="H141" s="3" t="n"/>
+      <c r="I141" s="3" t="n"/>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>t-BuLi and s-BuLi are bulkier and more basic; n-BuLi adds to hindered carbonyls less well than it deprotonates</t>
+        </is>
+      </c>
+      <c r="K141" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L141" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
+          <t>[Li]–C. Destroyed by water, alcohols, N–H and acidic C–H. [learned from the recorded reactions: a part of the reagent in 15,942 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>F141</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>Grignard reagent, chloride / iodide (R–MgCl, R–MgI: MeMgCl, iPrMgCl)</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>[#6]-[Mg]-[Cl,I]</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>the C–Mg carbon</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>carbon nucleophile and base: RMgCl and RMgI (MeMgCl, EtMgBr is F029, iPrMgCl, PhMgCl, vinylMgBr): addition to aldehydes, ketones (tertiary alcohols), esters (double addition), Weinreb amides (ketones), nitriles (ketones after hydrolysis), epoxides, CO2 (acids); iPrMgCl·LiCl (Knochel turbo-Grignard) does halogen–magnesium exchange on ArBr/ArI at −20 to 25 °C and tolerates esters and nitriles; Kumada coupling (Ni or Pd, Fe); Cu(I) catalysis gives 1,4-addition</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>conjugate acid, the C–H ≈ 45–50</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="n"/>
+      <c r="H142" s="3" t="n"/>
+      <c r="I142" s="3" t="n"/>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>bulky Grignards (tBuMgCl) reduce rather than add to hindered ketones</t>
+        </is>
+      </c>
+      <c r="K142" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L142" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
+          <t>C–Mg–Cl and C–Mg–I (the bromides are F029). Destroyed by water, alcohols and N–H. [learned from the recorded reactions: a part of the reagent in 1,500 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>F142</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>metal amide base (LDA, LiHMDS, NaHMDS, KHMDS, LiTMP)</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>[N-;X2;$([N-]([Si])[Si]),$([N-]([CX4])[CX4])]</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>the anionic N (a base, not a nucleophile)</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>strong, hindered, non-nucleophilic bases: LDA, LiHMDS, NaHMDS, KHMDS and LiTMP (THF, −78 °C): kinetic enolates of ketones, esters and amides, α-alkylation, aldol, Claisen and Dieckmann cyclisations, nitrile and sulfone α-deprotonation, ortho-lithiation with LiTMP; LiHMDS with Pd catalysts aminates ArX as an ammonia equivalent; KHMDS/NaHMDS give the more reactive, more thermodynamic (E/Z) enolates</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>conjugate acid, diisopropylamine ≈ 36 (THF); 2,2,6,6-tetramethylpiperidine ≈ 37; hexamethyldisilazane ≈ 26</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="n"/>
+      <c r="H143" s="3" t="n"/>
+      <c r="I143" s="3" t="n"/>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>very hindered, so it deprotonates rather than adds</t>
+        </is>
+      </c>
+      <c r="K143" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L143" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
+          <t>[N⁻] with two silyl or two alkyl groups (lithium, sodium or potassium amides). [learned from the recorded reactions: a part of the reagent in 7,016 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>F143</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>metal hydride (H⁻: NaH, KH, CaH2)</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>[#1;-]</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>the H⁻ (a base; rarely a hydride donor)</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>metal hydride as base: NaH (60% in mineral oil; DMF, THF, 0 °C → rt, H2 evolves) deprotonates alcohols, phenols, amides, azole N–H, thiols and 1,3-dicarbonyl compounds before alkylation or acylation (Williamson, N-alkylation, Claisen); KH is more soluble and basic; CaH2 dries solvents; reacts violently with water</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>conjugate acid, dihydrogen ≈ 35</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="n"/>
+      <c r="H144" s="3" t="n"/>
+      <c r="I144" s="3" t="n"/>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>a heterogeneous base; reaction starts at the solid surface</t>
+        </is>
+      </c>
+      <c r="K144" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L144" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
+          <t>H⁻: sodium hydride, potassium hydride, calcium hydride. [learned from the recorded reactions: a part of the reagent in 48,786 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>F144</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>borohydride (NaBH4, NaBH3CN, NaBH(OAc)3, LiBH4)</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>[$([BH4-]),$([BH3-]C#N),$([BH-](O)(O)O)]</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>the B–H hydride</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>mild hydride donors: NaBH4 reduces aldehydes and ketones (MeOH or EtOH, 0 °C; THF/H2O), acid chlorides and imines/iminiums, but not esters, amides, nitriles or acids unless activated (CaCl2, LiCl, I2, hot MeOH/THF, CeCl3 for Luche 1,2-reduction of enones); NaBH3CN reductively aminates at pH 4–6 (MeOH, AcOH), selective for the iminium over the carbonyl; NaBH(OAc)3 (STAB) reductive amination in DCE/THF with AcOH, tolerating acetals, esters, nitro; LiBH4 reduces esters (THF)</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="n"/>
+      <c r="H145" s="3" t="n"/>
+      <c r="I145" s="3" t="n"/>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>NaBH(OAc)3 is bulky and selective; NaBH4 reduces unhindered carbonyls fastest</t>
+        </is>
+      </c>
+      <c r="K145" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L145" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
+          <t>BH4⁻, BH3CN⁻, BH(OAc)3⁻ (sodium, lithium, potassium salts and tetraalkylammonium borohydrides). [learned from the recorded reactions: a part of the reagent in 29,729 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>F145</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>alkylaluminium hydride (DIBAL-H, Red-Al)</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>[AlH]</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>the Al–H hydride</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>DIBAL-H (1 M in toluene, hexane or CH2Cl2): ester → aldehyde (1 equiv, −78 °C, stops at the hemiacetal), nitrile → aldehyde (after hydrolysis), lactone → lactol, Weinreb amide → aldehyde; with excess or warmer: alcohols; α,β-unsaturated esters → allylic alcohols (2+ equiv); it is a Lewis acid and also opens epoxides and acetals. Red-Al (sodium bis(2-methoxyethoxy)aluminium hydride) reduces like LiAlH4 and dissolves in toluene. Work-up with Rochelle salt or the Fieser method</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="n"/>
+      <c r="H146" s="3" t="n"/>
+      <c r="I146" s="3" t="n"/>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>bulky and Lewis-acidic: coordinates the carbonyl O first</t>
+        </is>
+      </c>
+      <c r="K146" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L146" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
+          <t>R2Al–H: DIBAL-H and relatives (LiAlH4 is F042). [learned from the recorded reactions: a part of the reagent in 1,207 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>F146</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>phosphine (PPh3, PBu3, PCy3 and phosphine ligands: P with three carbons)</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>[PX3;+0]([#6])([#6])[#6]</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>the P lone pair</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>nucleophile and reductant: triphenylphosphine in the Mitsunobu reaction (with DEAD or DIAD: alcohol → ester, azide, ether, imide with inversion), Appel (CBr4 or CCl4: alcohol → halide), Staudinger (azide + PPh3 then H2O → amine), Wittig salt formation (+ R–X → phosphonium), deoxygenation of epoxides, sulfoxides and N-oxides; as a ligand on Pd/Rh/Ru/Ir (PPh3, PCy3, P(tBu)3, XPhos, SPhos, dppf, BINAP, Xantphos) for Suzuki, Heck, Sonogashira, Buchwald–Hartwig; oxidised to Ph3P=O (remove by crystallisation, ZnCl2 or silica)</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>conjugate acids: triphenylphosphine 2.7; tributylphosphine 8.4; tricyclohexylphosphine 9.7; tri-tert-butylphosphine 11.4</t>
+        </is>
+      </c>
+      <c r="H147" s="3" t="n"/>
+      <c r="I147" s="3" t="n"/>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>cone angle sets the ligand character: PPh3 145°, PCy3 170°, P(tBu)3 182°</t>
+        </is>
+      </c>
+      <c r="K147" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L147" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
+          <t>trialkyl and triaryl phosphines (P with three carbons), not phosphites or phosphine oxides (F103). [learned from the recorded reactions: a part of the reagent in 43,289 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>F147</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>phosphonium salt / ylide (Wittig reagents: R4P⁺, R3P=CR2)</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>[$([PX4+]([#6])([#6])([#6])[#6]),$([CX3]=[PX4]([#6])([#6])[#6])]</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>the ylide C (nucleophile) and the P⁺</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>Wittig reagents: a phosphonium salt R3P⁺–CH2R′ X⁻ with a base (n-BuLi, NaHMDS, KOtBu, NaH; K2CO3 for stabilised salts) gives the ylide, which condenses with an aldehyde or ketone to the alkene + Ph3P=O (non-stabilised ylides: mostly Z; ester- or ketone-stabilised: E; Schlosser modification: E); also the Horner–Wadsworth–Emmons relatives (F103); phosphonium salts are phase-transfer catalysts and Mitsunobu intermediates</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>methyltriphenylphosphonium ≈ 22 (DMSO); the ester-stabilised ylide precursor ≈ 8.5 (DMSO)</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="n"/>
+      <c r="H148" s="3" t="inlineStr">
+        <is>
+          <t>Ph3P=O leaves (the driving force)</t>
+        </is>
+      </c>
+      <c r="I148" s="3" t="n"/>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>hindered ketones react poorly with stabilised ylides</t>
+        </is>
+      </c>
+      <c r="K148" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L148" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
+          <t>R4P⁺ and R3P=CR2: phosphonium salts and phosphorus ylides. [learned from the recorded reactions: a part of the reagent in 1,200 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>F148</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>carbodiimide (EDC, DCC, DIC: N=C=N)</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>[NX2]=[CX2]=[NX2]</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>the central C</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>coupling and dehydrating agent: EDC·HCl (water-soluble urea, with HOBt/HOAt/Oxyma, DMAP cat.), DCC (insoluble DCU), DIC (soluble urea; solid-phase) activate a carboxylic acid to the O-acylisourea, which gives amides with amines, esters with alcohols (Steglich, DMAP), anhydrides, or rearranges to the unreactive N-acylurea (suppressed by HOBt); also Pfitzner–Moffatt oxidation (DCC/DMSO/H3PO4) and dehydration of primary amides and aldoximes to nitriles; sensitiser (DCC)</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="n"/>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>the urea (DCU, EDU) is the by-product</t>
+        </is>
+      </c>
+      <c r="I149" s="3" t="n"/>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>DCC and DIC are hindered nucleophiles but good dehydrating agents</t>
+        </is>
+      </c>
+      <c r="K149" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L149" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
+          <t>N=C=N: EDC, DCC, DIC and the other carbodiimides. [learned from the recorded reactions: a part of the reagent in 20,844 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>F149</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>uronium / phosphonium coupling reagent (HATU, HBTU, TBTU, BOP, PyBOP)</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>[$([CX3](=[N+;X3])([NX3])[OX2][#7]),$([PX4+]([#7])([#7])([#7])[OX2][#7])]</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>the uronium C / P⁺ (acyl transfer after the carboxylate attacks it)</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>amide coupling reagents: HATU (HOAt-based, fastest, least racemisation), HBTU, TBTU, HCTU (uronium/guanidinium), BOP, PyBOP, PyAOP (phosphonium), with DIPEA, NMM or Et3N in DMF, NMP or CH2Cl2 (0 °C → rt, 1–16 h); the carboxylate attacks the reagent to give the OBt/OAt active ester, which acylates the amine; excess reagent guanidinylates the amine (use ≤ 1 equiv or pre-activate the acid 1–5 min); BOP gives carcinogenic HMPA (use PyBOP); by-product tetramethylurea</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="n"/>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>HOAt (pKa 3.3) or HOBt (4.6) leaves from the active ester; tetramethylurea or tris(pyrrolidino)phosphine oxide is the by-product</t>
+        </is>
+      </c>
+      <c r="I150" s="3" t="n"/>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>works for hindered acids and amines better than carbodiimides; use HATU/HOAt for N-methyl and α,α-disubstituted amino acids</t>
+        </is>
+      </c>
+      <c r="K150" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L150" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
+          <t>C(=N⁺)(N)O–N / P⁺(N)(N)(N)O–N: HATU, HBTU, TBTU, HCTU, PyBOP, BOP. [learned from the recorded reactions: a part of the reagent in 20,496 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>F150</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>N-hydroxybenzotriazole (HOBt, HOAt: coupling additive)</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>[OX2H1,OX1-][nX3]1:[nX2]:[nX2]:c:c:1</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>the N–O⁻ / O–H oxygen</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>additive that makes carbodiimide couplings clean: traps the O-acylisourea as the HOBt/HOAt active ester, which acylates amines with little racemisation and without N-acylurea; HOAt is the more reactive (neighbouring-group effect of the pyridine N). Anhydrous HOBt is explosive (sold as the hydrate); OxymaPure and 6-Cl-HOBt are alternatives</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>HOBt 4.6; HOAt 3.3 (the O–H)</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="n"/>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>HOBt/HOAt leave from their active esters</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="n"/>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="K151" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L151" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
+          <t>N-hydroxybenzotriazole and N-hydroxy-7-azabenzotriazole. [learned from the recorded reactions: a part of the reagent in 16,557 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>F151</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>N-halo imide / amide (NBS, NCS, NIS, DBDMH, chloramine-T)</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>[NX3]([CX3]=[OX1])[Cl,Br,I]</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>the N–X halogen (X⁺ source)</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>electrophilic halogen: NBS (MeCN, DMF or CH2Cl2, 0 °C → rt) brominates activated arenes (anisoles, phenols, anilines, indoles, pyrroles, thiophenes, pyrazole C4), ketone α-positions (acid or TsOH cat.) and, with a radical initiator (AIBN, BPO or light; CCl4, PhCF3 or MeCN, reflux), allylic and benzylic C–H (Wohl–Ziegler); bromohydrins and bromoethers from alkenes (NBS/H2O–DMSO or ROH); NCS chlorinates, NIS iodinates (arenes with TFA/TfOH or alkynes with Ag⁺); use 1.0–1.1 equiv to avoid polyhalogenation; succinimide by-product</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="n"/>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>the imide anion (succinimide N–H pKa 9.6) leaves; Br⁺ is transferred</t>
+        </is>
+      </c>
+      <c r="I152" s="3" t="n"/>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>open; benzylic bromination selects the most stabilised radical position</t>
+        </is>
+      </c>
+      <c r="K152" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L152" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
+          <t>N(C=O)–Cl, –Br, –I: N-bromosuccinimide, N-chlorosuccinimide, N-iodosuccinimide, DBDMH, trichloroisocyanuric acid, chloramine-T. [learned from the recorded reactions: a part of the reagent in 1,233 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>F152</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>dihalogen / interhalogen (Br2, Cl2, I2, ICl, IBr)</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>[Cl,Br,I]-[Cl,Br,I]</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>the X–X bond</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>Br2 (CH2Cl2 or AcOH, 0 °C → rt): anti addition to alkenes and alkynes (via the bromonium ion), α-bromination of ketones (acid-catalysed enol; AcOH/HBr cat.), aromatic bromination (FeBr3 or Fe for benzene, none needed for phenols and anilines), Hell–Volhard–Zelinsky of carboxylic acids (PBr3 cat., Br2); Cl2 similar (radical chlorination of alkanes with light); I2 (with HIO3, H5IO6, CAN or Ag⁺ for arenes; base for phenols and imidazoles) for iodination, iodolactonisation (I2/NaHCO3), the haloform and iodoform reactions of methyl ketones (X2/NaOH); ICl and IBr are more electrophilic</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="n"/>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>X⁻ (HBr −9, HCl −7, HI −10)</t>
+        </is>
+      </c>
+      <c r="I153" s="3" t="n"/>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L153" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
+          <t>Br–Br, Cl–Cl, I–I, I–Cl, I–Br. [learned from the recorded reactions: a part of the reagent in 10,019 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>F153</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>halide anion (Cl⁻, Br⁻, I⁻: NaI, KBr, LiCl, Bu4NBr)</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>[Cl-,Br-,I-]</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>the anion (nucleophile, counter-ion)</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>NaI in acetone (Finkelstein: R–Cl or R–Br → R–I, driven by the precipitation of NaCl/NaBr); LiCl or LiBr in DMF (SN2 on tosylates and mesylates; Krapcho decarboxylation with LiCl, DMSO, H2O, 150 °C; dealkylation of methyl esters with LiI); halide opens epoxides and aziridines; Cu-catalysed aromatic Finkelstein (CuI/diamine, NaI); with an oxidant (Oxone, NaOCl, H2O2) Br⁻ and I⁻ become Br⁺ and I⁺ equivalents; Bu4NBr/Bu4NI as phase-transfer catalysts; as the counter-ion of hydrochlorides and of ammonium and phosphonium salts it is a spectator</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>conjugate acids HI −10, HBr −9, HCl −7</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="n"/>
+      <c r="H154" s="3" t="n"/>
+      <c r="I154" s="3" t="n"/>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>iodide is the most nucleophilic in protic solvents; chloride the most in DMF</t>
+        </is>
+      </c>
+      <c r="K154" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L154" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
+          <t>Cl⁻, Br⁻, I⁻. [learned from the recorded reactions: a part of the reagent in 63,960 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>F154</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>fluoride anion (F⁻: TBAF, CsF, KF)</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>[F-]</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>the anion</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>F⁻ sources (TBAF in THF; CsF; KF/18-crown-6; Et3N·3HF; HF·pyridine): removes silyl groups (TBS, TIPS, TBDPS, TMS; TBAF/THF, 0 °C → rt; buffer with AcOH for base-sensitive substrates) and C–SiMe3 groups (alkyne and aryl desilylation), SNAr fluorination of activated aryl chlorides and nitroarenes (halex: CsF or KF, DMSO or sulfolane, 120–180 °C), SN2 on alkyl sulfonates (TBAF, tert-amyl alcohol), activates boronic acids and silanes in Suzuki and Hiyama couplings; naked F⁻ in aprotic solvents is strongly basic (E2 elimination)</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>HF 3.2</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="n"/>
+      <c r="H155" s="3" t="n"/>
+      <c r="I155" s="3" t="n"/>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>TBAF is hygroscopic and basic; anhydrous F⁻ is a poor nucleophile in protic solvents (strong H-bonding)</t>
+        </is>
+      </c>
+      <c r="K155" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L155" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
+          <t>F⁻. [learned from the recorded reactions: a part of the reagent in 8,895 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>F155</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>azide anion (N3⁻: NaN3)</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>[N-]=[N+]=[N-]</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>the terminal N (nucleophile)</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>NaN3 (DMF, DMSO or water/acetone, 50–80 °C; TMSN3): SN2 on alkyl halides and sulfonates (with inversion) to alkyl azides, which are reduced to amines (H2/Pd, PPh3/H2O Staudinger, Zn/NH4Cl) or clicked with alkynes (CuAAC, RuAAC); epoxide opening (NaN3, NH4Cl, MeOH/H2O); SNAr on activated haloarenes and halo-azines; acyl azides (Curtius) from acid chlorides; tetrazoles from nitriles (NaN3, NH4Cl or ZnBr2, 100–130 °C); toxic; HN3 is explosive (do not acidify; avoid CH2Cl2 and CHCl3, which form diazidomethane)</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>hydrazoic acid 4.7</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="n"/>
+      <c r="H156" s="3" t="n"/>
+      <c r="I156" s="3" t="n"/>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>a small, strong nucleophile: SN2 even at hindered secondary centres</t>
+        </is>
+      </c>
+      <c r="K156" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L156" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
+          <t>N3⁻ (sodium, potassium azide; azide from TMSN3 and fluoride). [learned from the recorded reactions: a part of the reagent in 5,081 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>F156</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>carbonate / bicarbonate (CO3²⁻, HCO3⁻: K2CO3, Cs2CO3, Na2CO3, NaHCO3)</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>[$([CX3](=[OX1])([OX1-])[OX1-]),$([CX3](=[OX1])([OX1-])[OX2H1])]</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>the O⁻ (base), seldom the carbonyl C</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>the common mild inorganic base: K2CO3, Cs2CO3, Na2CO3, NaHCO3 in DMF, MeCN, acetone, THF/H2O or dioxane/H2O: O-, N- and S-alkylation of phenols, azoles, amides and thiols (Cs2CO3 is more soluble and gives a more naked anion), Suzuki, Buchwald–Hartwig, Heck and Ullmann couplings, SNAr, ester hydrolysis in MeOH/H2O (K2CO3), and neutralisation or work-up (saturated NaHCO3); saturated NaHCO3 buffers at pH ≈ 8.3</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>bicarbonate → carbonate 10.3 (water); carbonic acid 6.4</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="n"/>
+      <c r="H157" s="3" t="n"/>
+      <c r="I157" s="3" t="n"/>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>K2CO3 is poorly soluble in organic solvents (solid-liquid); Cs2CO3 and K3PO4 dissolve better</t>
+        </is>
+      </c>
+      <c r="K157" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L157" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
+          <t>CO3²⁻ and HCO3⁻. Recorded reactions often list carbonate as a reactant because the atom mapping assigned one of its O atoms to the product: such templates are artefacts. [learned from the recorded reactions: a part of the reagent in 135,546 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>F157</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>carbon dioxide (CO2, dry ice)</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>O=C=O</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>the carbon (electrophile)</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>electrophile for carbanions: ArLi, RLi and Grignard reagents add to CO2 (dry ice or gas; THF or Et2O, −78 °C → rt) to give, after acid, the carboxylic acid; Kolbe–Schmitt (phenoxide + CO2, 125 °C, 5 atm) gives salicylic acids; amines add reversibly to give carbamate salts (R2N–CO2⁻), which Cs2CO3/R–X/Bu4NI alkylate to carbamates; it is also what leaves in decarboxylations (Boc removal, malonic acid, Krapcho) and the C1 source of cyclic carbonates (epoxide + CO2)</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="n"/>
+      <c r="H158" s="3" t="n"/>
+      <c r="I158" s="3" t="n"/>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="K158" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L158" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
+          <t>O=C=O. [learned from the recorded reactions: a part of the reagent in 1,457 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>F158</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>formaldehyde (CH2=O: formalin, paraformaldehyde)</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>[CH2]=[OX1]</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>the carbonyl C (electrophile)</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>the most reactive aldehyde, with no α C–H: formalin (37% aqueous with methanol), paraformaldehyde (depolymerises with heat or base), trioxane. Hydroxymethylation of enolates and active methylenes (aldol, NaOH or K2CO3), Mannich (R2NH·HCl + CH2O + ketone), Eschweiler–Clarke N-methylation (CH2O/HCO2H), reductive amination to N-methyl (CH2O + NaBH3CN or NaBH(OAc)3), Pictet–Spengler (tryptamines, acid), Prins (alkenes, acid), Blanc chloromethylation (CH2O/HCl/ZnCl2), Cannizzaro (conc. NaOH), MOM and methylene acetals</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>≈ −7 (O-protonated aldehyde)</t>
+        </is>
+      </c>
+      <c r="H159" s="3" t="n"/>
+      <c r="I159" s="3" t="n"/>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="K159" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L159" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr">
+        <is>
+          <t>CH2=O: formaldehyde in all its forms. [learned from the recorded reactions: a part of the reagent in 3,349 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>F159</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>carbon disulfide / thiophosgene (CS2, CSCl2)</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>[SX1]=[$([CX2]=[SX1]),$([CX3](Cl)Cl)]</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>the thiocarbonyl C (electrophile)</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>CS2 with an amine and base (Et3N, NaOH) gives the dithiocarbamate (then S-alkylation to R2N–C(=S)–SR, or with EDC/TsCl/Boc2O the isothiocyanate); with an alkoxide the xanthate (Chugaev elimination; Barton–McCombie deoxygenation: ROC(=S)SMe then Bu3SnH/AIBN); with o-aminophenols, hydrazides and anthranilic acids the benzoxazole-, oxadiazole- and quinazoline-thiones; thiophosgene (CSCl2; CHCl3 or CH2Cl2/water, NaHCO3) turns R–NH2 into R–N=C=S and 1,2-diamines into cyclic thioureas; toxic; CS2 flash point −30 °C</t>
+        </is>
+      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="n"/>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>S²⁻/HS⁻ (from CS2) or Cl⁻ (from thiophosgene)</t>
+        </is>
+      </c>
+      <c r="I160" s="3" t="n"/>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="K160" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L160" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr">
+        <is>
+          <t>S=C=S and S=C(Cl)Cl. [learned from the recorded reactions: a part of the reagent in 476 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>F160</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>trialkyl borate (B(OMe)3, B(OiPr)3)</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>[BX3]([OX2][CX4])([OX2][CX4])[OX2][CX4]</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>the B (electrophile)</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>trimethyl and triisopropyl borate trap aryl- and alkyllithiums or Grignards (−78 °C, THF) to give the boronate, hydrolysed with aqueous HCl or NH4Cl to the boronic acid for Suzuki coupling (in situ quench: LDA or LiTMP + ArX in the presence of B(OiPr)3 tolerates halides); pinacol esterification; oxidation to phenols (H2O2/NaOH, NaBO3); B(OMe)3 also traps enolates</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="n"/>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>the alkoxide (MeO⁻, iPrO⁻) leaves</t>
+        </is>
+      </c>
+      <c r="I161" s="3" t="n"/>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>B(OiPr)3 is bulkier and gives less over-addition (borinic acids) than B(OMe)3</t>
+        </is>
+      </c>
+      <c r="K161" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L161" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="inlineStr">
+        <is>
+          <t>B(OR)3 with three alkyl groups (not boronic acids F081 or pinacol esters F082). [learned from the recorded reactions: a part of the reagent in 177 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>F161</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>deoxofluorinating agent (DAST, Deoxo-Fluor: R2N–SF3)</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>[NX3]-[SX4](-F)(-F)-F</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>the S–F fluorine (F⁻ donor) and the S</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>deoxofluorination: DAST (Et2NSF3), Deoxo-Fluor ((MeOCH2CH2)2NSF3), XtalFluor-E/M, PyFluor: R–OH → R–F by SN2 with inversion (CH2Cl2, −78 °C → rt), aldehydes and ketones → gem-difluorides (rt to reflux, slower), carboxylic acids → acyl fluorides; elimination and rearrangement compete for β-branched, benzylic and tertiary alcohols; DAST decomposes explosively above ≈ 90 °C (Deoxo-Fluor and XtalFluor are safer); generates HF: glass, quench with cold saturated NaHCO3</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="n"/>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>R2N–S(O)F after transfer of F⁻</t>
+        </is>
+      </c>
+      <c r="I162" s="3" t="n"/>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>hindered alcohols eliminate instead of fluorinating</t>
+        </is>
+      </c>
+      <c r="K162" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L162" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="inlineStr">
+        <is>
+          <t>R2N–SF3. [learned from the recorded reactions: a part of the reagent in 89 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>F162</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>hypervalent iodine (Dess–Martin periodinane, IBX, PIDA, PIFA)</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>[I;X3,X4,X5]</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>the I(III) / I(V) centre (an oxidant and group-transfer agent)</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>Dess–Martin periodinane (DMP: CH2Cl2, rt, optionally buffered with NaHCO3): primary alcohols → aldehydes, secondary → ketones, no over-oxidation, tolerates most functional groups; IBX (DMSO; or EtOAc/MeCN suspension at 80 °C): alcohols → carbonyls, ketones → enones with excess; PIDA/PIFA: Hofmann rearrangement of primary amides, oxidative dearomatisation of phenols (spirocycles), C–H amination and oxidative couplings, TEMPO/PIDA alcohol oxidation; iodonium salts transfer aryl groups</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="n"/>
+      <c r="H163" s="3" t="inlineStr">
+        <is>
+          <t>the iodoarene (ArI) leaves</t>
+        </is>
+      </c>
+      <c r="I163" s="3" t="n"/>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>DMP is mild; IBX is insoluble in most solvents</t>
+        </is>
+      </c>
+      <c r="K163" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L163" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="inlineStr">
+        <is>
+          <t>I with three or more neighbours: DMP, IBX, PIDA, PIFA, diaryliodonium salts. [learned from the recorded reactions: a part of the reagent in 3,830 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>F163</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>metal-oxo oxidant (CrO3, PCC, PDC, KMnO4, OsO4, RuO4, SeO2)</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>[Cr,Mn,Os,Ru,Se;$(*=O),$(*-[O-])]</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>the M=O oxygen (oxidant)</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>Jones reagent (CrO3, H2SO4, acetone: secondary alcohols → ketones, primary → acids), PCC/PDC (CH2Cl2 ± Celite or NaOAc: primary → aldehydes), KMnO4 (cold alkaline: alkenes → diols; hot or acidic: cleavage; alkylarenes → ArCO2H; aldehydes → acids), OsO4 (cat. with NMO: alkene → syn-diol; Sharpless asymmetric dihydroxylation with (DHQ)2PHAL/K3Fe(CN)6), RuO4 (RuCl3/NaIO4: alkene cleavage, ether → ester, arene → acid), SeO2 (allylic oxidation; α-oxidation of ketones to 1,2-diketones, dioxane/H2O reflux); toxic: Cr(VI), Os, Se</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="n"/>
+      <c r="H164" s="3" t="n"/>
+      <c r="I164" s="3" t="n"/>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>OsO4 adds to the less hindered face and the more electron-rich alkene</t>
+        </is>
+      </c>
+      <c r="K164" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L164" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="inlineStr">
+        <is>
+          <t>Cr, Mn, Os, Ru, Se with an oxo or oxide ligand. [learned from the recorded reactions: a part of the reagent in 4,844 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>F164</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>platinum-group metal catalyst (Pd, Pt, Rh, Ru, Ir, Ni: Pd/C, Pd(PPh3)4, Pd(OAc)2, Raney Ni)</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>[Pd,Pt,Rh,Ru,Ir,Ni]</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>the metal (catalyst)</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>Pd/C or Pd(OH)2/C with H2 (1 atm–50 psi; EtOH, MeOH, EtOAc): alkene and alkyne → alkane (Lindlar: cis-alkene), nitro, azide, nitrile and C=N → amine, hydrogenolysis of benzyl, Cbz and benzylic C–X, dehalogenation of aryl halides; Pd(PPh3)4, PdCl2(dppf), Pd(OAc)2, Pd2(dba)3 with phosphines: cross couplings (Suzuki with aqueous K2CO3 or K3PO4 in dioxane or toluene/EtOH, 80–110 °C; Buchwald–Hartwig C–N/C–O with XPhos, BINAP or Xantphos and NaOtBu or Cs2CO3; Heck; Sonogashira with CuI; Stille; Negishi; carbonylation); Pt/PtO2 (Adams) and Rh/Al2O3 hydrogenate arenes; Raney Ni desulfurises and reduces; Ru: Noyori transfer hydrogenation and metathesis; Ir: C–H borylation and asymmetric hydrogenation</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="n"/>
+      <c r="H165" s="3" t="n"/>
+      <c r="I165" s="3" t="n"/>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>ligand bulk sets which halide couples (ArCl needs bulky electron-rich phosphines)</t>
+        </is>
+      </c>
+      <c r="K165" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L165" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="inlineStr">
+        <is>
+          <t>Pd, Pt, Rh, Ru, Ir, Ni in any form (metal on carbon, salts, complexes). [learned from the recorded reactions: a part of the reagent in 101,490 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>F165</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>copper species (CuI, CuBr, CuCl, Cu(OAc)2, Cu2O)</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>[Cu]</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>the metal (catalyst, reagent)</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>CuI, CuBr, CuCl, CuCN, Cu(OAc)2, Cu2O: Ullmann and Goldberg C–N, C–O and C–S couplings (CuI + 1,10-phenanthroline, DMEDA or L-proline, K2CO3/K3PO4/Cs2CO3, DMSO or DMF, 90–130 °C), Chan–Lam (Cu(OAc)2, ArB(OH)2 + N–H/O–H, air, pyridine or Et3N, rt), Sandmeyer (ArN2⁺ + CuX/CuCN), Rosenmund–von Braun (ArBr + CuCN, DMF/NMP, 150–200 °C), Sonogashira co-catalyst, click (CuAAC: CuSO4/ascorbate or CuI/DIPEA), organocuprate conjugate additions (R2CuLi; RMgX + cat. CuI), aromatic Finkelstein, trifluoromethylation</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="n"/>
+      <c r="H166" s="3" t="n"/>
+      <c r="I166" s="3" t="n"/>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>ligands make Cu(I) soluble and lower the temperature</t>
+        </is>
+      </c>
+      <c r="K166" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L166" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="inlineStr">
+        <is>
+          <t>Cu in any oxidation state. [learned from the recorded reactions: a part of the reagent in 15,962 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>F166</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>metal in the zero oxidation state (Zn, Fe, Sn, Mg, Na, K, Li, Al, Sm, In dust, powder or turnings)</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>[Zn,Fe,Sn,Mg,Na,K,Li,Al,Sm,In,Mn,Ca;+0;D0]</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>the metal (electron donor)</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>Zn dust (activated with HCl, TMSCl or 1,2-dibromoethane): nitro → amine (Zn/NH4Cl, AcOH), Clemmensen (Zn(Hg)/HCl), Reformatsky, Negishi organozinc insertion, Troc removal; Fe powder with NH4Cl, AcOH or HCl (Béchamp): nitro → aniline, tolerating halogens, esters and nitriles; Sn or SnCl2·2H2O (EtOH reflux): nitro → amine; Mg turnings (activate with I2, 1,2-dibromoethane): Grignard formation in THF or Et2O, Mg/MeOH reductions; Li, Na, K (Birch: Na or Li/NH3 gives 1,4-dienes and trans-alkenes; Bouveault–Blanc; alkoxide formation); Al, Mn, In, Sm (SmI2: ketyl couplings)</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="n"/>
+      <c r="H167" s="3" t="n"/>
+      <c r="I167" s="3" t="n"/>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>surface area and activation decide the rate</t>
+        </is>
+      </c>
+      <c r="K167" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L167" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
+          <t>zero-valent Zn, Fe, Sn, Mg, Na, K, Li, Al, Sm, In, Mn, Ca (dust, powder, turnings, wire). [learned from the recorded reactions: a part of the reagent in 19,682 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>F167</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>metal / boron halide Lewis acid (BF3, BBr3, AlCl3, TiCl4, ZnCl2, SnCl4, FeCl3, MgBr2)</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>[B,Al,Ti,Zn,Sn,Fe,Mg,Zr,In,Cu,Sc,Yb,Ce,Ga,Mn,Co,Cd,Sb;$(*~[F,Cl,Br,I]);!$(*-[#6])]</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>the metal or B (electron-pair acceptor)</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>BBr3 and BCl3 (CH2Cl2, −78 °C → rt) cleave aryl methyl ethers, benzyl ethers and tert-butyl ethers (1 equiv per Lewis-basic site); AlCl3 drives Friedel–Crafts alkylation and acylation (stoichiometric for acylation), the Fries rearrangement and ArOMe demethylation next to C=O; BF3·OEt2 activates epoxides, acetals and ketals, silyl enol ethers (Mukaiyama aldol) and glycosylations; TiCl4 for Mukaiyama and Evans aldol, TiCl3/Zn or LiAlH4 for McMurry; ZnCl2 in the Fischer indole synthesis and as the Negishi transmetalation partner; SnCl4, FeCl3 for Friedel–Crafts and oxidative couplings; MgBr2·OEt2 chelation control; CeCl3 for Luche reduction</t>
+        </is>
+      </c>
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="n"/>
+      <c r="H168" s="3" t="n"/>
+      <c r="I168" s="3" t="n"/>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>bulky Lewis acids (MAD, BBr3 at low temperature) are more selective</t>
+        </is>
+      </c>
+      <c r="K168" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L168" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N168" s="3" t="inlineStr">
+        <is>
+          <t>B, Al, Ti, Zn, Sn, Fe, Mg, Zr, In, Cu, Sc, Yb, Ce, Ga, Mn, Co, Cd, Sb bonded to F, Cl, Br or I and to no carbon. [learned from the recorded reactions: a part of the reagent in 28,313 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>F168</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>quaternary ammonium (R4N⁺: Bu4N⁺ phase-transfer catalysts and salts)</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>[NX4+;H0]([#6])([#6])([#6])[#6]</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>the N⁺ (cation) and the counter-anion</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>tetraalkylammonium salts (Bu4N⁺ Br⁻, I⁻, HSO4⁻, F⁻, OH⁻, N3⁻; Aliquat 336; benzyltriethylammonium chloride) are phase-transfer catalysts (1–10 mol%): they carry OH⁻, CN⁻, N3⁻, F⁻, phenoxides and enolates into organic solvents for alkylation, Darzens, epoxidation, hypochlorite oxidations and biphasic NaOH(aq)/toluene or CH2Cl2 reactions; Bu4NI catalyses SN2 by iodide exchange; Hofmann elimination of R4N⁺ OH⁻ on heating gives the least-substituted alkene</t>
+        </is>
+      </c>
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H</t>
+        </is>
+      </c>
+      <c r="G169" s="3" t="n"/>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>the tertiary amine leaves in Hofmann elimination and SN2 at the α C</t>
+        </is>
+      </c>
+      <c r="I169" s="3" t="n"/>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>long chains make the ion pair soluble in organic solvents</t>
+        </is>
+      </c>
+      <c r="K169" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L169" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N169" s="3" t="inlineStr">
+        <is>
+          <t>R4N⁺ with four carbons on N (not a protonated amine, see ammonium salt). [learned from the recorded reactions: a part of the reagent in 12,339 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>F169</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>ammonium salt (protonated amine R3NH⁺, RNH3⁺, NH4⁺: amine hydrochlorides)</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>[NX4+;!H0]</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>the N⁺–H (acid)</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>amine hydrochlorides and other ammonium salts are the storage form of amines: they need a base (Et3N, DIPEA, NaHCO3, K2CO3) to free the amine before acylation, alkylation or reductive amination; NH4Cl is the mild acid for quenching, with Zn or Fe for nitro reduction, and the ammonia source for primary amides (NH4Cl + acid chloride, ester or anhydride + Et3N) and Strecker reactions; NH4OAc is the imine/enamine source in reductive amination to primary amines (NaBH3CN), Hantzsch and Debus–Radziszewski imidazole syntheses</t>
+        </is>
+      </c>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t>ammonium ion 9.25; triethylammonium 10.75; anilinium 4.6; pyridinium 5.2; piperidinium 11.1</t>
+        </is>
+      </c>
+      <c r="G170" s="3" t="n"/>
+      <c r="H170" s="3" t="n"/>
+      <c r="I170" s="3" t="n"/>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="K170" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L170" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>learned from the recorded reactions (tools/discover_fragments.py, tools/new_fragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N170" s="3" t="inlineStr">
+        <is>
+          <t>R3NH⁺, R2NH2⁺, RNH3⁺, NH4⁺ (a protonated amine or ammonia). [learned from the recorded reactions: a part of the reagent in 30,527 of the 1,090,843 learned reactions]</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>F170</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>aryl chloride next to a ring N (2-chloropyridine, 2-chlorothiazole, 2-chloropyrimidine)</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>[Cl;X1]-c:[nX2;+0]</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>the ring C–Cl carbon (attacked at the ipso position)</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>SNAr electrophile: the ring N takes the negative charge of the Meisenheimer complex, so amines (DIPEA, n-BuOH or NMP, 80–150 °C; 2-chloropyrimidines already at rt), alkoxides and thiolates displace Cl⁻ where an ordinary aryl chloride does not react. Suzuki, Buchwald–Hartwig and Negishi couplings work with ordinary Pd catalysts (Pd(PPh3)4, Pd(dppf)Cl2; XPhos or RuPhos for hindered partners). Hydrolysis (aq. HCl or NaOH, heat) to the pyridone-type lactam is the usual side reaction; H2/Pd-C or Zn/AcOH remove the Cl</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="n"/>
+      <c r="G171" s="3" t="inlineStr">
+        <is>
+          <t>≈ 0.7 (2-chloropyridinium; 2-chloropyrimidine is far less basic)</t>
+        </is>
+      </c>
+      <c r="H171" s="3" t="inlineStr">
+        <is>
+          <t>Cl⁻ leaves after addition; the rate follows how well the ring stabilises the anion (pyrimidine, N-oxide and nitro-pyridine &gt; pyridine)</t>
+        </is>
+      </c>
+      <c r="I171" s="3" t="n"/>
+      <c r="J171" s="3" t="inlineStr">
+        <is>
+          <t>a substituent next to the C–Cl slows attack; a 3-substituent has little effect on a coupling</t>
+        </is>
+      </c>
+      <c r="K171" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L171" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N171" s="3" t="inlineStr">
+        <is>
+          <t>Cl–c:n. 2-Chloropyridine, 2-chloropyrimidine, 2-chloropyrazine, 2-chlorothiazole, 2-chlorobenzothiazole, 1-chloroisoquinoline. A narrower split of F047 (aryl chloride), which it separates from the ordinary chloroarene that needs a Pd catalyst. [learned from the recorded reactions: in a sample of 200,000 training reactions 14,052 have this group together with its parent; the parent group was consumed in 73% of them against 13% of the 33,675 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 2,252 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>F171</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>aryl bromide next to a ring N (2-bromopyridine, 2-bromothiazole)</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>[Br;X1]-c:[nX2;+0]</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>the ring C–Br carbon</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>the easiest ring bromide to couple: Suzuki–Miyaura, Stille, Negishi, Sonogashira and Buchwald–Hartwig reactions (Pd(PPh3)4 or Pd(dppf)Cl2, 80–100 °C) and halogen–metal exchange (n-BuLi, −78 °C, or i-PrMgCl·LiCl) at the C–Br; SNAr with amines and alkoxides is slower than for the chloride or fluoride at the same position but works in hot DMSO or NMP</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="n"/>
+      <c r="G172" s="3" t="inlineStr">
+        <is>
+          <t>≈ 0.9 (2-bromopyridinium)</t>
+        </is>
+      </c>
+      <c r="H172" s="3" t="inlineStr">
+        <is>
+          <t>Br⁻ leaves from the Meisenheimer complex or by oxidative addition to Pd(0)</t>
+        </is>
+      </c>
+      <c r="I172" s="3" t="n"/>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>a substituent next to the C–Br slows coupling; the ring N can bind Pd, so bidentate ligands (dppf, Xantphos) help</t>
+        </is>
+      </c>
+      <c r="K172" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L172" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N172" s="3" t="inlineStr">
+        <is>
+          <t>Br–c:n. 2-Bromopyridine, 2-bromopyrimidine, 2-bromothiazole, 2-bromobenzothiazole. A narrower split of F013 (aryl bromide). [learned from the recorded reactions: in a sample of 200,000 training reactions 3,112 have this group together with its parent; the parent group was consumed in 73% of them against 50% of the 21,508 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 117 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>F172</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>aryl chloride with an ortho/para electron-withdrawing group (SNAr-activated)</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>[Cl;X1]-[c;$(c:c-[$([N+](=[OX1])[O-]),$([CX2]#[NX1]),$([CX4](F)(F)F),$([CX3]=[OX1]),$([SX4](=[OX1])=[OX1])]),$(c:c:c:c-[$([N+](=[OX1])[O-]),$([CX2]#[NX1]),$([CX4](F)(F)F),$([CX3]=[OX1]),$([SX4](=[OX1])=[OX1])])]</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>the ring C–Cl carbon (ipso)</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>SNAr electrophile: an ortho or para electron-withdrawing group (NO2 ≫ CN, C(=O)R, SO2R, CF3) stabilises the Meisenheimer anion, so amines (K2CO3 or DIPEA, DMSO/DMF/NMP, 60–120 °C), alkoxides and thiolates displace Cl⁻. Pd-catalysed coupling is easier than for an electron-rich chloride (Suzuki: Pd(dppf)Cl2). A nitro group is reduced first (Fe/NH4Cl, SnCl2, H2/Pd-C leaves the Cl at rt)</t>
+        </is>
+      </c>
+      <c r="F173" s="3" t="n"/>
+      <c r="G173" s="3" t="n"/>
+      <c r="H173" s="3" t="inlineStr">
+        <is>
+          <t>Cl⁻ after addition (rate-limiting step is the addition)</t>
+        </is>
+      </c>
+      <c r="I173" s="3" t="n"/>
+      <c r="J173" s="3" t="inlineStr">
+        <is>
+          <t>ortho substituents beyond the EWG slow SNAr and coupling; a second EWG (2,4-dinitro) makes it very reactive</t>
+        </is>
+      </c>
+      <c r="K173" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L173" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N173" s="3" t="inlineStr">
+        <is>
+          <t>Cl–c with a nitro, cyano, carbonyl, CF3 or sulfonyl group ortho or para on the same ring. A narrower split of F047 (aryl chloride); the fluoride is F085. [learned from the recorded reactions: in a sample of 200,000 training reactions 10,079 have this group together with its parent; the parent group was consumed in 32% of them against 30% of the 37,648 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 61 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>F173</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>aryl chloride with an ortho/para electron-donating group (deactivated)</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>[Cl;X1]-[c;$(c:c-[$([OX2H1]),$([OX2][#6]),$([NX3;+0;!$(N-[C,S,P]=[O,S,N]);!$(N-[#7,#8])])]),$(c:c:c:c-[$([OX2H1]),$([OX2][#6]),$([NX3;+0;!$(N-[C,S,P]=[O,S,N]);!$(N-[#7,#8])])])]</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>the ring C–Cl carbon</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>a poor SNAr electrophile (the donor destabilises the Meisenheimer anion) and a slow oxidative-addition partner: couplings need an electron-rich ligand (Pd2dba3 with XPhos, SPhos, RuPhos or t-Bu3P; Ni(cod)2 with a phosphine) at 100–110 °C; Grignard formation needs Mg/THF with an initiator; t-BuLi may deprotonate ortho to an OMe instead of exchanging the Cl; Pd/C–H2 does not remove it at rt</t>
+        </is>
+      </c>
+      <c r="F174" s="3" t="n"/>
+      <c r="G174" s="3" t="n"/>
+      <c r="H174" s="3" t="inlineStr">
+        <is>
+          <t>Cl⁻ only by special routes</t>
+        </is>
+      </c>
+      <c r="I174" s="3" t="n"/>
+      <c r="J174" s="3" t="inlineStr">
+        <is>
+          <t>an ortho OMe or NR2 also coordinates Pd and can help or hinder</t>
+        </is>
+      </c>
+      <c r="K174" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L174" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N174" s="3" t="inlineStr">
+        <is>
+          <t>Cl–c with an alkoxy, hydroxy or amino group ortho or para on the same ring (chloroanisole, chloroaniline). A narrower split of F047 (aryl chloride). [learned from the recorded reactions: in a sample of 200,000 training reactions 9,182 have this group together with its parent; the parent group was consumed in 20% of them against 33% of the 38,545 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 97 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>F174</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>benzylic chloride (Ar–CH2–Cl)</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>c-[CX4;H2]-[Cl;X1]</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>the CH2–Cl carbon</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>SN2 and SN1 electrophile, faster than a plain primary alkyl chloride (electron-rich aryl groups favour SN1 and solvolysis): amines (K2CO3 or Et3N, MeCN or DMF, rt–60 °C), alkoxides and phenoxides (Williamson), cyanide (NaCN, DMSO), azide (NaN3, DMF), thiols, malonate (NaH, DMF); catalytic NaI (acetone) speeds it up (Finkelstein). Arbuzov (P(OEt)3, heat) gives the benzylphosphonate; Pd(0) couples it with ArB(OH)2 to diarylmethanes. Lachrymatory, hydrolyses slowly in hot water</t>
+        </is>
+      </c>
+      <c r="F175" s="3" t="n"/>
+      <c r="G175" s="3" t="n"/>
+      <c r="H175" s="3" t="inlineStr">
+        <is>
+          <t>Cl⁻ (pKa of HCl ≈ −7): good</t>
+        </is>
+      </c>
+      <c r="I175" s="3" t="n"/>
+      <c r="J175" s="3" t="inlineStr">
+        <is>
+          <t>primary: open; an ortho substituent slows SN2 slightly</t>
+        </is>
+      </c>
+      <c r="K175" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L175" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N175" s="3" t="inlineStr">
+        <is>
+          <t>c–CH2–Cl. A narrower split of F011 (alkyl chloride) and F044 (1° alkyl halide); the bromide is F036. [learned from the recorded reactions: in a sample of 200,000 training reactions 2,301 have this group together with its parent; the parent group was consumed in 95% of them against 78% of the 8,832 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 78 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>F175</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>2-halo-azole (Cl/Br/I on a 5-ring carbon next to a ring N: thiazole, imidazole, oxazole)</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>[Cl,Br,I;X1]-[c;r5]:[nX2;r5;+0]</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>the ring C–X carbon (C2 of the azole)</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>SNAr electrophile at C2 (2-chlorobenzothiazole and 2-chlorobenzoxazole react with amines, alkoxides and thiolates at rt–80 °C; 2-chloroimidazoles need protection of the N–H and heat); Pd coupling (Suzuki, Sonogashira, Buchwald) with standard catalysts; halogen–metal exchange (n-BuLi, −78 °C) at C2 gives the 2-metallo azole, which also forms by deprotonating the C2–H of the unsubstituted azole</t>
+        </is>
+      </c>
+      <c r="F176" s="3" t="n"/>
+      <c r="G176" s="3" t="n"/>
+      <c r="H176" s="3" t="inlineStr">
+        <is>
+          <t>Cl⁻, Br⁻ or I⁻ after addition</t>
+        </is>
+      </c>
+      <c r="I176" s="3" t="n"/>
+      <c r="J176" s="3" t="inlineStr">
+        <is>
+          <t>a 4-substituent next to the ring N slows attack; N–H azoles need SEM, Boc or THP protection before metalation</t>
+        </is>
+      </c>
+      <c r="K176" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L176" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N176" s="3" t="inlineStr">
+        <is>
+          <t>Cl, Br or I on a five-membered ring carbon next to a ring N (2-chlorothiazole, 2-bromoimidazole, 2-chlorobenzothiazole). A narrower split of F047, F013 and F084 (aryl halides); the six-membered rings are F086. [learned from the recorded reactions: in a sample of 200,000 training reactions 2,284 have this group together with its parent; the parent group was consumed in 66% of them against 42% of the 69,678 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 74 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>F176</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>primary alkylamine (R–NH2 on sp3 C; not an aniline)</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>[NX3;H2;+0;!$(N~[!#6;!#1]);!$(N-[#6]=[!#6]);!$(N-[#6]#[!#6])]-[CX4]</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>the N (lone pair)</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>the strongest common nucleophile among primary amines: amide coupling (acid chlorides with Et3N or DIPEA at 0 °C; HATU, EDC/HOBt or T3P with DIPEA at rt), reductive amination (aldehyde, NaBH(OAc)3, AcOH, DCE; or NaBH3CN, MeOH), SNAr with halo-azines (DIPEA, n-BuOH or NMP, 80–150 °C), sulfonylation (RSO2Cl, pyridine or Et3N), carbamate and urea formation (Boc2O; isocyanates), SN2 alkylation (over-alkylation is common: use excess amine or Cs2CO3, DMF), aza-Michael addition, imine formation with aldehydes and ketones</t>
+        </is>
+      </c>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>≈ 35 (N–H; only very strong bases remove it)</t>
+        </is>
+      </c>
+      <c r="G177" s="3" t="inlineStr">
+        <is>
+          <t>≈ 10.6 (RNH3⁺; ethylammonium 10.7, benzylammonium 9.3, 2,2,2-trifluoroethylammonium 5.7)</t>
+        </is>
+      </c>
+      <c r="H177" s="3" t="n"/>
+      <c r="I177" s="3" t="n"/>
+      <c r="J177" s="3" t="inlineStr">
+        <is>
+          <t>low: NH2 is the least hindered amine; branching at the α carbon slows acylation and SN2, and a tert-alkyl amine is a poor nucleophile</t>
+        </is>
+      </c>
+      <c r="K177" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L177" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M177" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N177" s="3" t="inlineStr">
+        <is>
+          <t>NH2 on an sp3 carbon (not an aniline, amide or heteroaryl amine). A narrower split of F002 (amine 1°), whose SMARTS also matches anilines, which have their own fragments (F026, F115). [learned from the recorded reactions: in a sample of 200,000 training reactions 19,976 have this group together with its parent; the parent group was consumed in 94% of them against 74% of the 26,051 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 305 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>F177</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>cyclic secondary amine (piperidine, pyrrolidine, morpholine, piperazine N–H)</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>[NX3;H1;R;!$(NC=O);!$(N-c)]([CX4])[CX4]</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>the N–H nitrogen</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>a better nucleophile than an acyclic dialkylamine of similar basicity (the alkyl groups are tied back): SNAr with halo-arenes and halo-azines (K2CO3 or DIPEA, DMF/DMSO/NMP, 80–140 °C), Buchwald–Hartwig N-arylation (Pd2dba3 with RuPhos, NaOt-Bu), acylation and sulfonylation (rt), reductive amination (NaBH(OAc)3), alkylation (K2CO3, MeCN), carbamate protection (Boc2O, Cbz-Cl). Morpholine is less basic and less nucleophilic; piperazine reacts at both N unless one is protected</t>
+        </is>
+      </c>
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t>≈ 36 (N–H)</t>
+        </is>
+      </c>
+      <c r="G178" s="3" t="inlineStr">
+        <is>
+          <t>≈ 11.1 (piperidinium 11.1; pyrrolidinium 11.3; morpholinium 8.4; piperazinium 9.7)</t>
+        </is>
+      </c>
+      <c r="H178" s="3" t="n"/>
+      <c r="I178" s="3" t="n"/>
+      <c r="J178" s="3" t="inlineStr">
+        <is>
+          <t>low to moderate; 2-substituents on the ring slow acylation and arylation</t>
+        </is>
+      </c>
+      <c r="K178" s="3" t="inlineStr">
+        <is>
+          <t>low: 5- and 6-membered rings</t>
+        </is>
+      </c>
+      <c r="L178" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M178" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N178" s="3" t="inlineStr">
+        <is>
+          <t>N–H in a ring with two sp3 carbons: piperidine, pyrrolidine, morpholine, piperazine, azepane. A narrower split of F034 (amine 2°). [learned from the recorded reactions: in a sample of 200,000 training reactions 16,465 have this group together with its parent; the parent group was consumed in 93% of them against 77% of the 4,990 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 178 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>F178</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>acyclic secondary amine (R2NH: Et2NH, N-methylbenzylamine)</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>[NX3;H1;!R;!$(NC=O);!$(N-c)]([CX4])[CX4]</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>the N–H nitrogen</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>nucleophile and base: acylation, sulfonylation, SNAr, reductive amination, Mannich reactions and enamine formation with ketones and aldehydes. More hindered than a ring amine of the same size, so diisopropylamine is the precursor of the non-nucleophilic base LDA (n-BuLi, THF, −78 °C), and diethylamine is used as a volatile nucleophile</t>
+        </is>
+      </c>
+      <c r="F179" s="3" t="inlineStr">
+        <is>
+          <t>≈ 36 (N–H)</t>
+        </is>
+      </c>
+      <c r="G179" s="3" t="inlineStr">
+        <is>
+          <t>≈ 10.9 (Et2NH2⁺ 10.9; i-Pr2NH2⁺ 11.1; N-methylbenzylammonium 9.6)</t>
+        </is>
+      </c>
+      <c r="H179" s="3" t="n"/>
+      <c r="I179" s="3" t="n"/>
+      <c r="J179" s="3" t="inlineStr">
+        <is>
+          <t>moderate; two α-branches (diisopropylamine) make it non-nucleophilic</t>
+        </is>
+      </c>
+      <c r="K179" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L179" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M179" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N179" s="3" t="inlineStr">
+        <is>
+          <t>R2N–H with both substituents acyclic sp3 carbon. A narrower split of F034 (amine 2°); the ring amines are a separate fragment. [learned from the recorded reactions: in a sample of 200,000 training reactions 5,108 have this group together with its parent; the parent group was consumed in 77% of them against 93% of the 16,347 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 160 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>F179</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>trialkylamine, all three substituents acyclic (Et3N, DIPEA, Me2NR): a base</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>[NX3;H0;+0;!$(N-[C,S,P]=[O,S,N]);!$(N-C#N);!$(N-[#7,#8,#16])]([CX4;!R])([CX4;!R])[CX4;!R]</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>the N lone pair</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>an amine base and acid scavenger for acylations, sulfonylations, SN2 and SNAr (Et3N pKaH 10.75; DIPEA ≈ 11, hindered and non-nucleophilic); a nucleophilic catalyst when unhindered (DABCO, Et3N; DMAP is stronger). With alkyl halides it quaternises (Menshutkin) and the ammonium salt can undergo Hofmann elimination; oxidised to the N-oxide (mCPBA, H2O2); N-dealkylated by chloroformates (ACE-Cl, then MeOH)</t>
+        </is>
+      </c>
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t>no N–H (α C–H ≈ 40)</t>
+        </is>
+      </c>
+      <c r="G180" s="3" t="inlineStr">
+        <is>
+          <t>≈ 10.75 (Et3NH⁺; DIPEA-H⁺ ≈ 11; N,N-dimethylbenzylamine 9.0)</t>
+        </is>
+      </c>
+      <c r="H180" s="3" t="n"/>
+      <c r="I180" s="3" t="n"/>
+      <c r="J180" s="3" t="inlineStr">
+        <is>
+          <t>DIPEA is shielded (non-nucleophilic); Et3N moderately; Me2NR is open</t>
+        </is>
+      </c>
+      <c r="K180" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L180" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M180" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N180" s="3" t="inlineStr">
+        <is>
+          <t>N(CX4)(CX4)CX4 with no ring bond on the three carbons: Et3N, DIPEA, Me2N–R, Bu3N, DMAE. Recorded reactions list these as starting materials mainly when they act as a base, so the group counts as consumed when it is protonated. A narrower split of F093 (amine 3°). [learned from the recorded reactions: in a sample of 200,000 training reactions 4,800 have this group together with its parent; the parent group was consumed in 38% of them against 8% of the 27,939 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 272 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>F180</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>N,N-dialkylaniline (Ar–NR2: dimethylaniline, N-arylpiperazine/piperidine)</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>[NX3;H0;+0;!$(N-[C,S,P]=[O,S,N]);!$(N-C#N);!$(N-[#7,#8,#16])](-c)([CX4])[CX4]</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>the para carbon of the ring and the N lone pair</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>an electron-rich arene: electrophilic substitution para to the amine (Vilsmeier–Haack formylation POCl3/DMF, NBS or Br2 bromination, azo coupling with diazonium salts, nitration only with care); a weak base and nucleophile (pKaH 5.1 for N,N-dimethylaniline); oxidised by mCPBA to the N-oxide or by one-electron oxidants to the radical cation; N-dealkylated by chloroformates (von Braun); directed ortho-lithiation (n-BuLi, TMEDA). In arylpiperazines and arylpiperidines the N is usually a spectator</t>
+        </is>
+      </c>
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t>no N–H (α C–H ≈ 40)</t>
+        </is>
+      </c>
+      <c r="G181" s="3" t="inlineStr">
+        <is>
+          <t>≈ 5.1 (PhNHMe2⁺ 5.1; N-phenylpiperidinium 5.2; 4-nitro analogue ≈ 0.6)</t>
+        </is>
+      </c>
+      <c r="H181" s="3" t="n"/>
+      <c r="I181" s="3" t="n"/>
+      <c r="J181" s="3" t="inlineStr">
+        <is>
+          <t>an ortho substituent twists the NR2 out of conjugation and raises the basicity and nucleophilicity of N</t>
+        </is>
+      </c>
+      <c r="K181" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L181" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M181" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N181" s="3" t="inlineStr">
+        <is>
+          <t>Ar–N(C)C with N bonded to an aromatic carbon and two sp3 carbons (N,N-dimethylaniline, N-arylpiperazine, N-arylpiperidine, N-aryl morpholine). A narrower split of F093 (amine 3°). [learned from the recorded reactions: in a sample of 200,000 training reactions 14,219 have this group together with its parent; the parent group was consumed in 5% of them against 19% of the 18,520 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 161 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>F181</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>secondary amine on a ring N-heteroarene (2-alkylamino-pyridine / pyrimidine / thiazole: Ar(het)–NH–R)</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>[NX3;H1;+0;!$(N-[C,S,P]=[O,S,N]);!$(N-[#7,#8,#16])](-c:[nX2;+0])-[#6]</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>the N–H nitrogen and the ring N</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>a weak N-nucleophile, because the lone pair is delocalised into the ring (amidine-like): acylation needs acid chlorides, or HATU with heat or a stronger base (NaH, LiHMDS); Buchwald–Hartwig N-arylation (Pd2dba3, Xantphos, Cs2CO3); alkyl halides react at the ring N unless the N–H is deprotonated first (NaH, DMF). Made by SNAr of a 2-halo-azine with a primary amine (DIPEA, 100–140 °C) or by Buchwald coupling</t>
+        </is>
+      </c>
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t>≈ 26 (N–H; 2-(methylamino)pyridine, estimate in DMSO)</t>
+        </is>
+      </c>
+      <c r="G182" s="3" t="inlineStr">
+        <is>
+          <t>≈ 7 (2-(alkylamino)pyridinium 7.0; the ring N is the basic site)</t>
+        </is>
+      </c>
+      <c r="H182" s="3" t="n"/>
+      <c r="I182" s="3" t="n"/>
+      <c r="J182" s="3" t="inlineStr">
+        <is>
+          <t>a 3-substituent on the ring slows acylation and arylation</t>
+        </is>
+      </c>
+      <c r="K182" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L182" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M182" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N182" s="3" t="inlineStr">
+        <is>
+          <t>R–NH–c:n. 2-(Alkylamino)pyridine, 2-(alkylamino)pyrimidine, 2-(alkylamino)thiazole, aminopurines. A narrower split of F094 (secondary aryl amine); the NH2 versions are F115. [learned from the recorded reactions: in a sample of 200,000 training reactions 8,852 have this group together with its parent; the parent group was consumed in 11% of them against 39% of the 6,696 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 259 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>F182</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>2-aminoazole NH2 (2-aminothiazole, 2-aminoimidazole, 2-aminooxazole: NH2 on a 5-ring carbon next to a ring N)</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>[nX2;r5]:c-[NX3;H2;+0]</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>the NH2 nitrogen and the ring N</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>an amidine-like, weakly nucleophilic NH2: acylation with acid chlorides (pyridine or Et3N, DCM, 0 °C → rt) or HATU, urea formation with isocyanates, N-arylation (Buchwald: Pd2dba3/Xantphos), diazotisation to the 2-halo-azole (t-BuONO, CuBr2), Hantzsch-type condensation with α-halo ketones to fused imidazoles; the ring N is the more nucleophilic site for alkyl halides; Boc protection needs Boc2O with DMAP</t>
+        </is>
+      </c>
+      <c r="F183" s="3" t="inlineStr">
+        <is>
+          <t>≈ 26 (N–H, estimate in DMSO)</t>
+        </is>
+      </c>
+      <c r="G183" s="3" t="inlineStr">
+        <is>
+          <t>≈ 5.4 (2-aminothiazolium 5.4; 2-aminobenzimidazolium ≈ 7.5; 2-aminoimidazolium ≈ 8.5)</t>
+        </is>
+      </c>
+      <c r="H183" s="3" t="n"/>
+      <c r="I183" s="3" t="n"/>
+      <c r="J183" s="3" t="inlineStr">
+        <is>
+          <t>a 4-substituent next to the ring N slows acylation</t>
+        </is>
+      </c>
+      <c r="K183" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L183" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M183" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N183" s="3" t="inlineStr">
+        <is>
+          <t>NH2 on a five-membered ring carbon next to a ring N (2-aminothiazole, 2-aminoimidazole, 2-aminobenzimidazole, 2-aminooxazole). A narrower split of F115. [learned from the recorded reactions: in a sample of 200,000 training reactions 2,362 have this group together with its parent; the parent group was consumed in 76% of them against 34% of the 6,257 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 164 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>F183</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>aminopyridine / aminopyrimidine NH2 (NH2 on a 6-ring carbon next to a ring N)</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>[nX2;r6]:c-[NX3;H2;+0]</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>the NH2 nitrogen and the ring N</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>a weak nucleophile (amidine-like): acylation and sulfonylation need acid or sulfonyl chlorides with pyridine, or HATU/T3P with DIPEA and heat (bis-acylation is a side reaction); Buchwald–Hartwig coupling (Pd2dba3, Xantphos, Cs2CO3, dioxane, 100 °C); as the nucleophile in SNAr it needs the anion (NaH or LiHMDS); diazotisation to the 2-halo or 2-hydroxy azine; condensation with chloroacetaldehyde gives imidazo[1,2-a]pyridine through the ring N; electrophilic halogenation at C5 (NBS, MeCN)</t>
+        </is>
+      </c>
+      <c r="F184" s="3" t="inlineStr">
+        <is>
+          <t>≈ 28 (N–H; 2-aminopyridine, DMSO)</t>
+        </is>
+      </c>
+      <c r="G184" s="3" t="inlineStr">
+        <is>
+          <t>≈ 6.9 (2-aminopyridinium 6.9; 2-aminopyrimidinium 3.5; 2-aminopyrazinium 3.1)</t>
+        </is>
+      </c>
+      <c r="H184" s="3" t="n"/>
+      <c r="I184" s="3" t="n"/>
+      <c r="J184" s="3" t="inlineStr">
+        <is>
+          <t>a 3-substituent next to the NH2 slows acylation and arylation</t>
+        </is>
+      </c>
+      <c r="K184" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L184" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M184" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N184" s="3" t="inlineStr">
+        <is>
+          <t>NH2 on a six-membered ring carbon next to a ring N (2-aminopyridine, 2-aminopyrimidine, 2-aminopyrazine). A narrower split of F115. [learned from the recorded reactions: in a sample of 200,000 training reactions 6,270 have this group together with its parent; the parent group was consumed in 34% of them against 76% of the 2,349 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 161 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>F184</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>tertiary amide (R–C(=O)–NR2: DMF, DMA, Weinreb amide, N-acylpiperidine, N-alkyl lactam)</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>[CX3;!$(C(-[OX2,SX2,NX3])-[OX2,SX2,NX3])](=[OX1])[NX3;H0;+0]</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>the carbonyl C (hydrolysis, reduction, addition)</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>no N–H. The Weinreb amide (N-methoxy-N-methyl) gives a ketone with RMgX or RLi (one addition, a stable chelate) and an aldehyde with LiAlH4 or DIBAL-H. Other tertiary amides are reduced by LiAlH4 (THF, reflux) or BH3 to the amine, or by Schwartz reagent to the aldehyde; hydrolysed only under forcing conditions (6 M HCl or NaOH, reflux). DMF with POCl3 is the Vilsmeier reagent and with ArLi gives the aldehyde (Bouveault); DMF, DMA and NMP are polar solvents. Tf2O/2-fluoropyridine activation allows addition of nucleophiles; N,N-diethylbenzamides undergo ortho-lithiation (s-BuLi, TMEDA)</t>
+        </is>
+      </c>
+      <c r="F185" s="3" t="inlineStr">
+        <is>
+          <t>no N–H (α C–H ≈ 30)</t>
+        </is>
+      </c>
+      <c r="G185" s="3" t="inlineStr">
+        <is>
+          <t>≈ −0.3 (O-protonated DMF; N,N-dimethylacetamide −0.3)</t>
+        </is>
+      </c>
+      <c r="H185" s="3" t="inlineStr">
+        <is>
+          <t>NR2⁻: very poor</t>
+        </is>
+      </c>
+      <c r="I185" s="3" t="n"/>
+      <c r="J185" s="3" t="inlineStr">
+        <is>
+          <t>N,N-dialkyl groups shield the carbonyl; an α-quaternary centre makes hydrolysis very slow</t>
+        </is>
+      </c>
+      <c r="K185" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L185" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M185" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N185" s="3" t="inlineStr">
+        <is>
+          <t>R–C(=O)–NR2 (carbon or H on the carbonyl, two non-H substituents on N; not a carbamate or urea). A narrower split of F021 (amide). [learned from the recorded reactions: in a sample of 200,000 training reactions 22,467 have this group together with its parent; the parent group was consumed in 33% of them against 23% of the 48,835 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 255 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>F185</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>secondary amide (R–C(=O)–NH–R)</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>[#6][CX3](=[OX1])[NX3;H1;+0]-[#6]</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>the carbonyl C (hydrolysis, reduction), the N–H and the N</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
+        <is>
+          <t>the most robust carbonyl group: stable to base, mild acid and most nucleophiles; hydrolysed only by hot 6 M HCl or NaOH (reflux, hours); reduced by LiAlH4 (THF, reflux) or BH3·THF to the amine; N–H is a weak acid, deprotonated by NaH or LDA for N-alkylation (NaH, RX, DMF) or N-arylation (Goldberg: CuI, DMEDA, K3PO4; Pd/Xantphos); O-alkylation with Meerwein salt (Me3O⁺ BF4⁻) gives the imidate; Tf2O/2-chloropyridine activates it for nucleophiles (Movassaghi); POCl3 gives the imidoyl chloride (Bischler–Napieralski with an N-phenethyl group); a directing group for ortho-lithiation</t>
+        </is>
+      </c>
+      <c r="F186" s="3" t="inlineStr">
+        <is>
+          <t>≈ 17 (N–H; 25.9 in DMSO for N-methylacetamide)</t>
+        </is>
+      </c>
+      <c r="G186" s="3" t="inlineStr">
+        <is>
+          <t>≈ −0.5 (O-protonated amide)</t>
+        </is>
+      </c>
+      <c r="H186" s="3" t="inlineStr">
+        <is>
+          <t>NR⁻: very poor</t>
+        </is>
+      </c>
+      <c r="I186" s="3" t="n"/>
+      <c r="J186" s="3" t="inlineStr">
+        <is>
+          <t>N-alkyl groups, especially tert-alkyl, slow N-functionalisation; an α-quaternary centre protects the carbonyl</t>
+        </is>
+      </c>
+      <c r="K186" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L186" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M186" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N186" s="3" t="inlineStr">
+        <is>
+          <t>R–C(=O)–NH–R with carbon on the carbonyl. A narrower split of F021 (amide) and F095 (amide N–H). [learned from the recorded reactions: in a sample of 200,000 training reactions 24,590 have this group together with its parent; the parent group was consumed in 20% of them against 29% of the 46,712 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 342 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>F186</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>5-membered ring N–H amide / carbamate / urea (γ-lactam, oxazolidinone, hydantoin, thiazolidinedione N–H)</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>[NX3;H1;+0;r5;!a]-[CX3;!a]=[OX1]</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>the N–H (an acid) and the carbonyl C</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="inlineStr">
+        <is>
+          <t>an acidic N–H: deprotonated by K2CO3, Cs2CO3 or NaH for N-alkylation (RX, DMF), N-arylation (Chan–Lam: Cu(OAc)2, ArB(OH)2; Buchwald or CuI/DMEDA) and N-acylation (the Evans oxazolidinone: n-BuLi, or Et3N/DMAP, then RCOCl); thiazolidine-2,4-dione condenses at C5 with aldehydes (Knoevenagel: piperidine, AcOH); hydantoins open with aqueous base to the amino acid</t>
+        </is>
+      </c>
+      <c r="F187" s="3" t="inlineStr">
+        <is>
+          <t>≈ 17 (N–H of a γ-lactam; oxazolidinone ≈ 20 in DMSO, hydantoin 9.1, thiazolidine-2,4-dione 6.5)</t>
+        </is>
+      </c>
+      <c r="G187" s="3" t="inlineStr">
+        <is>
+          <t>≈ −0.5 (O-protonated amide)</t>
+        </is>
+      </c>
+      <c r="H187" s="3" t="inlineStr">
+        <is>
+          <t>NR⁻: poor</t>
+        </is>
+      </c>
+      <c r="I187" s="3" t="n"/>
+      <c r="J187" s="3" t="inlineStr">
+        <is>
+          <t>open at the N–H; a 4-substituent (Evans auxiliary) controls the face of the N-acyl enolate</t>
+        </is>
+      </c>
+      <c r="K187" s="3" t="inlineStr">
+        <is>
+          <t>low: 5-membered ring</t>
+        </is>
+      </c>
+      <c r="L187" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M187" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N187" s="3" t="inlineStr">
+        <is>
+          <t>N–H and C=O in the same five-membered ring: 2-pyrrolidinone, 2-oxazolidinone, hydantoin, thiazolidinedione, imidazolidinone. A narrower split of F095 (amide N–H). [learned from the recorded reactions: in a sample of 200,000 training reactions 3,523 have this group together with its parent; the parent group was consumed in 44% of them against 24% of the 39,389 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 147 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>F187</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>imide N–H (succinimide, glutarimide, thiazolidinedione, maleimide N–H): an acid</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>[CX3](=[OX1])[NX3;+0;H1][CX3]=[OX1]</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>the N–H (acid) and the carbonyl C</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>an acidic N–H (pKa 6–11): the anion alkylates cleanly (K2CO3, RX, DMF; or Mitsunobu with an alcohol: PPh3, DIAD), the Gabriel route to primary amines; N-halogenation gives NBS and NCS (Br2 or Cl2 with NaOH); N-hydroxylation gives NHS; NaOH opens the ring to the amic acid; one C=O is reduced selectively (NaBH4 gives the hydroxylactam, Et3SiH/TFA the lactam)</t>
+        </is>
+      </c>
+      <c r="F188" s="3" t="inlineStr">
+        <is>
+          <t>8.3 (phthalimide; succinimide 9.6; glutarimide 11.4; thiazolidinedione 6.5)</t>
+        </is>
+      </c>
+      <c r="G188" s="3" t="inlineStr">
+        <is>
+          <t>≈ −2 (O-protonated imide)</t>
+        </is>
+      </c>
+      <c r="H188" s="3" t="inlineStr">
+        <is>
+          <t>the imide N⁻ (pKa 8–10) leaves from N-acyl and N-sulfonyl imides</t>
+        </is>
+      </c>
+      <c r="I188" s="3" t="n"/>
+      <c r="J188" s="3" t="inlineStr">
+        <is>
+          <t>open at the N–H</t>
+        </is>
+      </c>
+      <c r="K188" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L188" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M188" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N188" s="3" t="inlineStr">
+        <is>
+          <t>C(=O)–NH–C(=O): phthalimide, succinimide, glutarimide, maleimide, thiazolidinedione with a free N–H. A narrower split of F121 (imide). [learned from the recorded reactions: in a sample of 200,000 training reactions 1,172 have this group together with its parent; the parent group was consumed in 13% of them against 63% of the 4,612 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 114 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>F188</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>N-substituted imide (N-alkyl phthalimide, N-alkyl succinimide: masked amine)</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>[CX3](=[OX1])[NX3;+0;H0]([#6,#7,#8])[CX3]=[OX1]</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>the carbonyl C (ring opening) and the C–N bond (deprotection)</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>a masked amine: the N-alkylphthalimide releases the primary amine with hydrazine hydrate (EtOH, reflux; Ing–Manske), MeNH2 (EtOH, rt) or ethylenediamine; NaBH4 then AcOH (Osby) is a mild alternative; NaOH or HCl hydrolysis is slow. N-Hydroxyphthalimide esters are redox-active esters (Ni, Zn or photoredox decarboxylative coupling); N-acyl imides are active acyl donors (LiOH/H2O2 cleaves an Evans auxiliary)</t>
+        </is>
+      </c>
+      <c r="F189" s="3" t="inlineStr">
+        <is>
+          <t>no N–H (α C–H of a succinimide ≈ 25)</t>
+        </is>
+      </c>
+      <c r="G189" s="3" t="inlineStr">
+        <is>
+          <t>≈ −2 (O-protonated imide)</t>
+        </is>
+      </c>
+      <c r="H189" s="3" t="inlineStr">
+        <is>
+          <t>the phthalimide or succinimide N⁻ leaves from the N-acyl form</t>
+        </is>
+      </c>
+      <c r="I189" s="3" t="n"/>
+      <c r="J189" s="3" t="inlineStr">
+        <is>
+          <t>the N-substituent slows the ring opening; tert-alkyl groups are very slow to deprotect</t>
+        </is>
+      </c>
+      <c r="K189" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L189" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M189" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N189" s="3" t="inlineStr">
+        <is>
+          <t>C(=O)–N(C, N or O)–C(=O): N-alkyl or N-aryl phthalimide, succinimide, N-hydroxyphthalimide, N-acyl imides (not N-halo: F151). A narrower split of F121 (imide). [learned from the recorded reactions: in a sample of 200,000 training reactions 2,882 have this group together with its parent; the parent group was consumed in 39% of them against 67% of the 2,902 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 76 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>F189</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>acyclic enone (chalcone, methyl vinyl ketone: a strong Michael acceptor)</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>[CX3;!R]=[CX3][CX3](=[OX1])[#6]</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>the β carbon (conjugate addition) and the carbonyl C (1,2-addition)</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>a strong Michael acceptor: soft nucleophiles add at the β carbon (thiols with Et3N; amines, aza-Michael, often uncatalysed; malonate and nitroalkanes with DBU or K2CO3; organocuprates R2CuLi, THF, −78 °C); a dienophile (Lewis-acid-catalysed Diels–Alder); hard nucleophiles (RLi, LiAlH4, NaBH4 with CeCl3: Luche) add 1,2 to the carbonyl; nucleophilic epoxidation (H2O2, NaOH; Weitz–Scheffer); selective C=C reduction (H2, Pd/C; NaBH4/NiCl2; L-Selectride; Stryker reagent); Nazarov cyclisation and Robinson annulation. It polymerises (methyl vinyl ketone) and adds water slowly</t>
+        </is>
+      </c>
+      <c r="F190" s="3" t="n"/>
+      <c r="G190" s="3" t="inlineStr">
+        <is>
+          <t>≈ −3 (O-protonated enone)</t>
+        </is>
+      </c>
+      <c r="H190" s="3" t="n"/>
+      <c r="I190" s="3" t="n"/>
+      <c r="J190" s="3" t="inlineStr">
+        <is>
+          <t>α- and β-substituents slow conjugate addition; a β,β-disubstituted enone is far less reactive</t>
+        </is>
+      </c>
+      <c r="K190" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L190" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M190" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N190" s="3" t="inlineStr">
+        <is>
+          <t>C=C–C(=O)–C with the C=C outside a ring: chalcone, methyl vinyl ketone, benzylideneacetone, mesityl oxide. A narrower split of F040 (enone). [learned from the recorded reactions: in a sample of 200,000 training reactions 1,270 have this group together with its parent; the parent group was consumed in 76% of them against 40% of the 1,290 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 137 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>F190</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>cyclic enone (cyclohexenone, cyclopentenone, chromone: ring C=C–C=O)</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>[CX3;R]=[CX3;R][CX3;R](=[OX1])[#6]</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>the β carbon (conjugate addition) and the carbonyl C</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>a Michael acceptor, less reactive than an acyclic enone but readily attacked by cuprates (R2CuLi with TMSCl: the classic 1,4-addition to cyclohexenone), thiols and amines under mild catalysis; Luche reduction (NaBH4, CeCl3, MeOH) gives the allylic alcohol; hydrogenation (H2, Pd/C) reduces the C=C first; nucleophilic epoxidation (H2O2, NaOH); Diels–Alder dienophile; photochemical [2+2]; the product of a Robinson annulation. Ring substituents at C4 and C5 direct the face of attack</t>
+        </is>
+      </c>
+      <c r="F191" s="3" t="n"/>
+      <c r="G191" s="3" t="inlineStr">
+        <is>
+          <t>≈ −3 (O-protonated enone)</t>
+        </is>
+      </c>
+      <c r="H191" s="3" t="n"/>
+      <c r="I191" s="3" t="n"/>
+      <c r="J191" s="3" t="inlineStr">
+        <is>
+          <t>ring conformation and 4-/5-substituents direct the face of attack; a 3-substituent (β) slows conjugate addition</t>
+        </is>
+      </c>
+      <c r="K191" s="3" t="inlineStr">
+        <is>
+          <t>low: 5- and 6-membered rings</t>
+        </is>
+      </c>
+      <c r="L191" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M191" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N191" s="3" t="inlineStr">
+        <is>
+          <t>C=C–C(=O) all in one ring: cyclohexenone, cyclopentenone, chromone, steroid 4-en-3-ones. A narrower split of F040 (enone). [learned from the recorded reactions: in a sample of 200,000 training reactions 1,231 have this group together with its parent; the parent group was consumed in 39% of them against 75% of the 1,329 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 129 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>F191</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>aryl nitrile (Ar–C≡N: benzonitrile, cyanopyridine)</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>c-[CX2]#[NX1]</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>the nitrile C (electrophile)</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>an electrophile at carbon, deactivated by conjugation: hydrolysed to the amide (H2O2/K2CO3, DMSO; or conc. H2SO4, heat) and the acid (6 M HCl or NaOH, reflux); reduced to the benzylamine (LiAlH4, THF; H2/Raney Ni with NH3; BH3·THF; CoCl2/NaBH4) or, with DIBAL-H (toluene, −78 °C), to the aldehyde; Grignard or organolithium addition gives an aryl ketone after hydrolysis; [3+2] with NaN3 (NH4Cl, DMF, 120 °C, or ZnBr2) gives the tetrazole; Pinner reaction (HCl, ROH) gives the imidate; hydroxylamine gives the amidoxime. As a strong EWG it activates ortho/para halides for SNAr and survives most Pd couplings</t>
+        </is>
+      </c>
+      <c r="F192" s="3" t="n"/>
+      <c r="G192" s="3" t="inlineStr">
+        <is>
+          <t>≈ −10 (N-protonated nitrile)</t>
+        </is>
+      </c>
+      <c r="H192" s="3" t="n"/>
+      <c r="I192" s="3" t="n"/>
+      <c r="J192" s="3" t="inlineStr">
+        <is>
+          <t>ortho substituents slow additions</t>
+        </is>
+      </c>
+      <c r="K192" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L192" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M192" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N192" s="3" t="inlineStr">
+        <is>
+          <t>Ar–C≡N: benzonitrile, cyanopyridine, cyanoarenes. A narrower split of F022 (nitrile). [learned from the recorded reactions: in a sample of 200,000 training reactions 11,169 have this group together with its parent; the parent group was consumed in 22% of them against 41% of the 6,653 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 169 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>F192</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>α-C–H of a ketone (R–CO–CH: pKa ≈ 19–20; aldol, enolate alkylation, α-halogenation)</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>[CX4;!H0;!$(C-[F,Cl,Br,I]);!$(C(-[CX3]=[OX1])-[CX3]=[OX1]);!$(C(-[CX3]=[OX1])-C#N);$(C-[CX3](=[OX1])-[#6])]</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>the α carbon and its C–H</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>forms the enol (acid) or enolate (base): aldol (NaOH/EtOH, or LDA, THF, −78 °C), α-alkylation (LDA kinetic at the less substituted side; NaH or KOt-Bu thermodynamic at the more substituted side; then R–X), α-halogenation (Br2/AcOH, NBS/TsOH, CuBr2), Mannich (HCHO, R2NH), Michael addition, α-arylation (Pd, Cs2CO3), Claisen–Schmidt condensation with ArCHO, Stork enamine alkylation, silyl enol ether formation (TMSCl with Et3N, or LDA then TMSCl)</t>
+        </is>
+      </c>
+      <c r="F193" s="3" t="inlineStr">
+        <is>
+          <t>≈ 19 (acetone 19.3; acetophenone 18.3; 26.5 and 24.7 in DMSO)</t>
+        </is>
+      </c>
+      <c r="G193" s="3" t="inlineStr">
+        <is>
+          <t>≈ −7 (O-protonated ketone)</t>
+        </is>
+      </c>
+      <c r="H193" s="3" t="n"/>
+      <c r="I193" s="3" t="n"/>
+      <c r="J193" s="3" t="inlineStr">
+        <is>
+          <t>a bulky base (LDA) takes the less substituted α C–H first; the more substituted gives the more stable enol or enolate</t>
+        </is>
+      </c>
+      <c r="K193" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L193" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M193" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N193" s="3" t="inlineStr">
+        <is>
+          <t>C–H on the carbon next to a ketone C=O (not an α-halo carbon, not between two carbonyls: F102). A narrower split of F101 (enolisable α-C–H). [learned from the recorded reactions: in a sample of 200,000 training reactions 14,443 have this group together with its parent; the parent group was consumed in 63% of them against 48% of the 27,041 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 221 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>F193</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>α-C–H of an ester or lactone (pKa ≈ 25; needs LDA/NaH-strength base)</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>[CX4;!H0;!$(C-[F,Cl,Br,I]);!$(C(-[CX3]=[OX1])-[CX3]=[OX1]);!$(C(-[CX3]=[OX1])-C#N);$(C-[CX3](=[OX1])-[OX2;H0;+0][#6])]</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>the α carbon and its C–H</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>needs a strong base (LDA or LiHMDS, THF, −78 °C; NaH or KOt-Bu in DMF) for the enolate: alkylation (R–I or R–Br), aldol, Claisen condensation (NaOEt in EtOH, matching alkoxide), Michael addition, α-hydroxylation (Davis oxaziridine), α-halogenation (LDA then NBS or I2), α-arylation (Pd, LiHMDS), Ireland–Claisen (silyl ketene acetal). Hydroxide or a non-matching alkoxide hydrolyses or transesterifies the ester instead</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>≈ 25 (ethyl acetate 25.6; 29.5 in DMSO)</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="inlineStr">
+        <is>
+          <t>≈ −6.5 (O-protonated ester)</t>
+        </is>
+      </c>
+      <c r="H194" s="3" t="n"/>
+      <c r="I194" s="3" t="n"/>
+      <c r="J194" s="3" t="inlineStr">
+        <is>
+          <t>a bulky base takes the less substituted α C–H; an α,α-disubstituted ester forms the enolate slowly</t>
+        </is>
+      </c>
+      <c r="K194" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L194" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M194" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N194" s="3" t="inlineStr">
+        <is>
+          <t>C–H on the carbon next to an ester or lactone C=O (not between two carbonyls: F102). A narrower split of F101 (enolisable α-C–H). [learned from the recorded reactions: in a sample of 200,000 training reactions 20,666 have this group together with its parent; the parent group was consumed in 50% of them against 56% of the 20,818 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 217 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>F194</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>α-C–H of a nitrile (pKa ≈ 25; cyanomethyl anion)</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>[CX4;!H0;!$(C-[F,Cl,Br,I]);!$(C(-[CX3]=[OX1])-C#N);!$(C(-C#N)-C#N);$(C-[CX2]#[NX1])]</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>the α carbon and its C–H</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>needs LDA, LiHMDS, KOt-Bu or NaH for the cyanomethyl anion: alkylation (LDA, THF, −78 °C, R–X), Thorpe self-condensation, conjugate addition, α-arylation (Pd/ZnF2, or SNAr with aryl fluorides and KHMDS). Benzylic nitriles (ArCH2CN, pKa 21.9 in DMSO) alkylate under phase-transfer conditions (50 % NaOH, Bu4N⁺ Br⁻, R–X)</t>
+        </is>
+      </c>
+      <c r="F195" s="3" t="inlineStr">
+        <is>
+          <t>≈ 25 (acetonitrile; 31.3 in DMSO; phenylacetonitrile 21.9 in DMSO)</t>
+        </is>
+      </c>
+      <c r="G195" s="3" t="inlineStr">
+        <is>
+          <t>≈ −10 (N-protonated nitrile)</t>
+        </is>
+      </c>
+      <c r="H195" s="3" t="n"/>
+      <c r="I195" s="3" t="n"/>
+      <c r="J195" s="3" t="inlineStr">
+        <is>
+          <t>open; α-branching slows alkylation</t>
+        </is>
+      </c>
+      <c r="K195" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L195" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M195" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N195" s="3" t="inlineStr">
+        <is>
+          <t>C–H on the carbon next to a nitrile C≡N (not between two carbonyls or nitriles: F102). A narrower split of F101 (enolisable α-C–H). [learned from the recorded reactions: in a sample of 200,000 training reactions 2,499 have this group together with its parent; the parent group was consumed in 57% of them against 53% of the 38,985 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 39 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>F195</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>α-C–H of an aldehyde (pKa ≈ 17; enolises most easily)</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>[CX4;!H0;!$(C-[F,Cl,Br,I]);$(C-[CX3H1]=[OX1])]</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>the α carbon and its C–H</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>the most acidic carbonyl C–H: enolises under mild conditions, so aldol condensations run with catalytic base (NaOH, K2CO3) or amine catalysis (proline or pyrrolidine through the enamine: Mannich, α-functionalisation, α-halogenation with NCS or NBS); self-condensation and polymerisation are the side reactions, so enolisable aldehydes are added slowly; α-stereocentres epimerise easily</t>
+        </is>
+      </c>
+      <c r="F196" s="3" t="inlineStr">
+        <is>
+          <t>≈ 17 (acetaldehyde 16.7)</t>
+        </is>
+      </c>
+      <c r="G196" s="3" t="inlineStr">
+        <is>
+          <t>≈ −7 (O-protonated aldehyde)</t>
+        </is>
+      </c>
+      <c r="H196" s="3" t="n"/>
+      <c r="I196" s="3" t="n"/>
+      <c r="J196" s="3" t="inlineStr">
+        <is>
+          <t>open; α-branching slows enolisation</t>
+        </is>
+      </c>
+      <c r="K196" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L196" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M196" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N196" s="3" t="inlineStr">
+        <is>
+          <t>C–H on the carbon next to an aldehyde C=O. A narrower split of F101 (enolisable α-C–H). [learned from the recorded reactions: in a sample of 200,000 training reactions 1,957 have this group together with its parent; the parent group was consumed in 93% of them against 51% of the 39,527 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 152 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="inlineStr">
+        <is>
+          <t>F196</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>aldimine / aldoxime (H–C=N: one substituent on carbon)</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>[CX3;H1]=[NX2]</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>the C of the C=N (electrophile) and the N</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>more electrophilic and less hindered than a ketimine: reduced and attacked under mild conditions (NaBH3CN at pH 6; Strecker; Mannich; allyl- and crotylboronates); formed reversibly from aldehydes and amines (MgSO4 or 4 Å sieves, or Dean–Stark) and hydrolysed easily; aldoximes dehydrate (Ac2O, Burgess reagent, SOCl2) to nitriles and are oxidised (NCS/pyridine, NaOCl) to nitrile oxides for [3+2] cycloadditions; with an α C–H it tautomerises to the enamine</t>
+        </is>
+      </c>
+      <c r="F197" s="3" t="inlineStr">
+        <is>
+          <t>≈ 11 (aldoxime O–H 10.7–11.3)</t>
+        </is>
+      </c>
+      <c r="G197" s="3" t="inlineStr">
+        <is>
+          <t>≈ 7 (aldimine; aldoxime ≈ 1)</t>
+        </is>
+      </c>
+      <c r="H197" s="3" t="n"/>
+      <c r="I197" s="3" t="n"/>
+      <c r="J197" s="3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="K197" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L197" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M197" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N197" s="3" t="inlineStr">
+        <is>
+          <t>H–C=N: aldimines, aldoximes, aldehyde hydrazones (formaldehyde-derived CH2=N is not included). A narrower split of F031 (imine). [learned from the recorded reactions: in a sample of 200,000 training reactions 1,490 have this group together with its parent; the parent group was consumed in 70% of them against 38% of the 8,096 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 107 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="inlineStr">
+        <is>
+          <t>F197</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>methanol (CH3–OH): reagent and solvent</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>[CH3]-[OX2H1]</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>the O–H (nucleophile) and, activated, the CH3–O bond</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
+          <t>solvent and reagent: Fischer esterification (H2SO4 or HCl, reflux; SOCl2 or TMSCl in MeOH; DCC/DMAP or EDC for acids), transesterification, methanolysis of acid chlorides and anhydrides, methyl ether formation (NaH then MeI; Mitsunobu with phenols), dimethyl acetal and ketal formation (TsOH or CSA, with HC(OMe)3), hydrogenation and NaBH4 reductions run in it. In base it is NaOMe; it quenches Grignard and organolithium reagents</t>
+        </is>
+      </c>
+      <c r="F198" s="3" t="inlineStr">
+        <is>
+          <t>15.5 (methanol; 29.0 in DMSO)</t>
+        </is>
+      </c>
+      <c r="G198" s="3" t="inlineStr">
+        <is>
+          <t>≈ −2.2 (CH3OH2⁺)</t>
+        </is>
+      </c>
+      <c r="H198" s="3" t="inlineStr">
+        <is>
+          <t>MeOH2⁺ leaves from the protonated alcohol (SN2 at CH3)</t>
+        </is>
+      </c>
+      <c r="I198" s="3" t="n"/>
+      <c r="J198" s="3" t="inlineStr">
+        <is>
+          <t>the smallest alcohol: the most nucleophilic towards hindered electrophiles</t>
+        </is>
+      </c>
+      <c r="K198" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L198" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M198" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N198" s="3" t="inlineStr">
+        <is>
+          <t>CH3–OH. Recorded reactions list it as a starting material mainly when it is the reagent. A narrower split of F014 (alcohol on sp3 C). [learned from the recorded reactions: in a sample of 200,000 training reactions 1,113 have this group together with its parent; the parent group was consumed in 94% of them against 57% of the 28,055 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 151 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="inlineStr">
+        <is>
+          <t>F198</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>ethanol (CH3CH2–OH): reagent and solvent</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>[CH3]-[CH2]-[OX2H1]</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>the O–H (nucleophile) and, activated, the CH3CH2–O bond</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>solvent and reagent: Fischer esterification (H2SO4 or HCl, reflux), transesterification, ethanolysis of acid chlorides and anhydrides, ethyl ether formation (NaH then EtI), diethyl acetal and ketal formation (TsOH, HC(OEt)3), NaOEt for Claisen and malonic ester syntheses (matching the ester avoids transesterification), a protic solvent for NaBH4 reductions and hydrogenations. It quenches Grignard and organolithium reagents</t>
+        </is>
+      </c>
+      <c r="F199" s="3" t="inlineStr">
+        <is>
+          <t>15.9 (ethanol; 29.8 in DMSO)</t>
+        </is>
+      </c>
+      <c r="G199" s="3" t="inlineStr">
+        <is>
+          <t>≈ −2.4 (CH3CH2OH2⁺)</t>
+        </is>
+      </c>
+      <c r="H199" s="3" t="inlineStr">
+        <is>
+          <t>EtOH2⁺ leaves from the protonated alcohol</t>
+        </is>
+      </c>
+      <c r="I199" s="3" t="n"/>
+      <c r="J199" s="3" t="inlineStr">
+        <is>
+          <t>small: slightly less nucleophilic than methanol</t>
+        </is>
+      </c>
+      <c r="K199" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L199" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M199" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N199" s="3" t="inlineStr">
+        <is>
+          <t>CH3–CH2–OH. Recorded reactions list it as a starting material mainly when it is the reagent. A narrower split of F003 (alcohol 1°). [learned from the recorded reactions: in a sample of 200,000 training reactions 866 have this group together with its parent; the parent group was consumed in 98% of them against 64% of the 14,113 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 95 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>F199</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>benzylic alcohol (Ar–CH2–OH)</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>c-[CX4;H2]-[OX2H1]</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>the O–H (nucleophile), the benzylic C–H (oxidation) and the C–O bond (activation)</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>oxidised to the aldehyde (MnO2, selective for benzylic and allylic; Dess–Martin periodinane; Swern; TEMPO/PhI(OAc)2; Cu/TEMPO/air) and to the acid (Jones, KMnO4); converted to the benzylic chloride or bromide readily (SOCl2, PBr3, MsCl then LiBr, CBr4/PPh3; fast and SN1-like for electron-rich aryl groups); Mitsunobu; ether and ester formation (NaH, RX; RCOCl, Et3N); hydrogenolysis of the C–O bond (H2, Pd/C) for neutral and electron-rich aryl groups; acid-catalysed Friedel–Crafts alkylation through the benzylic cation</t>
+        </is>
+      </c>
+      <c r="F200" s="3" t="inlineStr">
+        <is>
+          <t>15.4 (benzyl alcohol; 27.0 in DMSO)</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="inlineStr">
+        <is>
+          <t>≈ −2 (ArCH2OH2⁺)</t>
+        </is>
+      </c>
+      <c r="H200" s="3" t="inlineStr">
+        <is>
+          <t>H2O after protonation or activation (OMs, OTs, OTf); benzylic cation stabilised by the ring</t>
+        </is>
+      </c>
+      <c r="I200" s="3" t="n"/>
+      <c r="J200" s="3" t="inlineStr">
+        <is>
+          <t>open (primary)</t>
+        </is>
+      </c>
+      <c r="K200" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L200" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M200" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N200" s="3" t="inlineStr">
+        <is>
+          <t>Ar–CH2–OH. A narrower split of F130 (benzyl group on O, N or S) and of F003 (alcohol 1°). [learned from the recorded reactions: in a sample of 200,000 training reactions 3,672 have this group together with its parent; the parent group was consumed in 46% of them against 13% of the 28,607 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 385 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>F200</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>orthoester (R–C(OR)3: triethyl orthoformate, trimethyl orthoacetate)</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>[CX4]([OX2][#6])([OX2][#6])[OX2][#6]</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>the central carbon (electrophile) and the C–O bonds</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>a reagent: a water scavenger and a source of an ester, acetal or ethoxymethylene group. Acid-catalysed (TsOH, CSA) formation of acetals and ketals from carbonyls (HC(OMe)3, MeOH); esters from acids (heat); the Johnson–Claisen rearrangement with allylic alcohols (CH3C(OEt)3, cat. propionic acid, 140 °C); ethoxymethylene derivatives of active methylenes (HC(OEt)3, Ac2O); amidines and heterocycles with amines (with NaN3 gives tetrazoles; with 2-aminobenzamides gives quinazolinones). Hydrolyses at once in aqueous acid to the ester and alcohol</t>
+        </is>
+      </c>
+      <c r="F201" s="3" t="n"/>
+      <c r="G201" s="3" t="n"/>
+      <c r="H201" s="3" t="inlineStr">
+        <is>
+          <t>ROH after protonation (a stabilised dialkoxycarbenium ion)</t>
+        </is>
+      </c>
+      <c r="I201" s="3" t="n"/>
+      <c r="J201" s="3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="K201" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L201" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M201" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N201" s="3" t="inlineStr">
+        <is>
+          <t>C(OR)3 on carbon: triethyl orthoformate, trimethyl orthoacetate, trimethyl orthobenzoate. A reagent: it is consumed in nearly every recorded reaction that lists it. A narrower split of F039 (acetal / ketal). [learned from the recorded reactions: in a sample of 200,000 training reactions 465 have this group together with its parent; the parent group was consumed in 95% of them against 34% of the 6,540 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 108 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="inlineStr">
+        <is>
+          <t>F201</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>amide acetal / aminal ether (DMF-DMA: Me2N–CH(OMe)2)</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>[CX4]([OX2][#6])([OX2][#6])[NX3]</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>the central carbon (electrophile) and the OMe groups (methylation)</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>a formylating and methylating reagent: with active methylene groups and methyl ketones it gives the enaminone (toluene or neat, 80–110 °C), the usual route to pyrazoles, pyrimidines, isoxazoles and indoles (Leimgruber–Batcho: o-nitrotoluene, DMF-DMA, pyrrolidine, then reduction); it methylates carboxylic acids, phenols, thiols and N–H heterocycles on heating; with primary amides it gives the N-acyl formamidine; transaminates with amines; hydrolyses to DMF and methanol in water. Bredereck reagent (t-BuO–CH(NMe2)2) is the stronger, more hindered relative</t>
+        </is>
+      </c>
+      <c r="F202" s="3" t="n"/>
+      <c r="G202" s="3" t="n"/>
+      <c r="H202" s="3" t="inlineStr">
+        <is>
+          <t>MeOH or Me2NH</t>
+        </is>
+      </c>
+      <c r="I202" s="3" t="n"/>
+      <c r="J202" s="3" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="K202" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L202" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M202" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N202" s="3" t="inlineStr">
+        <is>
+          <t>C(OR)(OR)N: N,N-dimethylformamide dimethyl acetal (DMF-DMA), DMF diethyl acetal, Bredereck reagent. A reagent: it is consumed in nearly every recorded reaction that lists it. A narrower split of F039 (acetal / ketal). [learned from the recorded reactions: in a sample of 200,000 training reactions 337 have this group together with its parent; the parent group was consumed in 98% of them against 35% of the 6,668 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 75 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="inlineStr">
+        <is>
+          <t>F202</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>lactam, 5- to 7-membered (pyrrolidinone, piperidinone, caprolactam, oxindole)</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>[#6][CX3;r5,r6,r7](=[OX1])[NX3;r5,r6,r7;+0]</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>the carbonyl C (ring opening, reduction) and the N</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>ring amides are stable to nucleophiles; ring-opening hydrolysis needs hot strong acid or base; N–H lactams are alkylated (NaH, RX, DMF) or acylated (Boc2O, DMAP: the N-Boc lactam opens with LiOH or amines); N-substituted lactams are reduced by LiAlH4 or BH3 to the cyclic amine; Lawesson reagent gives the thiolactam; Meerwein salt gives the lactim ether; the α C–H forms the lactam enolate (LDA, THF, −78 °C; the N is protected)</t>
+        </is>
+      </c>
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t>≈ 17 (N–H; 2-pyrrolidinone 24.2 in DMSO)</t>
+        </is>
+      </c>
+      <c r="G203" s="3" t="inlineStr">
+        <is>
+          <t>≈ −0.2 (O-protonated 2-pyrrolidinone)</t>
+        </is>
+      </c>
+      <c r="H203" s="3" t="inlineStr">
+        <is>
+          <t>NR⁻: very poor</t>
+        </is>
+      </c>
+      <c r="I203" s="3" t="n"/>
+      <c r="J203" s="3" t="inlineStr">
+        <is>
+          <t>moderate; ring substituents next to the N or the carbonyl slow acylation and hydrolysis</t>
+        </is>
+      </c>
+      <c r="K203" s="3" t="inlineStr">
+        <is>
+          <t>low for 5- to 7-membered lactams (a β-lactam is strained and reacts very differently: it is not included)</t>
+        </is>
+      </c>
+      <c r="L203" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M203" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N203" s="3" t="inlineStr">
+        <is>
+          <t>Cyclic amide in a 5-, 6- or 7-membered ring: pyrrolidinone, piperidinone, caprolactam, oxindole, N-aryl lactams. A narrower split of F021 (amide). [learned from the recorded reactions: in a sample of 200,000 training reactions 14,911 have this group together with its parent; the parent group was consumed in 30% of them against 25% of the 56,391 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 37 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>F203</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>acyclic enamine / enaminone (N–CH=C: Me2N–CH=CH–C(=O)R from DMF-DMA)</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>[CX3]=[CX3;!R]-[NX3;+0;!$(N-C=O);!$(N-S(=O)=O);!$(N-c)]</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>the β carbon (nucleophile) and, in an enaminone, the N-bearing carbon (electrophile)</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>nucleophilic at the β carbon (Stork enamine alkylation and acylation, then H3O⁺ hydrolysis to the carbonyl); the enaminone from a methyl ketone and DMF-DMA (toluene or neat, 80–110 °C) is the standard precursor of heterocycles: hydrazines give pyrazoles, amidines and guanidines give pyrimidines, hydroxylamine gives isoxazoles, amines exchange the Me2N group by addition–elimination; hydrolysed by aqueous acid; reduced by NaBH3CN</t>
+        </is>
+      </c>
+      <c r="F204" s="3" t="n"/>
+      <c r="G204" s="3" t="inlineStr">
+        <is>
+          <t>≈ 9 (simple enamine; an enaminone ≈ 3 on O)</t>
+        </is>
+      </c>
+      <c r="H204" s="3" t="inlineStr">
+        <is>
+          <t>Me2NH after addition–elimination</t>
+        </is>
+      </c>
+      <c r="I204" s="3" t="n"/>
+      <c r="J204" s="3" t="inlineStr">
+        <is>
+          <t>open; the (E)-isomer dominates</t>
+        </is>
+      </c>
+      <c r="K204" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L204" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M204" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N204" s="3" t="inlineStr">
+        <is>
+          <t>N–CH=C with the carbon bonded to N outside a ring: enamines of acyclic ketones, DMF-DMA enaminones (Me2N–CH=CH–C(=O)R), push–pull alkenes. A narrower split of F127 (enamine / enaminone). [learned from the recorded reactions: in a sample of 200,000 training reactions 847 have this group together with its parent; the parent group was consumed in 77% of them against 46% of the 699 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 120 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>F204</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>acyclic imine / oxime / hydrazone (C=N not in a ring)</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>[CX3]=[NX2;!R]</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>the C of the C=N (electrophile) and the N</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>an electrophile at carbon, reduced to the amine (NaBH4, NaBH3CN, NaBH(OAc)3 in reductive amination; H2/Pd; LiAlH4); Strecker (TMSCN), Mannich and Grignard/organolithium addition; hydrolysed back to the carbonyl in aqueous acid. Oximes undergo Beckmann rearrangement (TsCl, PCl5, H2SO4), reduction to the amine (LiAlH4, H2/Raney Ni, Zn/AcOH) and, as aldoximes, dehydration to the nitrile; hydrazones give Wolff–Kishner and Shapiro reactions; Ellman N-sulfinyl imines add RMgX diastereoselectively; the α C–H forms the aza-enolate (LDA)</t>
+        </is>
+      </c>
+      <c r="F205" s="3" t="inlineStr">
+        <is>
+          <t>≈ 11 (oxime O–H: acetone oxime 12.4; benzaldoxime 10.7; an N-alkyl imine has no acidic H)</t>
+        </is>
+      </c>
+      <c r="G205" s="3" t="inlineStr">
+        <is>
+          <t>≈ 7 (N-alkyl imine; oxime ≈ 1; hydrazone ≈ 3)</t>
+        </is>
+      </c>
+      <c r="H205" s="3" t="n"/>
+      <c r="I205" s="3" t="n"/>
+      <c r="J205" s="3" t="inlineStr">
+        <is>
+          <t>ketimines are more hindered than aldimines; N-aryl imines are less basic and more hydrolytically labile</t>
+        </is>
+      </c>
+      <c r="K205" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L205" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M205" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N205" s="3" t="inlineStr">
+        <is>
+          <t>C=N with the nitrogen outside a ring: Schiff bases, oximes, hydrazones, N-sulfinyl imines. A narrower split of F031 (imine). [learned from the recorded reactions: in a sample of 200,000 training reactions 5,891 have this group together with its parent; the parent group was consumed in 57% of them against 20% of the 3,695 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 230 nats of log-likelihood]</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t>F205</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>2-sulfonyl / 2-sulfinyl azine (SO2R on a ring carbon next to a ring N: an SNAr leaving group)</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>[#6]-[S;$([SX3]=[OX1]),$([SX4](=[OX1])=[OX1])]-c:[nX2;+0]</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>the ring carbon bearing the sulfonyl or sulfinyl group (attacked at the ipso position)</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>an SNAr electrophile with an excellent leaving group (sulfinate), more reactive than the chloro analogue: amines (DIPEA, THF or MeCN, rt–60 °C), alkoxides, thiolates, cyanide and carbanions displace it at rt; 2-sulfonylpyrimidines arylate cysteine selectively at pH 7. Made by oxidising the methylthio-azine (mCPBA, DCM; Oxone, H2O/MeOH; H2O2 with Na2WO4). The other use of a heteroaryl sulfone is the Julia–Kocienski olefination (benzothiazolyl and phenyltetrazolyl sulfones, KHMDS, DME, −55 °C, with an aldehyde)</t>
+        </is>
+      </c>
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t>no acidic H on the ring; the α C–H of the sulfone ≈ 29 (DMSO)</t>
+        </is>
+      </c>
+      <c r="G206" s="3" t="inlineStr">
+        <is>
+          <t>≈ −2 (the ring N; weakly basic)</t>
+        </is>
+      </c>
+      <c r="H206" s="3" t="inlineStr">
+        <is>
+          <t>RSO2⁻ (sulfinate; pKa of the sulfinic acid ≈ 2): excellent</t>
+        </is>
+      </c>
+      <c r="I206" s="3" t="n"/>
+      <c r="J206" s="3" t="inlineStr">
+        <is>
+          <t>a substituent next to the C–S slows attack</t>
+        </is>
+      </c>
+      <c r="K206" s="3" t="inlineStr">
+        <is>
+          <t>none: not a ring fragment</t>
+        </is>
+      </c>
+      <c r="L206" s="3" t="inlineStr">
+        <is>
+          <t>typical values in water (DMSO where marked): Evans pKa table; Bordwell; Clayden, Organic Chemistry (approximate: the rest of the molecule shifts them)</t>
+        </is>
+      </c>
+      <c r="M206" s="3" t="inlineStr">
+        <is>
+          <t>sub-fragment learned from the recorded reactions (tools/subfragment_scan.py, tools/new_subfragments.py; RDKit-checked SMARTS)</t>
+        </is>
+      </c>
+      <c r="N206" s="3" t="inlineStr">
+        <is>
+          <t>R–S(=O)(=O)–c:n and R–S(=O)–c:n: 2-(methylsulfonyl)pyrimidine, 2-sulfonylpyridine, 2-(methylsulfonyl)benzothiazole. A narrower split of F071 (sulfone / sulfoxide). [learned from the recorded reactions: in a sample of 200,000 training reactions 990 have this group together with its parent; the parent group was consumed in 75% of them against 11% of the 5,014 that have the parent without this feature, for the same kind of reagent; on reactions the rates had not seen it adds 120 nats of log-likelihood]</t>
         </is>
       </c>
     </row>
